--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/srrb.ru</t>
+          <t>https://logos.hunter.io/srrb.ru</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/apni.ru</t>
+          <t>https://logos.hunter.io/apni.ru</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tvkinoradio.ru</t>
+          <t>https://logos.hunter.io/tvkinoradio.ru</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/politnavigator.net</t>
+          <t>https://logos.hunter.io/politnavigator.net</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bloknot.ru</t>
+          <t>https://logos.hunter.io/bloknot.ru</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/delovoymir.biz</t>
+          <t>https://logos.hunter.io/delovoymir.biz</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/business-magazine.online</t>
+          <t>https://logos.hunter.io/business-magazine.online</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/garant.ru</t>
+          <t>https://logos.hunter.io/garant.ru</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/prophotos.ru</t>
+          <t>https://logos.hunter.io/prophotos.ru</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/peopletalk.ru</t>
+          <t>https://logos.hunter.io/peopletalk.ru</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/versia.ru</t>
+          <t>https://logos.hunter.io/versia.ru</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/infox.ru</t>
+          <t>https://logos.hunter.io/infox.ru</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/samag.ru</t>
+          <t>https://logos.hunter.io/samag.ru</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/itweek.ru</t>
+          <t>https://logos.hunter.io/itweek.ru</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/1sept.ru</t>
+          <t>https://logos.hunter.io/1sept.ru</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/finversia.ru</t>
+          <t>https://logos.hunter.io/finversia.ru</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mir24.tv</t>
+          <t>https://logos.hunter.io/mir24.tv</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lenta.ru</t>
+          <t>https://logos.hunter.io/lenta.ru</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/7days.ru</t>
+          <t>https://logos.hunter.io/7days.ru</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vokrug.tv</t>
+          <t>https://logos.hunter.io/vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fedpress.ru</t>
+          <t>https://logos.hunter.io/fedpress.ru</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/securitylab.ru</t>
+          <t>https://logos.hunter.io/securitylab.ru</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/osnmedia.ru</t>
+          <t>https://logos.hunter.io/osnmedia.ru</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/snob.ru</t>
+          <t>https://logos.hunter.io/snob.ru</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/comnews.ru</t>
+          <t>https://logos.hunter.io/comnews.ru</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tproger.ru</t>
+          <t>https://logos.hunter.io/tproger.ru</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/cnews.ru</t>
+          <t>https://logos.hunter.io/cnews.ru</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/iz.ru</t>
+          <t>https://logos.hunter.io/iz.ru</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sport-express.ru</t>
+          <t>https://logos.hunter.io/sport-express.ru</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/newdaynews.ru</t>
+          <t>https://logos.hunter.io/newdaynews.ru</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gazetametro.ru</t>
+          <t>https://logos.hunter.io/gazetametro.ru</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/5-tv.ru</t>
+          <t>https://logos.hunter.io/5-tv.ru</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dk.ru</t>
+          <t>https://logos.hunter.io/dk.ru</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/strategyjournal.ru</t>
+          <t>https://logos.hunter.io/strategyjournal.ru</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/retailer.ru</t>
+          <t>https://logos.hunter.io/retailer.ru</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mk.ru</t>
+          <t>https://logos.hunter.io/mk.ru</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aif.ru</t>
+          <t>https://logos.hunter.io/aif.ru</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vedomosti.ru</t>
+          <t>https://logos.hunter.io/vedomosti.ru</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ng.ru</t>
+          <t>https://logos.hunter.io/ng.ru</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/business.ru</t>
+          <t>https://logos.hunter.io/business.ru</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kom-dir.ru</t>
+          <t>https://logos.hunter.io/kom-dir.ru</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/glavbukh.ru</t>
+          <t>https://logos.hunter.io/glavbukh.ru</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/26-2.ru</t>
+          <t>https://logos.hunter.io/26-2.ru</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/buhsoft.ru</t>
+          <t>https://logos.hunter.io/buhsoft.ru</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/pro-personal.ru</t>
+          <t>https://logos.hunter.io/pro-personal.ru</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kdelo.ru</t>
+          <t>https://logos.hunter.io/kdelo.ru</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tass.ru</t>
+          <t>https://logos.hunter.io/tass.ru</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gazeta.ru</t>
+          <t>https://logos.hunter.io/gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vm.ru</t>
+          <t>https://logos.hunter.io/vm.ru</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/news.ru</t>
+          <t>https://logos.hunter.io/news.ru</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/profile.ru</t>
+          <t>https://logos.hunter.io/profile.ru</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/oilcapital.ru</t>
+          <t>https://logos.hunter.io/oilcapital.ru</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/business-gazeta.ru</t>
+          <t>https://logos.hunter.io/business-gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ko.ru</t>
+          <t>https://logos.hunter.io/ko.ru</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dp.ru</t>
+          <t>https://logos.hunter.io/dp.ru</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/popmech.ru</t>
+          <t>https://logos.hunter.io/popmech.ru</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/svpressa.ru</t>
+          <t>https://logos.hunter.io/svpressa.ru</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ridus.ru</t>
+          <t>https://logos.hunter.io/ridus.ru</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dni.ru</t>
+          <t>https://logos.hunter.io/dni.ru</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/utro.ru</t>
+          <t>https://logos.hunter.io/utro.ru</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kleo.ru</t>
+          <t>https://logos.hunter.io/kleo.ru</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/newizv.ru</t>
+          <t>https://logos.hunter.io/newizv.ru</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/rosbalt.ru</t>
+          <t>https://logos.hunter.io/rosbalt.ru</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/monocle.ru</t>
+          <t>https://logos.hunter.io/monocle.ru</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/rg.ru</t>
+          <t>https://logos.hunter.io/rg.ru</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/runews24.ru</t>
+          <t>https://logos.hunter.io/runews24.ru</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/angi.ru</t>
+          <t>https://logos.hunter.io/angi.ru</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/naked-science.ru</t>
+          <t>https://logos.hunter.io/naked-science.ru</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/globalcio.ru</t>
+          <t>https://logos.hunter.io/globalcio.ru</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businesstory.ru</t>
+          <t>https://logos.hunter.io/businesstory.ru</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ict-online.ru</t>
+          <t>https://logos.hunter.io/ict-online.ru</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/logirus.ru</t>
+          <t>https://logos.hunter.io/logirus.ru</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/24gadget.ru</t>
+          <t>https://logos.hunter.io/24gadget.ru</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/marieclaire.com</t>
+          <t>https://logos.hunter.io/marieclaire.com</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/3dnews.ru</t>
+          <t>https://logos.hunter.io/3dnews.ru</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/servernews.ru</t>
+          <t>https://logos.hunter.io/servernews.ru</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/new-retail.ru</t>
+          <t>https://logos.hunter.io/new-retail.ru</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nakanune.ru</t>
+          <t>https://logos.hunter.io/nakanune.ru</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/telecomdaily.ru</t>
+          <t>https://logos.hunter.io/telecomdaily.ru</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bigpicture.ru</t>
+          <t>https://logos.hunter.io/bigpicture.ru</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kommersant.ru</t>
+          <t>https://logos.hunter.io/kommersant.ru</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/eadaily.com</t>
+          <t>https://logos.hunter.io/eadaily.com</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sostav.ru</t>
+          <t>https://logos.hunter.io/sostav.ru</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ura.news</t>
+          <t>https://logos.hunter.io/ura.news</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/seonews.ru</t>
+          <t>https://logos.hunter.io/seonews.ru</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/likeni.ru</t>
+          <t>https://logos.hunter.io/likeni.ru</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/life.ru</t>
+          <t>https://logos.hunter.io/life.ru</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sportmk.ru</t>
+          <t>https://logos.hunter.io/sportmk.ru</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/omanhit.ru</t>
+          <t>https://logos.hunter.io/omanhit.ru</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/avtovzglyad.ru</t>
+          <t>https://logos.hunter.io/avtovzglyad.ru</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ohotniki.ru</t>
+          <t>https://logos.hunter.io/ohotniki.ru</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mperspektiva.ru</t>
+          <t>https://logos.hunter.io/mperspektiva.ru</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/beautyhack.ru</t>
+          <t>https://logos.hunter.io/beautyhack.ru</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sobaka.ru</t>
+          <t>https://logos.hunter.io/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sobaka.ru</t>
+          <t>https://logos.hunter.io/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sobaka.ru</t>
+          <t>https://logos.hunter.io/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/forbes.ru</t>
+          <t>https://logos.hunter.io/forbes.ru</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/stroygaz.ru</t>
+          <t>https://logos.hunter.io/stroygaz.ru</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/regnum.ru</t>
+          <t>https://logos.hunter.io/regnum.ru</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/topcor.ru</t>
+          <t>https://logos.hunter.io/topcor.ru</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sfera.fm</t>
+          <t>https://logos.hunter.io/sfera.fm</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/brl.mk.ru</t>
+          <t>https://logos.hunter.io/brl.mk.ru</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/novate.ru</t>
+          <t>https://logos.hunter.io/novate.ru</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/beautycarteblanche.ru</t>
+          <t>https://logos.hunter.io/beautycarteblanche.ru</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vokrug.tv</t>
+          <t>https://logos.hunter.io/vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vokrugsveta.ru</t>
+          <t>https://logos.hunter.io/vokrugsveta.ru</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/oman.ru</t>
+          <t>https://logos.hunter.io/oman.ru</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/day.ru</t>
+          <t>https://logos.hunter.io/day.ru</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thegirl.ru</t>
+          <t>https://logos.hunter.io/thegirl.ru</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/starhit.ru</t>
+          <t>https://logos.hunter.io/starhit.ru</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/parents.ru</t>
+          <t>https://logos.hunter.io/parents.ru</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mydecor.ru</t>
+          <t>https://logos.hunter.io/mydecor.ru</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/doctorpiter.ru</t>
+          <t>https://logos.hunter.io/doctorpiter.ru</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/the-day.ru</t>
+          <t>https://logos.hunter.io/the-day.ru</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/maximonline.ru</t>
+          <t>https://logos.hunter.io/maximonline.ru</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/psychologies.ru</t>
+          <t>https://logos.hunter.io/psychologies.ru</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fashiontime.ru</t>
+          <t>https://logos.hunter.io/fashiontime.ru</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/oane.ws</t>
+          <t>https://logos.hunter.io/oane.ws</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/terrnews.com</t>
+          <t>https://logos.hunter.io/terrnews.com</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kadara.ru</t>
+          <t>https://logos.hunter.io/kadara.ru</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/monavista.ru</t>
+          <t>https://logos.hunter.io/monavista.ru</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vestnik.net</t>
+          <t>https://logos.hunter.io/vestnik.net</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nvspost.ru</t>
+          <t>https://logos.hunter.io/nvspost.ru</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/spb.kp.ru</t>
+          <t>https://logos.hunter.io/spb.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/belarus.kp.ru</t>
+          <t>https://logos.hunter.io/belarus.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/—</t>
+          <t>https://logos.hunter.io/—</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/news-24.ru</t>
+          <t>https://logos.hunter.io/news-24.ru</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/smi24.news</t>
+          <t>https://logos.hunter.io/smi24.news</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/obzor-gazet.ru</t>
+          <t>https://logos.hunter.io/obzor-gazet.ru</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/allmosnews.ru</t>
+          <t>https://logos.hunter.io/allmosnews.ru</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/promgoverment.ru</t>
+          <t>https://logos.hunter.io/promgoverment.ru</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/hotrs.su</t>
+          <t>https://logos.hunter.io/hotrs.su</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mirwiki.ru</t>
+          <t>https://logos.hunter.io/mirwiki.ru</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/news-bank.ru</t>
+          <t>https://logos.hunter.io/news-bank.ru</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/frequentflyers.ru</t>
+          <t>https://logos.hunter.io/frequentflyers.ru</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/adindex.ru</t>
+          <t>https://logos.hunter.io/adindex.ru</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/artagmag.ru</t>
+          <t>https://logos.hunter.io/artagmag.ru</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sport24.ru</t>
+          <t>https://logos.hunter.io/sport24.ru</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/prufy.ru</t>
+          <t>https://logos.hunter.io/prufy.ru</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/schoolotzyv.ru</t>
+          <t>https://logos.hunter.io/schoolotzyv.ru</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/moneytimes.ru</t>
+          <t>https://logos.hunter.io/moneytimes.ru</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/english.pravda.ru</t>
+          <t>https://logos.hunter.io/english.pravda.ru</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/medpulse.ru</t>
+          <t>https://logos.hunter.io/medpulse.ru</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/newsinfo.ru</t>
+          <t>https://logos.hunter.io/newsinfo.ru</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/politonline.ru</t>
+          <t>https://logos.hunter.io/politonline.ru</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/greatlove.ru</t>
+          <t>https://logos.hunter.io/greatlove.ru</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/yoki.ru</t>
+          <t>https://logos.hunter.io/yoki.ru</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ecosever.ru</t>
+          <t>https://logos.hunter.io/ecosever.ru</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nationaljournal.ru</t>
+          <t>https://logos.hunter.io/nationaljournal.ru</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/rusday.com</t>
+          <t>https://logos.hunter.io/rusday.com</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/electorat.info</t>
+          <t>https://logos.hunter.io/electorat.info</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mostimes.com</t>
+          <t>https://logos.hunter.io/mostimes.com</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/pora.ru</t>
+          <t>https://logos.hunter.io/pora.ru</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/glavtema.ru</t>
+          <t>https://logos.hunter.io/glavtema.ru</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/prbn.ru</t>
+          <t>https://logos.hunter.io/prbn.ru</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bigness.ru</t>
+          <t>https://logos.hunter.io/bigness.ru</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/militarytimes.ru</t>
+          <t>https://logos.hunter.io/militarytimes.ru</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fizcultprivet.ru</t>
+          <t>https://logos.hunter.io/fizcultprivet.ru</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/poplawok.ru</t>
+          <t>https://logos.hunter.io/poplawok.ru</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/autokolonka.ru</t>
+          <t>https://logos.hunter.io/autokolonka.ru</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/repairshome.ru</t>
+          <t>https://logos.hunter.io/repairshome.ru</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dailyshow.ru</t>
+          <t>https://logos.hunter.io/dailyshow.ru</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/missus.ru</t>
+          <t>https://logos.hunter.io/missus.ru</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bigcaucasus.com</t>
+          <t>https://logos.hunter.io/bigcaucasus.com</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/georgiatimes.info</t>
+          <t>https://logos.hunter.io/georgiatimes.info</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/pravda.ru</t>
+          <t>https://logos.hunter.io/pravda.ru</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aviation21.ru</t>
+          <t>https://logos.hunter.io/aviation21.ru</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/isguru.ru</t>
+          <t>https://logos.hunter.io/isguru.ru</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/asninfo.ru</t>
+          <t>https://logos.hunter.io/asninfo.ru</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/78.ru</t>
+          <t>https://logos.hunter.io/78.ru</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thevoicemag.ru</t>
+          <t>https://logos.hunter.io/thevoicemag.ru</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/moskvichmag.ru</t>
+          <t>https://logos.hunter.io/moskvichmag.ru</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/rbc.ru</t>
+          <t>https://logos.hunter.io/rbc.ru</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/moslenta.ru</t>
+          <t>https://logos.hunter.io/moslenta.ru</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kapital.kz</t>
+          <t>https://logos.hunter.io/kapital.kz</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lsm.kz</t>
+          <t>https://logos.hunter.io/lsm.kz</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/newsmaker.md</t>
+          <t>https://logos.hunter.io/newsmaker.md</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/akipress.org</t>
+          <t>https://logos.hunter.io/akipress.org</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/24.kg</t>
+          <t>https://logos.hunter.io/24.kg</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/noi.md</t>
+          <t>https://logos.hunter.io/noi.md</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/uzdaily.uz</t>
+          <t>https://logos.hunter.io/uzdaily.uz</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/inform.kz</t>
+          <t>https://logos.hunter.io/inform.kz</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/remedium.ru</t>
+          <t>https://logos.hunter.io/remedium.ru</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/medvestnik.ru</t>
+          <t>https://logos.hunter.io/medvestnik.ru</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/incrussia.ru</t>
+          <t>https://logos.hunter.io/incrussia.ru</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/apptractor.ru</t>
+          <t>https://logos.hunter.io/apptractor.ru</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/investfuture.ru</t>
+          <t>https://logos.hunter.io/investfuture.ru</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/onliner.by</t>
+          <t>https://logos.hunter.io/onliner.by</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bits.media</t>
+          <t>https://logos.hunter.io/bits.media</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/telegraf.news</t>
+          <t>https://logos.hunter.io/telegraf.news</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/liter.kz</t>
+          <t>https://logos.hunter.io/liter.kz</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/orda.kz</t>
+          <t>https://logos.hunter.io/orda.kz</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dcjournal.ru</t>
+          <t>https://logos.hunter.io/dcjournal.ru</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/telecombloger.ru</t>
+          <t>https://logos.hunter.io/telecombloger.ru</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/urbc.ru</t>
+          <t>https://logos.hunter.io/urbc.ru</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/haqqin.az</t>
+          <t>https://logos.hunter.io/haqqin.az</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mosregion.info</t>
+          <t>https://logos.hunter.io/mosregion.info</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sila-rf.ru</t>
+          <t>https://logos.hunter.io/sila-rf.ru</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sibmedia.ru</t>
+          <t>https://logos.hunter.io/sibmedia.ru</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ladys.media</t>
+          <t>https://logos.hunter.io/ladys.media</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/socialinform.ru</t>
+          <t>https://logos.hunter.io/socialinform.ru</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/myeconomy.ru</t>
+          <t>https://logos.hunter.io/myeconomy.ru</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ecopravda.ru</t>
+          <t>https://logos.hunter.io/ecopravda.ru</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/medzdrav.info</t>
+          <t>https://logos.hunter.io/medzdrav.info</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/today.ua</t>
+          <t>https://logos.hunter.io/today.ua</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/beautyhunter.ru</t>
+          <t>https://logos.hunter.io/beautyhunter.ru</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/informator.ua</t>
+          <t>https://logos.hunter.io/informator.ua</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/itechua.com</t>
+          <t>https://logos.hunter.io/itechua.com</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mignews.ua</t>
+          <t>https://logos.hunter.io/mignews.ua</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/it-world.ru</t>
+          <t>https://logos.hunter.io/it-world.ru</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gazeta.ua</t>
+          <t>https://logos.hunter.io/gazeta.ua</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/homebusinessmag.com</t>
+          <t>https://logos.hunter.io/homebusinessmag.com</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/miamiherald.com</t>
+          <t>https://logos.hunter.io/miamiherald.com</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kansascity.com</t>
+          <t>https://logos.hunter.io/kansascity.com</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techtimes.com</t>
+          <t>https://logos.hunter.io/techtimes.com</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/brainzmagazine.com</t>
+          <t>https://logos.hunter.io/brainzmagazine.com</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/latinpost.com</t>
+          <t>https://logos.hunter.io/latinpost.com</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/jpost.com</t>
+          <t>https://logos.hunter.io/jpost.com</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thewestnews.com</t>
+          <t>https://logos.hunter.io/thewestnews.com</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vinnews.com</t>
+          <t>https://logos.hunter.io/vinnews.com</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fxstreet.com</t>
+          <t>https://logos.hunter.io/fxstreet.com</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/inc.com</t>
+          <t>https://logos.hunter.io/inc.com</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/computing.co.uk</t>
+          <t>https://logos.hunter.io/computing.co.uk</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/crn.com</t>
+          <t>https://logos.hunter.io/crn.com</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/intlbm.com</t>
+          <t>https://logos.hunter.io/intlbm.com</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/adexchanger.com</t>
+          <t>https://logos.hunter.io/adexchanger.com</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thedrum.com</t>
+          <t>https://logos.hunter.io/thedrum.com</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/globalbankingandfinance.com</t>
+          <t>https://logos.hunter.io/globalbankingandfinance.com</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/financedigest.com</t>
+          <t>https://logos.hunter.io/financedigest.com</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fastcompany.com</t>
+          <t>https://logos.hunter.io/fastcompany.com</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/technologymagazine.com</t>
+          <t>https://logos.hunter.io/technologymagazine.com</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aimagazine.com</t>
+          <t>https://logos.hunter.io/aimagazine.com</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businesschief.eu</t>
+          <t>https://logos.hunter.io/businesschief.eu</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/housingwire.com</t>
+          <t>https://logos.hunter.io/housingwire.com</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/paymentscardsandmobile.com</t>
+          <t>https://logos.hunter.io/paymentscardsandmobile.com</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/digitalconnectmag.com</t>
+          <t>https://logos.hunter.io/digitalconnectmag.com</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/healthcarebusinesstoday.com</t>
+          <t>https://logos.hunter.io/healthcarebusinesstoday.com</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/digiday.com</t>
+          <t>https://logos.hunter.io/digiday.com</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aitimejournal.com</t>
+          <t>https://logos.hunter.io/aitimejournal.com</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/geekextreme.com</t>
+          <t>https://logos.hunter.io/geekextreme.com</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/coingape.com</t>
+          <t>https://logos.hunter.io/coingape.com</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/arabianbusiness.com</t>
+          <t>https://logos.hunter.io/arabianbusiness.com</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businesstechnet.com</t>
+          <t>https://logos.hunter.io/businesstechnet.com</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techstacy.com</t>
+          <t>https://logos.hunter.io/techstacy.com</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/europeanbusinessreview.com</t>
+          <t>https://logos.hunter.io/europeanbusinessreview.com</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/educationtechnologyinsights.com</t>
+          <t>https://logos.hunter.io/educationtechnologyinsights.com</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/digitaljournal.com</t>
+          <t>https://logos.hunter.io/digitaljournal.com</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ealthybyte.com</t>
+          <t>https://logos.hunter.io/ealthybyte.com</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techinasia.com</t>
+          <t>https://logos.hunter.io/techinasia.com</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/siliconcanals.com</t>
+          <t>https://logos.hunter.io/siliconcanals.com</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bizfortune.com</t>
+          <t>https://logos.hunter.io/bizfortune.com</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ciobulletin.com</t>
+          <t>https://logos.hunter.io/ciobulletin.com</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/abcmoney.co.uk</t>
+          <t>https://logos.hunter.io/abcmoney.co.uk</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ceo-review.com</t>
+          <t>https://logos.hunter.io/ceo-review.com</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/corporatevision-news.com</t>
+          <t>https://logos.hunter.io/corporatevision-news.com</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/startupsmagazine.co.uk</t>
+          <t>https://logos.hunter.io/startupsmagazine.co.uk</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lux-life.digital</t>
+          <t>https://logos.hunter.io/lux-life.digital</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/build-review.com</t>
+          <t>https://logos.hunter.io/build-review.com</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/smenews.digital</t>
+          <t>https://logos.hunter.io/smenews.digital</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ghpnews.digital</t>
+          <t>https://logos.hunter.io/ghpnews.digital</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/acquisition-international.com</t>
+          <t>https://logos.hunter.io/acquisition-international.com</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ealthandfinance.digital</t>
+          <t>https://logos.hunter.io/ealthandfinance.digital</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/eubusinessnews.com</t>
+          <t>https://logos.hunter.io/eubusinessnews.com</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/meamarkets.digital</t>
+          <t>https://logos.hunter.io/meamarkets.digital</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/apacinsider.digital</t>
+          <t>https://logos.hunter.io/apacinsider.digital</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/coventryobserver.co.uk</t>
+          <t>https://logos.hunter.io/coventryobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bromsgrovestandard.co.uk</t>
+          <t>https://logos.hunter.io/bromsgrovestandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/droitwichstandard.co.uk</t>
+          <t>https://logos.hunter.io/droitwichstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/eveshamobserver.co.uk</t>
+          <t>https://logos.hunter.io/eveshamobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kidderminsterstandard.co.uk</t>
+          <t>https://logos.hunter.io/kidderminsterstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/leamingtonobserver.co.uk</t>
+          <t>https://logos.hunter.io/leamingtonobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/malvernobserver.co.uk</t>
+          <t>https://logos.hunter.io/malvernobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/redditchstandard.co.uk</t>
+          <t>https://logos.hunter.io/redditchstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/rugbyobserver.co.uk</t>
+          <t>https://logos.hunter.io/rugbyobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/solihullobserver.co.uk</t>
+          <t>https://logos.hunter.io/solihullobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/stratfordobserver.co.uk</t>
+          <t>https://logos.hunter.io/stratfordobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/orcesterobserver.co.uk</t>
+          <t>https://logos.hunter.io/orcesterobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/richmond.com</t>
+          <t>https://logos.hunter.io/richmond.com</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fredericksburg.com</t>
+          <t>https://logos.hunter.io/fredericksburg.com</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/roanoke.com</t>
+          <t>https://logos.hunter.io/roanoke.com</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/newsadvance.com</t>
+          <t>https://logos.hunter.io/newsadvance.com</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dailyprogress.com</t>
+          <t>https://logos.hunter.io/dailyprogress.com</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/heraldcourier.com</t>
+          <t>https://logos.hunter.io/heraldcourier.com</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/martinsvillebulletin.com</t>
+          <t>https://logos.hunter.io/martinsvillebulletin.com</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/newsvirginian.com</t>
+          <t>https://logos.hunter.io/newsvirginian.com</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thefranklinnewspost.com</t>
+          <t>https://logos.hunter.io/thefranklinnewspost.com</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/godanriver.com</t>
+          <t>https://logos.hunter.io/godanriver.com</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/starexponent.com</t>
+          <t>https://logos.hunter.io/starexponent.com</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/smithmountainlake.com</t>
+          <t>https://logos.hunter.io/smithmountainlake.com</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/swvatoday.com</t>
+          <t>https://logos.hunter.io/swvatoday.com</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/naludamagazine.com</t>
+          <t>https://logos.hunter.io/naludamagazine.com</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tech-critter.com</t>
+          <t>https://logos.hunter.io/tech-critter.com</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nasilemaktech.com</t>
+          <t>https://logos.hunter.io/nasilemaktech.com</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/myeverydaytech.com</t>
+          <t>https://logos.hunter.io/myeverydaytech.com</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businessfostermagazine.com</t>
+          <t>https://logos.hunter.io/businessfostermagazine.com</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/business-money.com</t>
+          <t>https://logos.hunter.io/business-money.com</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businesscloud.co.uk</t>
+          <t>https://logos.hunter.io/businesscloud.co.uk</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gritdaily.com</t>
+          <t>https://logos.hunter.io/gritdaily.com</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thesiliconreview.com</t>
+          <t>https://logos.hunter.io/thesiliconreview.com</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thestreet.com</t>
+          <t>https://logos.hunter.io/thestreet.com</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thedefiant.io</t>
+          <t>https://logos.hunter.io/thedefiant.io</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/smartechdaily.com</t>
+          <t>https://logos.hunter.io/smartechdaily.com</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/meditechtoday.com</t>
+          <t>https://logos.hunter.io/meditechtoday.com</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/financialtechtimes.com</t>
+          <t>https://logos.hunter.io/financialtechtimes.com</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/blocktelegraph.io</t>
+          <t>https://logos.hunter.io/blocktelegraph.io</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/transittomorrow.com</t>
+          <t>https://logos.hunter.io/transittomorrow.com</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/highnetworthmag.com</t>
+          <t>https://logos.hunter.io/highnetworthmag.com</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/pharmatechnews.com</t>
+          <t>https://logos.hunter.io/pharmatechnews.com</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxurylamag.com</t>
+          <t>https://logos.hunter.io/luxurylamag.com</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxurymiamimag.com</t>
+          <t>https://logos.hunter.io/luxurymiamimag.com</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lawnewsday.com</t>
+          <t>https://logos.hunter.io/lawnewsday.com</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gametechdaily.com</t>
+          <t>https://logos.hunter.io/gametechdaily.com</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ealthtechdaily.com</t>
+          <t>https://logos.hunter.io/ealthtechdaily.com</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sportstechtoday.com</t>
+          <t>https://logos.hunter.io/sportstechtoday.com</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/meditechwire.com</t>
+          <t>https://logos.hunter.io/meditechwire.com</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/coinreviewnews.com</t>
+          <t>https://logos.hunter.io/coinreviewnews.com</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/innotechtoday.com</t>
+          <t>https://logos.hunter.io/innotechtoday.com</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/csq.com</t>
+          <t>https://logos.hunter.io/csq.com</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techfundingnews.com</t>
+          <t>https://logos.hunter.io/techfundingnews.com</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/millennialmagazine.com</t>
+          <t>https://logos.hunter.io/millennialmagazine.com</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/deccanherald.com</t>
+          <t>https://logos.hunter.io/deccanherald.com</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/amazingarchitecture.com</t>
+          <t>https://logos.hunter.io/amazingarchitecture.com</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/healthworkscollective.com</t>
+          <t>https://logos.hunter.io/healthworkscollective.com</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/goodmenproject.com</t>
+          <t>https://logos.hunter.io/goodmenproject.com</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gilmorehealth.com</t>
+          <t>https://logos.hunter.io/gilmorehealth.com</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/papermag.com</t>
+          <t>https://logos.hunter.io/papermag.com</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bust.com</t>
+          <t>https://logos.hunter.io/bust.com</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/villagevoice.com</t>
+          <t>https://logos.hunter.io/villagevoice.com</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/irvineweekly.com</t>
+          <t>https://logos.hunter.io/irvineweekly.com</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/marinatimes.com</t>
+          <t>https://logos.hunter.io/marinatimes.com</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thecharlotteweekly.com</t>
+          <t>https://logos.hunter.io/thecharlotteweekly.com</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/theleadernews.com</t>
+          <t>https://logos.hunter.io/theleadernews.com</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fortbendstar.com</t>
+          <t>https://logos.hunter.io/fortbendstar.com</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lakerlutznews.com</t>
+          <t>https://logos.hunter.io/lakerlutznews.com</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/laweekly.com</t>
+          <t>https://logos.hunter.io/laweekly.com</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ocweekly.com</t>
+          <t>https://logos.hunter.io/ocweekly.com</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/inbuzzer.com</t>
+          <t>https://logos.hunter.io/inbuzzer.com</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businessmole.com</t>
+          <t>https://logos.hunter.io/businessmole.com</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/instrumentalfx.co</t>
+          <t>https://logos.hunter.io/instrumentalfx.co</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fadmagazine.com</t>
+          <t>https://logos.hunter.io/fadmagazine.com</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/eraveyou.com</t>
+          <t>https://logos.hunter.io/eraveyou.com</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sportsgossip.com</t>
+          <t>https://logos.hunter.io/sportsgossip.com</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sportsmedia101.com</t>
+          <t>https://logos.hunter.io/sportsmedia101.com</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bostonsportsextra.com</t>
+          <t>https://logos.hunter.io/bostonsportsextra.com</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fangsbites.com</t>
+          <t>https://logos.hunter.io/fangsbites.com</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/alltechmagazine.com</t>
+          <t>https://logos.hunter.io/alltechmagazine.com</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/architectureartdesigns.com</t>
+          <t>https://logos.hunter.io/architectureartdesigns.com</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ceotodaymagazine.com</t>
+          <t>https://logos.hunter.io/ceotodaymagazine.com</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/insidermonkey.com</t>
+          <t>https://logos.hunter.io/insidermonkey.com</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/securityonline.info</t>
+          <t>https://logos.hunter.io/securityonline.info</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/securityexpress.info</t>
+          <t>https://logos.hunter.io/securityexpress.info</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/meterpreter.org</t>
+          <t>https://logos.hunter.io/meterpreter.org</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techiexpert.com</t>
+          <t>https://logos.hunter.io/techiexpert.com</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxuryhousingtrends.com</t>
+          <t>https://logos.hunter.io/luxuryhousingtrends.com</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/iplocation.net</t>
+          <t>https://logos.hunter.io/iplocation.net</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/opsmatters.com</t>
+          <t>https://logos.hunter.io/opsmatters.com</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businesshonor.com</t>
+          <t>https://logos.hunter.io/businesshonor.com</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/highways.today</t>
+          <t>https://logos.hunter.io/highways.today</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/hometownstation.com</t>
+          <t>https://logos.hunter.io/hometownstation.com</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/latintimes.com</t>
+          <t>https://logos.hunter.io/latintimes.com</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techloy.com</t>
+          <t>https://logos.hunter.io/techloy.com</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/americancraftbeer.com</t>
+          <t>https://logos.hunter.io/americancraftbeer.com</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/beerconnoisseur.com</t>
+          <t>https://logos.hunter.io/beerconnoisseur.com</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/porchdrinking.com</t>
+          <t>https://logos.hunter.io/porchdrinking.com</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mantelligence.com</t>
+          <t>https://logos.hunter.io/mantelligence.com</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/brulosophy.com</t>
+          <t>https://logos.hunter.io/brulosophy.com</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ashingtonbeerblog.com</t>
+          <t>https://logos.hunter.io/ashingtonbeerblog.com</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/breweriesinpa.com</t>
+          <t>https://logos.hunter.io/breweriesinpa.com</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sandiegobeer.news</t>
+          <t>https://logos.hunter.io/sandiegobeer.news</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/livemusicblog.com</t>
+          <t>https://logos.hunter.io/livemusicblog.com</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/mybeerbuzz.com</t>
+          <t>https://logos.hunter.io/mybeerbuzz.com</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/highways.today</t>
+          <t>https://logos.hunter.io/highways.today</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxuryhousingtrends.com</t>
+          <t>https://logos.hunter.io/luxuryhousingtrends.com</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/timesla.com</t>
+          <t>https://logos.hunter.io/timesla.com</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gearrice.com</t>
+          <t>https://logos.hunter.io/gearrice.com</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/inkl.com</t>
+          <t>https://logos.hunter.io/inkl.com</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nyweekly.com</t>
+          <t>https://logos.hunter.io/nyweekly.com</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/artistweekly.com</t>
+          <t>https://logos.hunter.io/artistweekly.com</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ceoweekly.com</t>
+          <t>https://logos.hunter.io/ceoweekly.com</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/atlwire.com</t>
+          <t>https://logos.hunter.io/atlwire.com</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thechicagojournal.com</t>
+          <t>https://logos.hunter.io/thechicagojournal.com</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/emonthlynews.com</t>
+          <t>https://logos.hunter.io/emonthlynews.com</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lawire.com</t>
+          <t>https://logos.hunter.io/lawire.com</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/beautyscene.net</t>
+          <t>https://logos.hunter.io/beautyscene.net</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/londonlovesproperty.com</t>
+          <t>https://logos.hunter.io/londonlovesproperty.com</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/londonlovestech.com</t>
+          <t>https://logos.hunter.io/londonlovestech.com</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nimvo.com</t>
+          <t>https://logos.hunter.io/nimvo.com</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/chaospin.com</t>
+          <t>https://logos.hunter.io/chaospin.com</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/malemodelscene.net</t>
+          <t>https://logos.hunter.io/malemodelscene.net</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thebusinesswomanmedia.com</t>
+          <t>https://logos.hunter.io/thebusinesswomanmedia.com</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techbullion.com</t>
+          <t>https://logos.hunter.io/techbullion.com</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fashionuer.com</t>
+          <t>https://logos.hunter.io/fashionuer.com</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/moneyinc.com</t>
+          <t>https://logos.hunter.io/moneyinc.com</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/londonlovesbusiness.com</t>
+          <t>https://logos.hunter.io/londonlovesbusiness.com</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bmmagazine.co.uk</t>
+          <t>https://logos.hunter.io/bmmagazine.co.uk</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/designscene.net</t>
+          <t>https://logos.hunter.io/designscene.net</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fashionuer.com</t>
+          <t>https://logos.hunter.io/fashionuer.com</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/entrepreneurhandbook.co.uk</t>
+          <t>https://logos.hunter.io/entrepreneurhandbook.co.uk</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/notorious-mag.com</t>
+          <t>https://logos.hunter.io/notorious-mag.com</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thelondoneconomic.com</t>
+          <t>https://logos.hunter.io/thelondoneconomic.com</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techstartups.com</t>
+          <t>https://logos.hunter.io/techstartups.com</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/swaggermagazine.com</t>
+          <t>https://logos.hunter.io/swaggermagazine.com</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aijourn.com</t>
+          <t>https://logos.hunter.io/aijourn.com</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/financefeeds.com</t>
+          <t>https://logos.hunter.io/financefeeds.com</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sciencetimes.com</t>
+          <t>https://logos.hunter.io/sciencetimes.com</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/itechpost.com</t>
+          <t>https://logos.hunter.io/itechpost.com</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/plainenglish.io</t>
+          <t>https://logos.hunter.io/plainenglish.io</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techround.co.uk</t>
+          <t>https://logos.hunter.io/techround.co.uk</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/eureporter.co</t>
+          <t>https://logos.hunter.io/eureporter.co</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dataconomy.com</t>
+          <t>https://logos.hunter.io/dataconomy.com</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ceoworld.biz</t>
+          <t>https://logos.hunter.io/ceoworld.biz</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/allwomenstalk.com</t>
+          <t>https://logos.hunter.io/allwomenstalk.com</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ceoworld.biz</t>
+          <t>https://logos.hunter.io/ceoworld.biz</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/u.today</t>
+          <t>https://logos.hunter.io/u.today</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/esternjournal.com</t>
+          <t>https://logos.hunter.io/esternjournal.com</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techworm.net</t>
+          <t>https://logos.hunter.io/techworm.net</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ibtimes.com</t>
+          <t>https://logos.hunter.io/ibtimes.com</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/theubj.com</t>
+          <t>https://logos.hunter.io/theubj.com</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/archiscene.net</t>
+          <t>https://logos.hunter.io/archiscene.net</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/largest.org</t>
+          <t>https://logos.hunter.io/largest.org</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dailycivil.com</t>
+          <t>https://logos.hunter.io/dailycivil.com</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tidtiltech.dk</t>
+          <t>https://logos.hunter.io/tidtiltech.dk</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/asianatimes.com</t>
+          <t>https://logos.hunter.io/asianatimes.com</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/musicraiser.net</t>
+          <t>https://logos.hunter.io/musicraiser.net</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/utilizewindows.com</t>
+          <t>https://logos.hunter.io/utilizewindows.com</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thetvjunkies.com</t>
+          <t>https://logos.hunter.io/thetvjunkies.com</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tu.tv</t>
+          <t>https://logos.hunter.io/tu.tv</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/networthrant.com</t>
+          <t>https://logos.hunter.io/networthrant.com</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/jewelbeat.com</t>
+          <t>https://logos.hunter.io/jewelbeat.com</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/desksgram.net</t>
+          <t>https://logos.hunter.io/desksgram.net</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/vxchnge.com</t>
+          <t>https://logos.hunter.io/vxchnge.com</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/liberalco.org</t>
+          <t>https://logos.hunter.io/liberalco.org</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kiwibox.com</t>
+          <t>https://logos.hunter.io/kiwibox.com</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ebsta.me</t>
+          <t>https://logos.hunter.io/ebsta.me</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techktimes.co.uk</t>
+          <t>https://logos.hunter.io/techktimes.co.uk</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/koreaittimes.com</t>
+          <t>https://logos.hunter.io/koreaittimes.com</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/breakingac.com</t>
+          <t>https://logos.hunter.io/breakingac.com</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/maryberryrecipes.co.uk</t>
+          <t>https://logos.hunter.io/maryberryrecipes.co.uk</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/londontime.co</t>
+          <t>https://logos.hunter.io/londontime.co</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/theluxurylifestylemagazine.com</t>
+          <t>https://logos.hunter.io/theluxurylifestylemagazine.com</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxurylifestylemag.co.uk</t>
+          <t>https://logos.hunter.io/luxurylifestylemag.co.uk</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxurialifestyle.com</t>
+          <t>https://logos.hunter.io/luxurialifestyle.com</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/spacedaily.com</t>
+          <t>https://logos.hunter.io/spacedaily.com</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/racinecountyeye.com</t>
+          <t>https://logos.hunter.io/racinecountyeye.com</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/timesofisrael.com</t>
+          <t>https://logos.hunter.io/timesofisrael.com</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/hardreset.info</t>
+          <t>https://logos.hunter.io/hardreset.info</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/imei.info</t>
+          <t>https://logos.hunter.io/imei.info</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/applesn.info</t>
+          <t>https://logos.hunter.io/applesn.info</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dataconomy.com</t>
+          <t>https://logos.hunter.io/dataconomy.com</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/radaronline.com</t>
+          <t>https://logos.hunter.io/radaronline.com</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/okmagazine.com</t>
+          <t>https://logos.hunter.io/okmagazine.com</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/onderwall.com</t>
+          <t>https://logos.hunter.io/onderwall.com</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/knewz.com</t>
+          <t>https://logos.hunter.io/knewz.com</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/frontpagedetectives.com</t>
+          <t>https://logos.hunter.io/frontpagedetectives.com</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/omensgolfjournal.com</t>
+          <t>https://logos.hunter.io/omensgolfjournal.com</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/morninghoney.com</t>
+          <t>https://logos.hunter.io/morninghoney.com</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/dailycoin.com</t>
+          <t>https://logos.hunter.io/dailycoin.com</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bestforandroid.com</t>
+          <t>https://logos.hunter.io/bestforandroid.com</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/esthawaiitoday.com</t>
+          <t>https://logos.hunter.io/esthawaiitoday.com</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/midweek.com</t>
+          <t>https://logos.hunter.io/midweek.com</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/hawaiitribune-herald.com</t>
+          <t>https://logos.hunter.io/hawaiitribune-herald.com</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/thegardenisland.com</t>
+          <t>https://logos.hunter.io/thegardenisland.com</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/staradvertiser.com</t>
+          <t>https://logos.hunter.io/staradvertiser.com</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ustimesnow.com</t>
+          <t>https://logos.hunter.io/ustimesnow.com</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/homecrux.com</t>
+          <t>https://logos.hunter.io/homecrux.com</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/modelifestylemagazine.com</t>
+          <t>https://logos.hunter.io/modelifestylemagazine.com</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aiworldtoday.net</t>
+          <t>https://logos.hunter.io/aiworldtoday.net</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/digitalconvey.com</t>
+          <t>https://logos.hunter.io/digitalconvey.com</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/trillmag.com</t>
+          <t>https://logos.hunter.io/trillmag.com</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businessoutstanders.com</t>
+          <t>https://logos.hunter.io/businessoutstanders.com</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/metapress.com</t>
+          <t>https://logos.hunter.io/metapress.com</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/geeky-gadgets.com</t>
+          <t>https://logos.hunter.io/geeky-gadgets.com</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gizchina.com</t>
+          <t>https://logos.hunter.io/gizchina.com</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/coinprwire.com</t>
+          <t>https://logos.hunter.io/coinprwire.com</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/psbios.me</t>
+          <t>https://logos.hunter.io/psbios.me</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/timebulletin.com</t>
+          <t>https://logos.hunter.io/timebulletin.com</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/cyberpress.org</t>
+          <t>https://logos.hunter.io/cyberpress.org</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gbhackers.com</t>
+          <t>https://logos.hunter.io/gbhackers.com</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/cybersecuritynews.com</t>
+          <t>https://logos.hunter.io/cybersecuritynews.com</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/analyticsinsight.net</t>
+          <t>https://logos.hunter.io/analyticsinsight.net</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/secureblitz.com</t>
+          <t>https://logos.hunter.io/secureblitz.com</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techdee.com</t>
+          <t>https://logos.hunter.io/techdee.com</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/talkandroid.com</t>
+          <t>https://logos.hunter.io/talkandroid.com</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/technology.org</t>
+          <t>https://logos.hunter.io/technology.org</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/kalilinuxtutorials.com</t>
+          <t>https://logos.hunter.io/kalilinuxtutorials.com</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/startup.info</t>
+          <t>https://logos.hunter.io/startup.info</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fontsarena.com</t>
+          <t>https://logos.hunter.io/fontsarena.com</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/applegazette.com</t>
+          <t>https://logos.hunter.io/applegazette.com</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bonjouridee.com</t>
+          <t>https://logos.hunter.io/bonjouridee.com</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/hardwaresecrets.com</t>
+          <t>https://logos.hunter.io/hardwaresecrets.com</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/fontmirror.com</t>
+          <t>https://logos.hunter.io/fontmirror.com</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/technochops.com</t>
+          <t>https://logos.hunter.io/technochops.com</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/socialnewsdaily.com</t>
+          <t>https://logos.hunter.io/socialnewsdaily.com</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/cssbasics.com</t>
+          <t>https://logos.hunter.io/cssbasics.com</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tubetorial.com</t>
+          <t>https://logos.hunter.io/tubetorial.com</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/apps.uk</t>
+          <t>https://logos.hunter.io/apps.uk</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/paktales.com</t>
+          <t>https://logos.hunter.io/paktales.com</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/только</t>
+          <t>https://logos.hunter.io/только</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techdee.com</t>
+          <t>https://logos.hunter.io/techdee.com</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/technoroll.org</t>
+          <t>https://logos.hunter.io/technoroll.org</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techstrange.com</t>
+          <t>https://logos.hunter.io/techstrange.com</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techrado.com</t>
+          <t>https://logos.hunter.io/techrado.com</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35801,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/travellingforbusiness.co.uk</t>
+          <t>https://logos.hunter.io/travellingforbusiness.co.uk</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35873,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/evpowered.co.uk</t>
+          <t>https://logos.hunter.io/evpowered.co.uk</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/electrichome.uk</t>
+          <t>https://logos.hunter.io/electrichome.uk</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/propertyportfolioinvestor.co.uk</t>
+          <t>https://logos.hunter.io/propertyportfolioinvestor.co.uk</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techzeel.net</t>
+          <t>https://logos.hunter.io/techzeel.net</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/learningtoday.net</t>
+          <t>https://logos.hunter.io/learningtoday.net</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/allinsider.net</t>
+          <t>https://logos.hunter.io/allinsider.net</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36305,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sportzbuzz.net</t>
+          <t>https://logos.hunter.io/sportzbuzz.net</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36377,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/nextluxury.com</t>
+          <t>https://logos.hunter.io/nextluxury.com</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/stepbystepbusiness.com</t>
+          <t>https://logos.hunter.io/stepbystepbusiness.com</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36521,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/jt.org</t>
+          <t>https://logos.hunter.io/jt.org</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36593,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/blueandgreentomorrow.com</t>
+          <t>https://logos.hunter.io/blueandgreentomorrow.com</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techspotty.com</t>
+          <t>https://logos.hunter.io/techspotty.com</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/aboutchromebooks.com</t>
+          <t>https://logos.hunter.io/aboutchromebooks.com</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/digitaledge.org</t>
+          <t>https://logos.hunter.io/digitaledge.org</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/connectioncafe.com</t>
+          <t>https://logos.hunter.io/connectioncafe.com</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tabletmonkeys.com</t>
+          <t>https://logos.hunter.io/tabletmonkeys.com</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/quantumrun.com</t>
+          <t>https://logos.hunter.io/quantumrun.com</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/gadgetfreeks.com</t>
+          <t>https://logos.hunter.io/gadgetfreeks.com</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/hatsontech.co.uk</t>
+          <t>https://logos.hunter.io/hatsontech.co.uk</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/voddler.co.uk</t>
+          <t>https://logos.hunter.io/voddler.co.uk</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/citybiz.co</t>
+          <t>https://logos.hunter.io/citybiz.co</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/insiderpaper.com</t>
+          <t>https://logos.hunter.io/insiderpaper.com</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37457,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/onlinebizbooster.net</t>
+          <t>https://logos.hunter.io/onlinebizbooster.net</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businessandpower.com</t>
+          <t>https://logos.hunter.io/businessandpower.com</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37601,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/solidsmack.com</t>
+          <t>https://logos.hunter.io/solidsmack.com</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37673,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/jguru.com</t>
+          <t>https://logos.hunter.io/jguru.com</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/alltechbuzz.net</t>
+          <t>https://logos.hunter.io/alltechbuzz.net</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/baycitizen.org</t>
+          <t>https://logos.hunter.io/baycitizen.org</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/silicon</t>
+          <t>https://logos.hunter.io/silicon</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/triphippies.com</t>
+          <t>https://logos.hunter.io/triphippies.com</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/learningtoday.net</t>
+          <t>https://logos.hunter.io/learningtoday.net</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38105,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ecommercefastlane.com</t>
+          <t>https://logos.hunter.io/ecommercefastlane.com</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/netizensreport.com</t>
+          <t>https://logos.hunter.io/netizensreport.com</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/startup</t>
+          <t>https://logos.hunter.io/startup</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/guruhitech.com</t>
+          <t>https://logos.hunter.io/guruhitech.com</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/britishwire.com</t>
+          <t>https://logos.hunter.io/britishwire.com</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/investing.com</t>
+          <t>https://logos.hunter.io/investing.com</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/the-tech-trend.com</t>
+          <t>https://logos.hunter.io/the-tech-trend.com</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38609,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/arrington-worldwide.co.uk</t>
+          <t>https://logos.hunter.io/arrington-worldwide.co.uk</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/archeyes.com</t>
+          <t>https://logos.hunter.io/archeyes.com</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38753,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/sportswane.com</t>
+          <t>https://logos.hunter.io/sportswane.com</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/techwalls.com</t>
+          <t>https://logos.hunter.io/techwalls.com</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38897,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/lawbhoomi.com</t>
+          <t>https://logos.hunter.io/lawbhoomi.com</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38969,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/businessnewsthisweek.com</t>
+          <t>https://logos.hunter.io/businessnewsthisweek.com</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/guardian.ng</t>
+          <t>https://logos.hunter.io/guardian.ng</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/londondaily.news</t>
+          <t>https://logos.hunter.io/londondaily.news</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/london-post.co.uk</t>
+          <t>https://logos.hunter.io/london-post.co.uk</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/omenontopp.com</t>
+          <t>https://logos.hunter.io/omenontopp.com</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/impactwealth.org</t>
+          <t>https://logos.hunter.io/impactwealth.org</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/africa.businessinsider.com</t>
+          <t>https://logos.hunter.io/africa.businessinsider.com</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39473,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/measurescopez.com</t>
+          <t>https://logos.hunter.io/measurescopez.com</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ukbusinesstimes.co.uk</t>
+          <t>https://logos.hunter.io/ukbusinesstimes.co.uk</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/londoninsider.co.uk</t>
+          <t>https://logos.hunter.io/londoninsider.co.uk</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/ibusiness.news</t>
+          <t>https://logos.hunter.io/ibusiness.news</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/theluxauthority.com</t>
+          <t>https://logos.hunter.io/theluxauthority.com</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/congress.net</t>
+          <t>https://logos.hunter.io/congress.net</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/bitzuma.com</t>
+          <t>https://logos.hunter.io/bitzuma.com</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39977,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/asiapresswire.com</t>
+          <t>https://logos.hunter.io/asiapresswire.com</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/grazia.si</t>
+          <t>https://logos.hunter.io/grazia.si</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/luxuo.com</t>
+          <t>https://logos.hunter.io/luxuo.com</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40193,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/glamour.bg</t>
+          <t>https://logos.hunter.io/glamour.bg</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/digitalbusiness.kz</t>
+          <t>https://logos.hunter.io/digitalbusiness.kz</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/zakon.kz</t>
+          <t>https://logos.hunter.io/zakon.kz</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40490,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/informburo.kz</t>
+          <t>https://logos.hunter.io/informburo.kz</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/rasdaily.kz</t>
+          <t>https://logos.hunter.io/rasdaily.kz</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/caravan.kz</t>
+          <t>https://logos.hunter.io/caravan.kz</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/tengrinews.kz</t>
+          <t>https://logos.hunter.io/tengrinews.kz</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/centralmedia24.kz</t>
+          <t>https://logos.hunter.io/centralmedia24.kz</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logo.clearbit.com/orda.kz</t>
+          <t>https://logos.hunter.io/orda.kz</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/srrb.ru</t>
+          <t>https://srrb.ru/apple-touch-icon.png</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/apni.ru</t>
+          <t>https://apni.ru/uploads/Logo.svg</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tvkinoradio.ru</t>
+          <t>https://tvkinoradio.ru/img/logo/tvkinoradio.png</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/politnavigator.net</t>
+          <t>https://www.politnavigator.net/wp-content/themes/politnav-puzzle/images/pnlogo.png</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bloknot.ru</t>
+          <t>https://bloknot.ru/static/images/logo_color3.png</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/delovoymir.biz</t>
+          <t>https://region.center/data/moduleslogos/ac5557cf56c5ab10d8b525864891e909.png</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business-magazine.online</t>
+          <t>https://region.center/data/moduleslogos/f339af0da3f8d6b5a8da975d0ace7c62.svg</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/garant.ru</t>
+          <t>https://www.garant.ru/static/www/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/prophotos.ru</t>
+          <t>https://my.prophotos.ru/assets/logo_prophotos_big-e2a018230a87b9724c0abdf904d49c3eec5d3dcd4d221a7af7207022b2b98c81.png</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/peopletalk.ru</t>
+          <t>https://peopletalk.ru/wp-content/themes/peopletalk2019/dist/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/versia.ru</t>
+          <t>https://versia.ru/images/newspaper.png</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/infox.ru</t>
+          <t>https://www.infox.ru/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/samag.ru</t>
+          <t>https://www.samag.ru/img/logo.jpg</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/itweek.ru</t>
+          <t>https://www.itweek.ru/images/itweek/logo.png</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/1sept.ru</t>
+          <t>https://1sept.ru/theme/logo.svg</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/finversia.ru</t>
+          <t>https://finversia.ru/site/themes/lapuzzle/images/header/Header_Logo.svg</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mir24.tv</t>
+          <t>https://images.mir24.tv/jzZtwM40HO2JiUckYTI5gRZ-PCCVCb3RBK_sOV818Dc/czM6Ly9taXIyNC10di9tZWRpYS9TZXR0aW5nc0xvZ28vaW1hZ2UvYWQ1ZTVmODItNWEyNS00MDVlLWIxYmItOTVmODlmMTZiMzY5L2xvZ29GLnN2Zw.svg</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lenta.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/01/Lenta.svg</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/7days.ru</t>
+          <t>https://cdn.7days.ru/bitrix/templates/7days-redesign-2021/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vokrug.tv</t>
+          <t>https://www.vokrug.tv/images/logo-new.svg</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fedpress.ru</t>
+          <t>https://fedpress.ru/themes/fp/images/main/logo-text.png</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/securitylab.ru</t>
+          <t>https://www.securitylab.ru/img/logo/logo-header.svg</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/osnmedia.ru</t>
+          <t>https://www.osnmedia.ru/wp-content/uploads/2025/05/logo-new-light.png</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/snob.ru</t>
+          <t>https://snob.ru/apple-touch-icon.png</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/comnews.ru</t>
+          <t>https://www.comnews.ru/themes/site/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tproger.ru</t>
+          <t>https://tproger.ru/images/favicons/favicon.svg</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/cnews.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/07/CNews_logo.svg</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/iz.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Izvestia.svg</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sport-express.ru</t>
+          <t>https://ss.sport-express.net/fb/img/icons/logos/se-logo.svg</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newdaynews.ru</t>
+          <t>https://newdaynews.ru/global/flb/newdaynews.logo.svg</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gazetametro.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/5f/Metro_International_Logo.svg</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/5-tv.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c0/5-tv_logo_%282023%29.svg</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dk.ru</t>
+          <t>https://www.dk.ru/assets/logo_dk-756cff44c32801053911cb9f9243f9c8.svg</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/strategyjournal.ru</t>
+          <t>https://strategyjournal.ru/wp-content/themes/strategyjournal/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/retailer.ru</t>
+          <t>https://retailer.ru/wp-content/themes/monstroid2/assets/images/retailer-logo.svg</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mk.ru</t>
+          <t>https://www.mk.ru/media/mkru2020/img/mk-logo.svg</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aif.ru</t>
+          <t>https://aif.ru/redesign2018/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vedomosti.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Vedomosti_logo.svg</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ng.ru</t>
+          <t>https://www.ng.ru/bitrix/templates/ng/i/logo.png</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business.ru</t>
+          <t>https://www.business.ru/themes/business_ru/assets/frontend/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kom-dir.ru</t>
+          <t>https://www.kom-dir.ru/themes/kom-dir_ru/assets/frontend/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/glavbukh.ru</t>
+          <t>https://www.glavbukh.ru/themes/glavbukh_ru/assets/frontend/images/logo_red.svg</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/26-2.ru</t>
+          <t>https://www.26-2.ru/themes/26-2_ru/assets/frontend/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/buhsoft.ru</t>
+          <t>https://www.buhsoft.ru/themes/buhsoft_ru/assets/frontend/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pro-personal.ru</t>
+          <t>https://www.pro-personal.ru/themes/pro-personal_ru/assets/frontend/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kdelo.ru</t>
+          <t>https://www.kdelo.ru/themes/kdelo_ru/assets/frontend/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tass.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/95/TASS_Logo_%28Latin%29_2022.svg</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gazeta.ru</t>
+          <t>https://static.gazeta.ru/nm2015/i/logo_gazeta.svg</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vm.ru</t>
+          <t>https://vm.ru/img/main_logo.svg</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/news.ru</t>
+          <t>https://news.ru/assets/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/profile.ru</t>
+          <t>https://cdn.profile.ru/wp-content/themes/profile/assets/img/profile-logo-delovoy.svg</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/oilcapital.ru</t>
+          <t>https://oilcapital.ru/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business-gazeta.ru</t>
+          <t>https://business-gazeta.ru/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ko.ru</t>
+          <t>https://ko.ru/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dp.ru</t>
+          <t>https://www.dp.ru/assets/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/popmech.ru</t>
+          <t>https://popmech.ru/_nuxt/img/logo-techinsider-full_2203343.svg</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/svpressa.ru</t>
+          <t>https://svpressa.ru/i/logo-svpressa.svg</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ridus.ru</t>
+          <t>https://www.ridus.ru/_images/logo.png</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dni.ru</t>
+          <t>https://dni.ru/static/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/utro.ru</t>
+          <t>https://utro.ru/static/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kleo.ru</t>
+          <t>https://www.kleo.ru/wp-content/uploads/2026/01/kleo-logo.svg</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newizv.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/15/%D0%9D%D0%98_%D0%BB%D0%BE%D0%B3%D0%BE.png</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rosbalt.ru</t>
+          <t>https://www.rosbalt.ru/img/icons/icon-512x512.png</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/monocle.ru</t>
+          <t>https://monocle.ru/static/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rg.ru</t>
+          <t>https://cdnstatic.rg.ru/svg/touch-icon.svg</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/runews24.ru</t>
+          <t>https://runews24.ru/assets/images/logo2.png</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/angi.ru</t>
+          <t>https://www.angi.ru/images/homepage.png</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/naked-science.ru</t>
+          <t>https://naked-science.ru/assets/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/globalcio.ru</t>
+          <t>https://globalcio.ru/local/static/html/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businesstory.ru</t>
+          <t>https://businesstory.ru/wp-content/uploads/2026/05/bs-logo.png</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ict-online.ru</t>
+          <t>https://www.ict-online.ru/old/gif/max_mess_logo.svg</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/logirus.ru</t>
+          <t>https://logirus.ru/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/24gadget.ru</t>
+          <t>https://24gadget.ru/templates/Default/images/new/logo_s.gif</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/marieclaire.com</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Marie_Claire_Magazine_logo.svg</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/3dnews.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/4b/3DNews_logo.svg</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/servernews.ru</t>
+          <t>https://servernews.ru/assets/external/servernews.ru/images/logo.jpg</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/new-retail.ru</t>
+          <t>https://new-retail.ru/img/logo/logo.png</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nakanune.ru</t>
+          <t>https://media.nakanune.ru/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/telecomdaily.ru</t>
+          <t>https://telecomdaily.ru/faaf6981f14537b11b8277d64fabc69f.png</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bigpicture.ru</t>
+          <t>https://bigpicture.ru/wp-content/themes/bigpicture-new/assets/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kommersant.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Logo_Kommersant.svg</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/eadaily.com</t>
+          <t>https://static1.eadaily.com/i/logos/logo-squared-400.png</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sostav.ru</t>
+          <t>https://www.sostav.ru/app/public/design/logo2918-05v3.svg</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ura.news</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/69/URA.RU_logo.svg</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/seonews.ru</t>
+          <t>https://www.seonews.ru/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/likeni.ru</t>
+          <t>https://www.likeni.ru/assets/img/logo-mini.png</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/life.ru</t>
+          <t>https://life.ru/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/omanhit.ru</t>
+          <t>https://www.womanhit.ru/static/images/og/womanhit_ru_og_logo_1200_720.png</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/avtovzglyad.ru</t>
+          <t>https://www.avtovzglyad.ru/static/images/avtovzglyad-logo.svg</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ohotniki.ru</t>
+          <t>https://www.ohotniki.ru/static/images/ohotniki-logo.svg</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mperspektiva.ru</t>
+          <t>https://mperspektiva.ru/local/templates/mp/s/images/tmp_file/header/dec-logo.webp</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautyhack.ru</t>
+          <t>https://beautyhack.ru/assets/images/logo2.png</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sobaka.ru</t>
+          <t>https://www.sobaka.ru/img/sobaka.svg</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sobaka.ru</t>
+          <t>https://www.sobaka.ru/img/sobaka.svg</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sobaka.ru</t>
+          <t>https://www.sobaka.ru/img/sobaka.svg</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/forbes.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/db/Forbes_logo.svg</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/stroygaz.ru</t>
+          <t>https://stroygaz.ru/upload/uf/e61/oekrgwiovsiba5ajvv6147lsauedss2g.webp</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/regnum.ru</t>
+          <t>https://regnum.ru/main_logo.svg</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/topcor.ru</t>
+          <t>https://topcor.ru/templates/topcor/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sfera.fm</t>
+          <t>https://sfera.fm/assets/media/logo/logo_sfera_header.png</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/brl.mk.ru</t>
+          <t>https://brl.mk.ru/media/mkru2020/img/mk-logo.svg</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/novate.ru</t>
+          <t>https://novate.ru/img/logo.svg</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautycarteblanche.ru</t>
+          <t>https://static.tildacdn.com/tild3930-3036-4536-a464-363733353938/BCB_logo_1.svg</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vokrug.tv</t>
+          <t>https://www.vokrug.tv/images/logo-new.svg</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vokrugsveta.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/vokrugsveta/8b7f3beb.svg</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/oman.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/woman/2cb6624f.svg</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/day.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/wday/2cb6624f.svg</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thegirl.ru</t>
+          <t>https://thegirl.ru/public/sprites/thegirl/e5cb1e72ce8b.svg</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/starhit.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/starhit/500f077c.svg</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/parents.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/parents/b1a1d258.svg</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mydecor.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/mcmaison/2cb6624f.svg</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/doctorpiter.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/doctorpiter/e4197781.svg</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/the-day.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/wday/2cb6624f.svg</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/maximonline.ru</t>
+          <t>https://cdn.hsmedia.ru/dist/maxim/f8d1d209.svg</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/psychologies.ru</t>
+          <t>https://cdn.hsmedia.ru/ump-webapp-public/dist/client/assets/psychologies_lg_bg-light-DG40Nryg.svg</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fashiontime.ru</t>
+          <t>https://www.fashiontime.ru/bitrix/templates/ft.v3/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/oane.ws</t>
+          <t>https://oane.ws/templates/oane_new/logo-old.png</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/terrnews.com</t>
+          <t>https://terrnews.com/templates/Hint-utf8/images/logo66.png</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kadara.ru</t>
+          <t>https://kadara.ru/wp-content/uploads/2019/12/kadara-logo.png</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/monavista.ru</t>
+          <t>https://monavista.ru/templates/newshub/images/logo-old.png</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vestnik.net</t>
+          <t>https://vestnik.net/images/logo_in_html.png</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nvspost.ru</t>
+          <t>https://nvspost.ru/templates/lifewatcher/images/logo3.png</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/spb.kp.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/K_Pravda_Logo_Modern.svg</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/belarus.kp.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/K_Pravda_Logo_Modern.svg</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/news-24.ru</t>
+          <t>https://news-24.ru/wp-content/uploads/2025/01/logon24.png</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/smi24.news</t>
+          <t>https://smi24.news/wp-content/uploads/2024/12/group-158-1.svg</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/frequentflyers.ru</t>
+          <t>https://www.frequentflyers.ru/wp-content/uploads/2015/10/fflogo6.png</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/adindex.ru</t>
+          <t>https://adindex.ru/assets/img/logo-adindex.svg</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/artagmag.ru</t>
+          <t>https://static.tildacdn.com/tild3938-6436-4639-b565-343838653436/Logo.svg</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sport24.ru</t>
+          <t>https://img.artlebedev.ru/everything/sport24/identity/media/icons/s24_port.svg</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/prufy.ru</t>
+          <t>https://prufy.ru/images/reg/prufy.ru.svg</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moneytimes.ru</t>
+          <t>https://www.moneytimes.ru/images/moneytimes-logo.png</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/english.pravda.ru</t>
+          <t>https://english.pravda.ru/pix/logo_white.png</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/medpulse.ru</t>
+          <t>https://www.medpulse.ru/image/upload/logo512.jpg</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newsinfo.ru</t>
+          <t>https://www.newsinfo.ru/images/newsinfo-logo.png</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/politonline.ru</t>
+          <t>https://www.politonline.ru/assets/logo-5-4679515ece2fdfeb4567553a15565643.png</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/yoki.ru</t>
+          <t>https://www.yoki.ru/images/yoki-logo.png</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ecosever.ru</t>
+          <t>https://www.ecosever.ru/images/ecosever-logo.png</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nationaljournal.ru</t>
+          <t>https://www.nationaljournal.ru/pix/nationaljournal-logo.png</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rusday.com</t>
+          <t>https://www.rusday.com/pix/rusday-logo.png</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/electorat.info</t>
+          <t>https://www.electorat.info/pix/electorat-logo.png</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mostimes.com</t>
+          <t>https://www.mostimes.com/images/mostimes-logo.png</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pora.ru</t>
+          <t>https://www.pora.ru/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/glavtema.ru</t>
+          <t>https://www.glavtema.ru/pix/glavtema-logo.png</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/prbn.ru</t>
+          <t>https://www.prbn.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bigness.ru</t>
+          <t>https://www.bigness.ru/pix/logo.gif</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/militarytimes.ru</t>
+          <t>https://www.militarytimes.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fizcultprivet.ru</t>
+          <t>https://www.fizcultprivet.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/poplawok.ru</t>
+          <t>https://www.poplawok.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/autokolonka.ru</t>
+          <t>https://www.autokolonka.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/repairshome.ru</t>
+          <t>https://www.repairshome.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dailyshow.ru</t>
+          <t>https://www.dailyshow.ru/images/dailyshow-logo.gif</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/missus.ru</t>
+          <t>https://www.missus.ru/pix/logo.gif</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bigcaucasus.com</t>
+          <t>https://www.bigcaucasus.com/pix/smalllogo.jpg</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/georgiatimes.info</t>
+          <t>https://www.georgiatimes.info/images/georgiatimes-logo.jpg</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pravda.ru</t>
+          <t>https://www.pravda.ru/pix/logo600_60.png</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aviation21.ru</t>
+          <t>https://aviation21.ru/wp-content/uploads/2017/03/logo-1.png</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/asninfo.ru</t>
+          <t>https://asninfo.ru/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/78.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/24/TV78logo.svg</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thevoicemag.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/67/Logo_of_Russian_magazine_The_Voice.svg</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moskvichmag.ru</t>
+          <t>https://moskvichmag.ru/wp-content/themes/moskmag-new/assets/img/svg/mm-xl-logo.svg</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rbc.ru</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f1/RBK_logo.svg</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moslenta.ru</t>
+          <t>https://moslenta.ru/favicon.svg</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kapital.kz</t>
+          <t>https://kapital.kz/logo.png</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lsm.kz</t>
+          <t>https://lsm.kz/static/img/logo.png</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newsmaker.md</t>
+          <t>https://newsmaker.md/wp-content/uploads/2019/01/logo_square.jpg</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/akipress.org</t>
+          <t>https://cdn-1.aki.kg/st_akipress/logo_wide_300x48.png</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/24.kg</t>
+          <t>https://24.kg/assets/39aedacb/images/logo.png</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/noi.md</t>
+          <t>https://noi.md/images/logo_noi_blue.jpg</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/uzdaily.uz</t>
+          <t>https://www.uzdaily.uz/static/web/files/logo.258d31191858.svg</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/inform.kz</t>
+          <t>https://www.inform.kz/static/img/favicon.svg</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/remedium.ru</t>
+          <t>https://remedium.ru/upload/medialibrary/43b/Remedium-logo-2019-MAIN.png</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/medvestnik.ru</t>
+          <t>https://medvestnik.ru/apps/mv/assets/cache/images/c7aa52eecd.svg</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/incrussia.ru</t>
+          <t>https://incrussia.ru/wp-content/themes/inc/img/ink_logo_space.svg</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/apptractor.ru</t>
+          <t>https://apptractor.ru/wp-content/uploads/2025/10/logowebp-1.webp</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/investfuture.ru</t>
+          <t>https://investfuture.ru/static/logo.png</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/onliner.by</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Logo-onliner-by.png</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bits.media</t>
+          <t>https://bits.media/local/templates/bits.media/images/bits4.png</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/telegraf.news</t>
+          <t>https://telegraf.news/_astro/logo_black.hKlVZoUa.svg</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/liter.kz</t>
+          <t>https://liter.kz/build/images/liter-logo-news.png</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/orda.kz</t>
+          <t>https://orda.kz/img/logo_d.svg</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dcjournal.ru</t>
+          <t>https://dcjournal.ru/theme/codirf/images/h-logo6.png</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/telecombloger.ru</t>
+          <t>https://telecombloger.ru/wp-content/uploads/2024/12/Logo.png</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/urbc.ru</t>
+          <t>https://urbc.ru/templates/Default/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/haqqin.az</t>
+          <t>https://upload.wikimedia.org/wikipedia/ru/9/9d/%D0%9B%D0%BE%D0%B3%D0%BE%D1%82%D0%B8%D0%BF_Haqqin.az.svg</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mosregion.info</t>
+          <t>https://www.mosregion.info/wp-content/uploads/2024/09/mosregion_logo.png</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sila-rf.ru</t>
+          <t>https://www.sila-rf.ru/wp-content/uploads/2022/02/sila-rf.png</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sibmedia.ru</t>
+          <t>https://www.sibmedia.ru/wp-content/uploads/2024/07/sibmedia_logo.png</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ladys.media</t>
+          <t>https://www.ladys.media/wp-content/themes/ladys/images/logos/logo_desktop.svg</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/socialinform.ru</t>
+          <t>https://www.socialinform.ru/wp-content/uploads/2024/02/socnews_logo-1.png</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/myeconomy.ru</t>
+          <t>https://www.myeconomy.ru/wp-content/uploads/2024/11/economy-logo.png</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ecopravda.ru</t>
+          <t>https://www.ecopravda.ru/wp-content/uploads/2022/07/Group-210.jpg</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/medzdrav.info</t>
+          <t>https://medzdrav.info/wp-content/uploads/2024/01/logo_header.svg</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/today.ua</t>
+          <t>https://today.ua/svg/logo.svg</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautyhunter.ru</t>
+          <t>https://beautyhunter.ru/attachments/Image/bhlogo36.png</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/informator.ua</t>
+          <t>https://informator.ua/images/logo.svg</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/itechua.com</t>
+          <t>https://itechua.com/wp-content/uploads/2024/08/itechua-logo.png</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mignews.ua</t>
+          <t>https://mignews.ua/static/img/logo_ua.png</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/it-world.ru</t>
+          <t>https://www.it-world.ru/local/templates/.default/img/logo/logo_s1.svg</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gazeta.ua</t>
+          <t>https://gazeta.ua/images/svg/gazeta.svg</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://srrb.ru/apple-touch-icon.png</t>
+          <t>https://logos.hunter.io/srrb.ru</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://apni.ru/uploads/Logo.svg</t>
+          <t>https://logos.hunter.io/apni.ru</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://tvkinoradio.ru/img/logo/tvkinoradio.png</t>
+          <t>https://logos.hunter.io/tvkinoradio.ru</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.politnavigator.net/wp-content/themes/politnav-puzzle/images/pnlogo.png</t>
+          <t>https://logos.hunter.io/politnavigator.net</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://bloknot.ru/static/images/logo_color3.png</t>
+          <t>https://logos.hunter.io/bloknot.ru</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://region.center/data/moduleslogos/ac5557cf56c5ab10d8b525864891e909.png</t>
+          <t>https://logos.hunter.io/delovoymir.biz</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://region.center/data/moduleslogos/f339af0da3f8d6b5a8da975d0ace7c62.svg</t>
+          <t>https://logos.hunter.io/business-magazine.online</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.garant.ru/static/www/img/logo.svg</t>
+          <t>https://logos.hunter.io/garant.ru</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://my.prophotos.ru/assets/logo_prophotos_big-e2a018230a87b9724c0abdf904d49c3eec5d3dcd4d221a7af7207022b2b98c81.png</t>
+          <t>https://logos.hunter.io/prophotos.ru</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://peopletalk.ru/wp-content/themes/peopletalk2019/dist/img/logo.svg</t>
+          <t>https://logos.hunter.io/peopletalk.ru</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://versia.ru/images/newspaper.png</t>
+          <t>https://logos.hunter.io/versia.ru</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.infox.ru/img/logo.png</t>
+          <t>https://logos.hunter.io/infox.ru</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.samag.ru/img/logo.jpg</t>
+          <t>https://logos.hunter.io/samag.ru</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.itweek.ru/images/itweek/logo.png</t>
+          <t>https://logos.hunter.io/itweek.ru</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://1sept.ru/theme/logo.svg</t>
+          <t>https://logos.hunter.io/1sept.ru</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://finversia.ru/site/themes/lapuzzle/images/header/Header_Logo.svg</t>
+          <t>https://logos.hunter.io/finversia.ru</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://images.mir24.tv/jzZtwM40HO2JiUckYTI5gRZ-PCCVCb3RBK_sOV818Dc/czM6Ly9taXIyNC10di9tZWRpYS9TZXR0aW5nc0xvZ28vaW1hZ2UvYWQ1ZTVmODItNWEyNS00MDVlLWIxYmItOTVmODlmMTZiMzY5L2xvZ29GLnN2Zw.svg</t>
+          <t>https://logos.hunter.io/mir24.tv</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/01/Lenta.svg</t>
+          <t>https://logos.hunter.io/lenta.ru</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://cdn.7days.ru/bitrix/templates/7days-redesign-2021/images/logo.svg</t>
+          <t>https://logos.hunter.io/7days.ru</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.vokrug.tv/images/logo-new.svg</t>
+          <t>https://logos.hunter.io/vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://fedpress.ru/themes/fp/images/main/logo-text.png</t>
+          <t>https://logos.hunter.io/fedpress.ru</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.securitylab.ru/img/logo/logo-header.svg</t>
+          <t>https://logos.hunter.io/securitylab.ru</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.osnmedia.ru/wp-content/uploads/2025/05/logo-new-light.png</t>
+          <t>https://logos.hunter.io/osnmedia.ru</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://snob.ru/apple-touch-icon.png</t>
+          <t>https://logos.hunter.io/snob.ru</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.comnews.ru/themes/site/images/logo.png</t>
+          <t>https://logos.hunter.io/comnews.ru</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://tproger.ru/images/favicons/favicon.svg</t>
+          <t>https://logos.hunter.io/tproger.ru</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/07/CNews_logo.svg</t>
+          <t>https://logos.hunter.io/cnews.ru</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Izvestia.svg</t>
+          <t>https://logos.hunter.io/iz.ru</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://ss.sport-express.net/fb/img/icons/logos/se-logo.svg</t>
+          <t>https://logos.hunter.io/sport-express.ru</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://newdaynews.ru/global/flb/newdaynews.logo.svg</t>
+          <t>https://logos.hunter.io/newdaynews.ru</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/5f/Metro_International_Logo.svg</t>
+          <t>https://logos.hunter.io/gazetametro.ru</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c0/5-tv_logo_%282023%29.svg</t>
+          <t>https://logos.hunter.io/5-tv.ru</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.dk.ru/assets/logo_dk-756cff44c32801053911cb9f9243f9c8.svg</t>
+          <t>https://logos.hunter.io/dk.ru</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://strategyjournal.ru/wp-content/themes/strategyjournal/img/logo.svg</t>
+          <t>https://logos.hunter.io/strategyjournal.ru</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://retailer.ru/wp-content/themes/monstroid2/assets/images/retailer-logo.svg</t>
+          <t>https://logos.hunter.io/retailer.ru</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.mk.ru/media/mkru2020/img/mk-logo.svg</t>
+          <t>https://logos.hunter.io/mk.ru</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://aif.ru/redesign2018/img/logo.svg</t>
+          <t>https://logos.hunter.io/aif.ru</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Vedomosti_logo.svg</t>
+          <t>https://logos.hunter.io/vedomosti.ru</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.ng.ru/bitrix/templates/ng/i/logo.png</t>
+          <t>https://logos.hunter.io/ng.ru</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.business.ru/themes/business_ru/assets/frontend/images/logo.png</t>
+          <t>https://logos.hunter.io/business.ru</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.kom-dir.ru/themes/kom-dir_ru/assets/frontend/images/logo.png</t>
+          <t>https://logos.hunter.io/kom-dir.ru</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.glavbukh.ru/themes/glavbukh_ru/assets/frontend/images/logo_red.svg</t>
+          <t>https://logos.hunter.io/glavbukh.ru</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.26-2.ru/themes/26-2_ru/assets/frontend/images/logo.png</t>
+          <t>https://logos.hunter.io/26-2.ru</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.buhsoft.ru/themes/buhsoft_ru/assets/frontend/images/logo.png</t>
+          <t>https://logos.hunter.io/buhsoft.ru</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.pro-personal.ru/themes/pro-personal_ru/assets/frontend/images/logo.png</t>
+          <t>https://logos.hunter.io/pro-personal.ru</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.kdelo.ru/themes/kdelo_ru/assets/frontend/images/logo.png</t>
+          <t>https://logos.hunter.io/kdelo.ru</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/95/TASS_Logo_%28Latin%29_2022.svg</t>
+          <t>https://logos.hunter.io/tass.ru</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://static.gazeta.ru/nm2015/i/logo_gazeta.svg</t>
+          <t>https://logos.hunter.io/gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://vm.ru/img/main_logo.svg</t>
+          <t>https://logos.hunter.io/vm.ru</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://news.ru/assets/images/logo.svg</t>
+          <t>https://logos.hunter.io/news.ru</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://cdn.profile.ru/wp-content/themes/profile/assets/img/profile-logo-delovoy.svg</t>
+          <t>https://logos.hunter.io/profile.ru</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://oilcapital.ru/img/logo.svg</t>
+          <t>https://logos.hunter.io/oilcapital.ru</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://business-gazeta.ru/img/logo.svg</t>
+          <t>https://logos.hunter.io/business-gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://ko.ru/img/logo.png</t>
+          <t>https://logos.hunter.io/ko.ru</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.dp.ru/assets/images/logo.png</t>
+          <t>https://logos.hunter.io/dp.ru</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://popmech.ru/_nuxt/img/logo-techinsider-full_2203343.svg</t>
+          <t>https://logos.hunter.io/popmech.ru</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://svpressa.ru/i/logo-svpressa.svg</t>
+          <t>https://logos.hunter.io/svpressa.ru</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.ridus.ru/_images/logo.png</t>
+          <t>https://logos.hunter.io/ridus.ru</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://dni.ru/static/img/logo.png</t>
+          <t>https://logos.hunter.io/dni.ru</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://utro.ru/static/img/logo.png</t>
+          <t>https://logos.hunter.io/utro.ru</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.kleo.ru/wp-content/uploads/2026/01/kleo-logo.svg</t>
+          <t>https://logos.hunter.io/kleo.ru</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/15/%D0%9D%D0%98_%D0%BB%D0%BE%D0%B3%D0%BE.png</t>
+          <t>https://logos.hunter.io/newizv.ru</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.rosbalt.ru/img/icons/icon-512x512.png</t>
+          <t>https://logos.hunter.io/rosbalt.ru</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://monocle.ru/static/img/logo.svg</t>
+          <t>https://logos.hunter.io/monocle.ru</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://cdnstatic.rg.ru/svg/touch-icon.svg</t>
+          <t>https://logos.hunter.io/rg.ru</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://runews24.ru/assets/images/logo2.png</t>
+          <t>https://logos.hunter.io/runews24.ru</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.angi.ru/images/homepage.png</t>
+          <t>https://logos.hunter.io/angi.ru</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://naked-science.ru/assets/images/logo.svg</t>
+          <t>https://logos.hunter.io/naked-science.ru</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://globalcio.ru/local/static/html/images/logo.svg</t>
+          <t>https://logos.hunter.io/globalcio.ru</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://businesstory.ru/wp-content/uploads/2026/05/bs-logo.png</t>
+          <t>https://logos.hunter.io/businesstory.ru</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.ict-online.ru/old/gif/max_mess_logo.svg</t>
+          <t>https://logos.hunter.io/ict-online.ru</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://logirus.ru/img/logo.png</t>
+          <t>https://logos.hunter.io/logirus.ru</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://24gadget.ru/templates/Default/images/new/logo_s.gif</t>
+          <t>https://logos.hunter.io/24gadget.ru</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Marie_Claire_Magazine_logo.svg</t>
+          <t>https://logos.hunter.io/marieclaire.com</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/4b/3DNews_logo.svg</t>
+          <t>https://logos.hunter.io/3dnews.ru</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://servernews.ru/assets/external/servernews.ru/images/logo.jpg</t>
+          <t>https://logos.hunter.io/servernews.ru</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://new-retail.ru/img/logo/logo.png</t>
+          <t>https://logos.hunter.io/new-retail.ru</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://media.nakanune.ru/images/logo.png</t>
+          <t>https://logos.hunter.io/nakanune.ru</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://telecomdaily.ru/faaf6981f14537b11b8277d64fabc69f.png</t>
+          <t>https://logos.hunter.io/telecomdaily.ru</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://bigpicture.ru/wp-content/themes/bigpicture-new/assets/img/logo.svg</t>
+          <t>https://logos.hunter.io/bigpicture.ru</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Logo_Kommersant.svg</t>
+          <t>https://logos.hunter.io/kommersant.ru</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://static1.eadaily.com/i/logos/logo-squared-400.png</t>
+          <t>https://logos.hunter.io/eadaily.com</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.sostav.ru/app/public/design/logo2918-05v3.svg</t>
+          <t>https://logos.hunter.io/sostav.ru</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/69/URA.RU_logo.svg</t>
+          <t>https://logos.hunter.io/ura.news</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.seonews.ru/images/logo.svg</t>
+          <t>https://logos.hunter.io/seonews.ru</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.likeni.ru/assets/img/logo-mini.png</t>
+          <t>https://logos.hunter.io/likeni.ru</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://life.ru/img/logo.png</t>
+          <t>https://logos.hunter.io/life.ru</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.womanhit.ru/static/images/og/womanhit_ru_og_logo_1200_720.png</t>
+          <t>https://logos.hunter.io/omanhit.ru</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.avtovzglyad.ru/static/images/avtovzglyad-logo.svg</t>
+          <t>https://logos.hunter.io/avtovzglyad.ru</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.ohotniki.ru/static/images/ohotniki-logo.svg</t>
+          <t>https://logos.hunter.io/ohotniki.ru</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://mperspektiva.ru/local/templates/mp/s/images/tmp_file/header/dec-logo.webp</t>
+          <t>https://logos.hunter.io/mperspektiva.ru</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://beautyhack.ru/assets/images/logo2.png</t>
+          <t>https://logos.hunter.io/beautyhack.ru</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.sobaka.ru/img/sobaka.svg</t>
+          <t>https://logos.hunter.io/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.sobaka.ru/img/sobaka.svg</t>
+          <t>https://logos.hunter.io/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.sobaka.ru/img/sobaka.svg</t>
+          <t>https://logos.hunter.io/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/db/Forbes_logo.svg</t>
+          <t>https://logos.hunter.io/forbes.ru</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://stroygaz.ru/upload/uf/e61/oekrgwiovsiba5ajvv6147lsauedss2g.webp</t>
+          <t>https://logos.hunter.io/stroygaz.ru</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://regnum.ru/main_logo.svg</t>
+          <t>https://logos.hunter.io/regnum.ru</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://topcor.ru/templates/topcor/images/logo.png</t>
+          <t>https://logos.hunter.io/topcor.ru</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://sfera.fm/assets/media/logo/logo_sfera_header.png</t>
+          <t>https://logos.hunter.io/sfera.fm</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://brl.mk.ru/media/mkru2020/img/mk-logo.svg</t>
+          <t>https://logos.hunter.io/brl.mk.ru</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://novate.ru/img/logo.svg</t>
+          <t>https://logos.hunter.io/novate.ru</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3930-3036-4536-a464-363733353938/BCB_logo_1.svg</t>
+          <t>https://logos.hunter.io/beautycarteblanche.ru</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.vokrug.tv/images/logo-new.svg</t>
+          <t>https://logos.hunter.io/vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/vokrugsveta/8b7f3beb.svg</t>
+          <t>https://logos.hunter.io/vokrugsveta.ru</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/woman/2cb6624f.svg</t>
+          <t>https://logos.hunter.io/oman.ru</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/wday/2cb6624f.svg</t>
+          <t>https://logos.hunter.io/day.ru</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://thegirl.ru/public/sprites/thegirl/e5cb1e72ce8b.svg</t>
+          <t>https://logos.hunter.io/thegirl.ru</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/starhit/500f077c.svg</t>
+          <t>https://logos.hunter.io/starhit.ru</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/parents/b1a1d258.svg</t>
+          <t>https://logos.hunter.io/parents.ru</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/mcmaison/2cb6624f.svg</t>
+          <t>https://logos.hunter.io/mydecor.ru</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/doctorpiter/e4197781.svg</t>
+          <t>https://logos.hunter.io/doctorpiter.ru</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/wday/2cb6624f.svg</t>
+          <t>https://logos.hunter.io/the-day.ru</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/dist/maxim/f8d1d209.svg</t>
+          <t>https://logos.hunter.io/maximonline.ru</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://cdn.hsmedia.ru/ump-webapp-public/dist/client/assets/psychologies_lg_bg-light-DG40Nryg.svg</t>
+          <t>https://logos.hunter.io/psychologies.ru</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.fashiontime.ru/bitrix/templates/ft.v3/images/logo.png</t>
+          <t>https://logos.hunter.io/fashiontime.ru</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://oane.ws/templates/oane_new/logo-old.png</t>
+          <t>https://logos.hunter.io/oane.ws</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://terrnews.com/templates/Hint-utf8/images/logo66.png</t>
+          <t>https://logos.hunter.io/terrnews.com</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://kadara.ru/wp-content/uploads/2019/12/kadara-logo.png</t>
+          <t>https://logos.hunter.io/kadara.ru</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://monavista.ru/templates/newshub/images/logo-old.png</t>
+          <t>https://logos.hunter.io/monavista.ru</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://vestnik.net/images/logo_in_html.png</t>
+          <t>https://logos.hunter.io/vestnik.net</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://nvspost.ru/templates/lifewatcher/images/logo3.png</t>
+          <t>https://logos.hunter.io/nvspost.ru</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/K_Pravda_Logo_Modern.svg</t>
+          <t>https://logos.hunter.io/spb.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/K_Pravda_Logo_Modern.svg</t>
+          <t>https://logos.hunter.io/belarus.kp.ru</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://news-24.ru/wp-content/uploads/2025/01/logon24.png</t>
+          <t>https://logos.hunter.io/news-24.ru</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://smi24.news/wp-content/uploads/2024/12/group-158-1.svg</t>
+          <t>https://logos.hunter.io/smi24.news</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://www.frequentflyers.ru/wp-content/uploads/2015/10/fflogo6.png</t>
+          <t>https://logos.hunter.io/frequentflyers.ru</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://adindex.ru/assets/img/logo-adindex.svg</t>
+          <t>https://logos.hunter.io/adindex.ru</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://static.tildacdn.com/tild3938-6436-4639-b565-343838653436/Logo.svg</t>
+          <t>https://logos.hunter.io/artagmag.ru</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://img.artlebedev.ru/everything/sport24/identity/media/icons/s24_port.svg</t>
+          <t>https://logos.hunter.io/sport24.ru</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://prufy.ru/images/reg/prufy.ru.svg</t>
+          <t>https://logos.hunter.io/prufy.ru</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://www.moneytimes.ru/images/moneytimes-logo.png</t>
+          <t>https://logos.hunter.io/moneytimes.ru</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://english.pravda.ru/pix/logo_white.png</t>
+          <t>https://logos.hunter.io/english.pravda.ru</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://www.medpulse.ru/image/upload/logo512.jpg</t>
+          <t>https://logos.hunter.io/medpulse.ru</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://www.newsinfo.ru/images/newsinfo-logo.png</t>
+          <t>https://logos.hunter.io/newsinfo.ru</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://www.politonline.ru/assets/logo-5-4679515ece2fdfeb4567553a15565643.png</t>
+          <t>https://logos.hunter.io/politonline.ru</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://www.yoki.ru/images/yoki-logo.png</t>
+          <t>https://logos.hunter.io/yoki.ru</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://www.ecosever.ru/images/ecosever-logo.png</t>
+          <t>https://logos.hunter.io/ecosever.ru</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://www.nationaljournal.ru/pix/nationaljournal-logo.png</t>
+          <t>https://logos.hunter.io/nationaljournal.ru</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://www.rusday.com/pix/rusday-logo.png</t>
+          <t>https://logos.hunter.io/rusday.com</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://www.electorat.info/pix/electorat-logo.png</t>
+          <t>https://logos.hunter.io/electorat.info</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://www.mostimes.com/images/mostimes-logo.png</t>
+          <t>https://logos.hunter.io/mostimes.com</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://www.pora.ru/images/logo.png</t>
+          <t>https://logos.hunter.io/pora.ru</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://www.glavtema.ru/pix/glavtema-logo.png</t>
+          <t>https://logos.hunter.io/glavtema.ru</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://www.prbn.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/prbn.ru</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://www.bigness.ru/pix/logo.gif</t>
+          <t>https://logos.hunter.io/bigness.ru</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://www.militarytimes.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/militarytimes.ru</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://www.fizcultprivet.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/fizcultprivet.ru</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://www.poplawok.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/poplawok.ru</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://www.autokolonka.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/autokolonka.ru</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://www.repairshome.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/repairshome.ru</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://www.dailyshow.ru/images/dailyshow-logo.gif</t>
+          <t>https://logos.hunter.io/dailyshow.ru</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://www.missus.ru/pix/logo.gif</t>
+          <t>https://logos.hunter.io/missus.ru</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://www.bigcaucasus.com/pix/smalllogo.jpg</t>
+          <t>https://logos.hunter.io/bigcaucasus.com</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://www.georgiatimes.info/images/georgiatimes-logo.jpg</t>
+          <t>https://logos.hunter.io/georgiatimes.info</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://www.pravda.ru/pix/logo600_60.png</t>
+          <t>https://logos.hunter.io/pravda.ru</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://aviation21.ru/wp-content/uploads/2017/03/logo-1.png</t>
+          <t>https://logos.hunter.io/aviation21.ru</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://asninfo.ru/images/logo.png</t>
+          <t>https://logos.hunter.io/asninfo.ru</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/24/TV78logo.svg</t>
+          <t>https://logos.hunter.io/78.ru</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/67/Logo_of_Russian_magazine_The_Voice.svg</t>
+          <t>https://logos.hunter.io/thevoicemag.ru</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://moskvichmag.ru/wp-content/themes/moskmag-new/assets/img/svg/mm-xl-logo.svg</t>
+          <t>https://logos.hunter.io/moskvichmag.ru</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f1/RBK_logo.svg</t>
+          <t>https://logos.hunter.io/rbc.ru</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://moslenta.ru/favicon.svg</t>
+          <t>https://logos.hunter.io/moslenta.ru</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://kapital.kz/logo.png</t>
+          <t>https://logos.hunter.io/kapital.kz</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://lsm.kz/static/img/logo.png</t>
+          <t>https://logos.hunter.io/lsm.kz</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://newsmaker.md/wp-content/uploads/2019/01/logo_square.jpg</t>
+          <t>https://logos.hunter.io/newsmaker.md</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://cdn-1.aki.kg/st_akipress/logo_wide_300x48.png</t>
+          <t>https://logos.hunter.io/akipress.org</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://24.kg/assets/39aedacb/images/logo.png</t>
+          <t>https://logos.hunter.io/24.kg</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://noi.md/images/logo_noi_blue.jpg</t>
+          <t>https://logos.hunter.io/noi.md</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://www.uzdaily.uz/static/web/files/logo.258d31191858.svg</t>
+          <t>https://logos.hunter.io/uzdaily.uz</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://www.inform.kz/static/img/favicon.svg</t>
+          <t>https://logos.hunter.io/inform.kz</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://remedium.ru/upload/medialibrary/43b/Remedium-logo-2019-MAIN.png</t>
+          <t>https://logos.hunter.io/remedium.ru</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://medvestnik.ru/apps/mv/assets/cache/images/c7aa52eecd.svg</t>
+          <t>https://logos.hunter.io/medvestnik.ru</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://incrussia.ru/wp-content/themes/inc/img/ink_logo_space.svg</t>
+          <t>https://logos.hunter.io/incrussia.ru</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://apptractor.ru/wp-content/uploads/2025/10/logowebp-1.webp</t>
+          <t>https://logos.hunter.io/apptractor.ru</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://investfuture.ru/static/logo.png</t>
+          <t>https://logos.hunter.io/investfuture.ru</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Logo-onliner-by.png</t>
+          <t>https://logos.hunter.io/onliner.by</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://bits.media/local/templates/bits.media/images/bits4.png</t>
+          <t>https://logos.hunter.io/bits.media</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://telegraf.news/_astro/logo_black.hKlVZoUa.svg</t>
+          <t>https://logos.hunter.io/telegraf.news</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://liter.kz/build/images/liter-logo-news.png</t>
+          <t>https://logos.hunter.io/liter.kz</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://orda.kz/img/logo_d.svg</t>
+          <t>https://logos.hunter.io/orda.kz</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://dcjournal.ru/theme/codirf/images/h-logo6.png</t>
+          <t>https://logos.hunter.io/dcjournal.ru</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://telecombloger.ru/wp-content/uploads/2024/12/Logo.png</t>
+          <t>https://logos.hunter.io/telecombloger.ru</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://urbc.ru/templates/Default/images/logo.svg</t>
+          <t>https://logos.hunter.io/urbc.ru</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/ru/9/9d/%D0%9B%D0%BE%D0%B3%D0%BE%D1%82%D0%B8%D0%BF_Haqqin.az.svg</t>
+          <t>https://logos.hunter.io/haqqin.az</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://www.mosregion.info/wp-content/uploads/2024/09/mosregion_logo.png</t>
+          <t>https://logos.hunter.io/mosregion.info</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://www.sila-rf.ru/wp-content/uploads/2022/02/sila-rf.png</t>
+          <t>https://logos.hunter.io/sila-rf.ru</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://www.sibmedia.ru/wp-content/uploads/2024/07/sibmedia_logo.png</t>
+          <t>https://logos.hunter.io/sibmedia.ru</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://www.ladys.media/wp-content/themes/ladys/images/logos/logo_desktop.svg</t>
+          <t>https://logos.hunter.io/ladys.media</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://www.socialinform.ru/wp-content/uploads/2024/02/socnews_logo-1.png</t>
+          <t>https://logos.hunter.io/socialinform.ru</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://www.myeconomy.ru/wp-content/uploads/2024/11/economy-logo.png</t>
+          <t>https://logos.hunter.io/myeconomy.ru</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://www.ecopravda.ru/wp-content/uploads/2022/07/Group-210.jpg</t>
+          <t>https://logos.hunter.io/ecopravda.ru</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://medzdrav.info/wp-content/uploads/2024/01/logo_header.svg</t>
+          <t>https://logos.hunter.io/medzdrav.info</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://today.ua/svg/logo.svg</t>
+          <t>https://logos.hunter.io/today.ua</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://beautyhunter.ru/attachments/Image/bhlogo36.png</t>
+          <t>https://logos.hunter.io/beautyhunter.ru</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://informator.ua/images/logo.svg</t>
+          <t>https://logos.hunter.io/informator.ua</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://itechua.com/wp-content/uploads/2024/08/itechua-logo.png</t>
+          <t>https://logos.hunter.io/itechua.com</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://mignews.ua/static/img/logo_ua.png</t>
+          <t>https://logos.hunter.io/mignews.ua</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://www.it-world.ru/local/templates/.default/img/logo/logo_s1.svg</t>
+          <t>https://logos.hunter.io/it-world.ru</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://gazeta.ua/images/svg/gazeta.svg</t>
+          <t>https://logos.hunter.io/gazeta.ua</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/srrb.ru</t>
+          <t>https://cdn.brandfetch.io/srrb.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/apni.ru</t>
+          <t>https://cdn.brandfetch.io/apni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tvkinoradio.ru</t>
+          <t>https://cdn.brandfetch.io/tvkinoradio.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/politnavigator.net</t>
+          <t>https://cdn.brandfetch.io/politnavigator.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bloknot.ru</t>
+          <t>https://cdn.brandfetch.io/bloknot.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/delovoymir.biz</t>
+          <t>https://cdn.brandfetch.io/delovoymir.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business-magazine.online</t>
+          <t>https://cdn.brandfetch.io/business-magazine.online?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/garant.ru</t>
+          <t>https://cdn.brandfetch.io/garant.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/prophotos.ru</t>
+          <t>https://cdn.brandfetch.io/prophotos.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/peopletalk.ru</t>
+          <t>https://cdn.brandfetch.io/peopletalk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/versia.ru</t>
+          <t>https://cdn.brandfetch.io/versia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/infox.ru</t>
+          <t>https://cdn.brandfetch.io/infox.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/samag.ru</t>
+          <t>https://cdn.brandfetch.io/samag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/itweek.ru</t>
+          <t>https://cdn.brandfetch.io/itweek.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/1sept.ru</t>
+          <t>https://cdn.brandfetch.io/1sept.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/finversia.ru</t>
+          <t>https://cdn.brandfetch.io/finversia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mir24.tv</t>
+          <t>https://cdn.brandfetch.io/mir24.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lenta.ru</t>
+          <t>https://cdn.brandfetch.io/lenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/7days.ru</t>
+          <t>https://cdn.brandfetch.io/7days.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vokrug.tv</t>
+          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fedpress.ru</t>
+          <t>https://cdn.brandfetch.io/fedpress.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/securitylab.ru</t>
+          <t>https://cdn.brandfetch.io/securitylab.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/osnmedia.ru</t>
+          <t>https://cdn.brandfetch.io/osnmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/snob.ru</t>
+          <t>https://cdn.brandfetch.io/snob.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/comnews.ru</t>
+          <t>https://cdn.brandfetch.io/comnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tproger.ru</t>
+          <t>https://cdn.brandfetch.io/tproger.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/cnews.ru</t>
+          <t>https://cdn.brandfetch.io/cnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/iz.ru</t>
+          <t>https://cdn.brandfetch.io/iz.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sport-express.ru</t>
+          <t>https://cdn.brandfetch.io/sport-express.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newdaynews.ru</t>
+          <t>https://cdn.brandfetch.io/newdaynews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gazetametro.ru</t>
+          <t>https://cdn.brandfetch.io/gazetametro.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/5-tv.ru</t>
+          <t>https://cdn.brandfetch.io/5-tv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dk.ru</t>
+          <t>https://cdn.brandfetch.io/dk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/strategyjournal.ru</t>
+          <t>https://cdn.brandfetch.io/strategyjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/retailer.ru</t>
+          <t>https://cdn.brandfetch.io/retailer.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mk.ru</t>
+          <t>https://cdn.brandfetch.io/mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aif.ru</t>
+          <t>https://cdn.brandfetch.io/aif.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vedomosti.ru</t>
+          <t>https://cdn.brandfetch.io/vedomosti.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ng.ru</t>
+          <t>https://cdn.brandfetch.io/ng.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business.ru</t>
+          <t>https://cdn.brandfetch.io/business.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kom-dir.ru</t>
+          <t>https://cdn.brandfetch.io/kom-dir.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/glavbukh.ru</t>
+          <t>https://cdn.brandfetch.io/glavbukh.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/26-2.ru</t>
+          <t>https://cdn.brandfetch.io/26-2.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/buhsoft.ru</t>
+          <t>https://cdn.brandfetch.io/buhsoft.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pro-personal.ru</t>
+          <t>https://cdn.brandfetch.io/pro-personal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kdelo.ru</t>
+          <t>https://cdn.brandfetch.io/kdelo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tass.ru</t>
+          <t>https://cdn.brandfetch.io/tass.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gazeta.ru</t>
+          <t>https://cdn.brandfetch.io/gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vm.ru</t>
+          <t>https://cdn.brandfetch.io/vm.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/news.ru</t>
+          <t>https://cdn.brandfetch.io/news.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/profile.ru</t>
+          <t>https://cdn.brandfetch.io/profile.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/oilcapital.ru</t>
+          <t>https://cdn.brandfetch.io/oilcapital.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business-gazeta.ru</t>
+          <t>https://cdn.brandfetch.io/business-gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ko.ru</t>
+          <t>https://cdn.brandfetch.io/ko.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dp.ru</t>
+          <t>https://cdn.brandfetch.io/dp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/popmech.ru</t>
+          <t>https://cdn.brandfetch.io/popmech.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/svpressa.ru</t>
+          <t>https://cdn.brandfetch.io/svpressa.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ridus.ru</t>
+          <t>https://cdn.brandfetch.io/ridus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dni.ru</t>
+          <t>https://cdn.brandfetch.io/dni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/utro.ru</t>
+          <t>https://cdn.brandfetch.io/utro.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kleo.ru</t>
+          <t>https://cdn.brandfetch.io/kleo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newizv.ru</t>
+          <t>https://cdn.brandfetch.io/newizv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rosbalt.ru</t>
+          <t>https://cdn.brandfetch.io/rosbalt.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/monocle.ru</t>
+          <t>https://cdn.brandfetch.io/monocle.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rg.ru</t>
+          <t>https://cdn.brandfetch.io/rg.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/runews24.ru</t>
+          <t>https://cdn.brandfetch.io/runews24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/angi.ru</t>
+          <t>https://cdn.brandfetch.io/angi.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/naked-science.ru</t>
+          <t>https://cdn.brandfetch.io/naked-science.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/globalcio.ru</t>
+          <t>https://cdn.brandfetch.io/globalcio.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businesstory.ru</t>
+          <t>https://cdn.brandfetch.io/businesstory.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ict-online.ru</t>
+          <t>https://cdn.brandfetch.io/ict-online.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/logirus.ru</t>
+          <t>https://cdn.brandfetch.io/logirus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/24gadget.ru</t>
+          <t>https://cdn.brandfetch.io/24gadget.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/marieclaire.com</t>
+          <t>https://cdn.brandfetch.io/marieclaire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/3dnews.ru</t>
+          <t>https://cdn.brandfetch.io/3dnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/servernews.ru</t>
+          <t>https://cdn.brandfetch.io/servernews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/new-retail.ru</t>
+          <t>https://cdn.brandfetch.io/new-retail.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nakanune.ru</t>
+          <t>https://cdn.brandfetch.io/nakanune.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/telecomdaily.ru</t>
+          <t>https://cdn.brandfetch.io/telecomdaily.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bigpicture.ru</t>
+          <t>https://cdn.brandfetch.io/bigpicture.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kommersant.ru</t>
+          <t>https://cdn.brandfetch.io/kommersant.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/eadaily.com</t>
+          <t>https://cdn.brandfetch.io/eadaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sostav.ru</t>
+          <t>https://cdn.brandfetch.io/sostav.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ura.news</t>
+          <t>https://cdn.brandfetch.io/ura.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/seonews.ru</t>
+          <t>https://cdn.brandfetch.io/seonews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/likeni.ru</t>
+          <t>https://cdn.brandfetch.io/likeni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/life.ru</t>
+          <t>https://cdn.brandfetch.io/life.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sportmk.ru</t>
+          <t>https://cdn.brandfetch.io/sportmk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/omanhit.ru</t>
+          <t>https://cdn.brandfetch.io/omanhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/avtovzglyad.ru</t>
+          <t>https://cdn.brandfetch.io/avtovzglyad.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ohotniki.ru</t>
+          <t>https://cdn.brandfetch.io/ohotniki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mperspektiva.ru</t>
+          <t>https://cdn.brandfetch.io/mperspektiva.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautyhack.ru</t>
+          <t>https://cdn.brandfetch.io/beautyhack.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sobaka.ru</t>
+          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sobaka.ru</t>
+          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sobaka.ru</t>
+          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/forbes.ru</t>
+          <t>https://cdn.brandfetch.io/forbes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/stroygaz.ru</t>
+          <t>https://cdn.brandfetch.io/stroygaz.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/regnum.ru</t>
+          <t>https://cdn.brandfetch.io/regnum.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/topcor.ru</t>
+          <t>https://cdn.brandfetch.io/topcor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sfera.fm</t>
+          <t>https://cdn.brandfetch.io/sfera.fm?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/brl.mk.ru</t>
+          <t>https://cdn.brandfetch.io/brl.mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/novate.ru</t>
+          <t>https://cdn.brandfetch.io/novate.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautycarteblanche.ru</t>
+          <t>https://cdn.brandfetch.io/beautycarteblanche.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vokrug.tv</t>
+          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vokrugsveta.ru</t>
+          <t>https://cdn.brandfetch.io/vokrugsveta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/oman.ru</t>
+          <t>https://cdn.brandfetch.io/oman.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/day.ru</t>
+          <t>https://cdn.brandfetch.io/day.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thegirl.ru</t>
+          <t>https://cdn.brandfetch.io/thegirl.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/starhit.ru</t>
+          <t>https://cdn.brandfetch.io/starhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/parents.ru</t>
+          <t>https://cdn.brandfetch.io/parents.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mydecor.ru</t>
+          <t>https://cdn.brandfetch.io/mydecor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/doctorpiter.ru</t>
+          <t>https://cdn.brandfetch.io/doctorpiter.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/the-day.ru</t>
+          <t>https://cdn.brandfetch.io/the-day.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/maximonline.ru</t>
+          <t>https://cdn.brandfetch.io/maximonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/psychologies.ru</t>
+          <t>https://cdn.brandfetch.io/psychologies.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fashiontime.ru</t>
+          <t>https://cdn.brandfetch.io/fashiontime.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/oane.ws</t>
+          <t>https://cdn.brandfetch.io/oane.ws?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/terrnews.com</t>
+          <t>https://cdn.brandfetch.io/terrnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kadara.ru</t>
+          <t>https://cdn.brandfetch.io/kadara.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/monavista.ru</t>
+          <t>https://cdn.brandfetch.io/monavista.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vestnik.net</t>
+          <t>https://cdn.brandfetch.io/vestnik.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nvspost.ru</t>
+          <t>https://cdn.brandfetch.io/nvspost.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/spb.kp.ru</t>
+          <t>https://cdn.brandfetch.io/spb.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/belarus.kp.ru</t>
+          <t>https://cdn.brandfetch.io/belarus.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/—</t>
+          <t>https://cdn.brandfetch.io/—?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/news-24.ru</t>
+          <t>https://cdn.brandfetch.io/news-24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/smi24.news</t>
+          <t>https://cdn.brandfetch.io/smi24.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/obzor-gazet.ru</t>
+          <t>https://cdn.brandfetch.io/obzor-gazet.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/allmosnews.ru</t>
+          <t>https://cdn.brandfetch.io/allmosnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/promgoverment.ru</t>
+          <t>https://cdn.brandfetch.io/promgoverment.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/hotrs.su</t>
+          <t>https://cdn.brandfetch.io/hotrs.su?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mirwiki.ru</t>
+          <t>https://cdn.brandfetch.io/mirwiki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/news-bank.ru</t>
+          <t>https://cdn.brandfetch.io/news-bank.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/frequentflyers.ru</t>
+          <t>https://cdn.brandfetch.io/frequentflyers.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/adindex.ru</t>
+          <t>https://cdn.brandfetch.io/adindex.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/artagmag.ru</t>
+          <t>https://cdn.brandfetch.io/artagmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sport24.ru</t>
+          <t>https://cdn.brandfetch.io/sport24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/prufy.ru</t>
+          <t>https://cdn.brandfetch.io/prufy.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/schoolotzyv.ru</t>
+          <t>https://cdn.brandfetch.io/schoolotzyv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moneytimes.ru</t>
+          <t>https://cdn.brandfetch.io/moneytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/english.pravda.ru</t>
+          <t>https://cdn.brandfetch.io/english.pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/medpulse.ru</t>
+          <t>https://cdn.brandfetch.io/medpulse.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newsinfo.ru</t>
+          <t>https://cdn.brandfetch.io/newsinfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/politonline.ru</t>
+          <t>https://cdn.brandfetch.io/politonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/greatlove.ru</t>
+          <t>https://cdn.brandfetch.io/greatlove.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/yoki.ru</t>
+          <t>https://cdn.brandfetch.io/yoki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ecosever.ru</t>
+          <t>https://cdn.brandfetch.io/ecosever.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nationaljournal.ru</t>
+          <t>https://cdn.brandfetch.io/nationaljournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rusday.com</t>
+          <t>https://cdn.brandfetch.io/rusday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/electorat.info</t>
+          <t>https://cdn.brandfetch.io/electorat.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mostimes.com</t>
+          <t>https://cdn.brandfetch.io/mostimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pora.ru</t>
+          <t>https://cdn.brandfetch.io/pora.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/glavtema.ru</t>
+          <t>https://cdn.brandfetch.io/glavtema.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/prbn.ru</t>
+          <t>https://cdn.brandfetch.io/prbn.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bigness.ru</t>
+          <t>https://cdn.brandfetch.io/bigness.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/militarytimes.ru</t>
+          <t>https://cdn.brandfetch.io/militarytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fizcultprivet.ru</t>
+          <t>https://cdn.brandfetch.io/fizcultprivet.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/poplawok.ru</t>
+          <t>https://cdn.brandfetch.io/poplawok.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/autokolonka.ru</t>
+          <t>https://cdn.brandfetch.io/autokolonka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/repairshome.ru</t>
+          <t>https://cdn.brandfetch.io/repairshome.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dailyshow.ru</t>
+          <t>https://cdn.brandfetch.io/dailyshow.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/missus.ru</t>
+          <t>https://cdn.brandfetch.io/missus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bigcaucasus.com</t>
+          <t>https://cdn.brandfetch.io/bigcaucasus.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/georgiatimes.info</t>
+          <t>https://cdn.brandfetch.io/georgiatimes.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pravda.ru</t>
+          <t>https://cdn.brandfetch.io/pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aviation21.ru</t>
+          <t>https://cdn.brandfetch.io/aviation21.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/isguru.ru</t>
+          <t>https://cdn.brandfetch.io/isguru.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/asninfo.ru</t>
+          <t>https://cdn.brandfetch.io/asninfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/78.ru</t>
+          <t>https://cdn.brandfetch.io/78.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thevoicemag.ru</t>
+          <t>https://cdn.brandfetch.io/thevoicemag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moskvichmag.ru</t>
+          <t>https://cdn.brandfetch.io/moskvichmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rbc.ru</t>
+          <t>https://cdn.brandfetch.io/rbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moslenta.ru</t>
+          <t>https://cdn.brandfetch.io/moslenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kapital.kz</t>
+          <t>https://cdn.brandfetch.io/kapital.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lsm.kz</t>
+          <t>https://cdn.brandfetch.io/lsm.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newsmaker.md</t>
+          <t>https://cdn.brandfetch.io/newsmaker.md?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/akipress.org</t>
+          <t>https://cdn.brandfetch.io/akipress.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/24.kg</t>
+          <t>https://cdn.brandfetch.io/24.kg?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/noi.md</t>
+          <t>https://cdn.brandfetch.io/noi.md?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/uzdaily.uz</t>
+          <t>https://cdn.brandfetch.io/uzdaily.uz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/inform.kz</t>
+          <t>https://cdn.brandfetch.io/inform.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/remedium.ru</t>
+          <t>https://cdn.brandfetch.io/remedium.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/medvestnik.ru</t>
+          <t>https://cdn.brandfetch.io/medvestnik.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/incrussia.ru</t>
+          <t>https://cdn.brandfetch.io/incrussia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/apptractor.ru</t>
+          <t>https://cdn.brandfetch.io/apptractor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/investfuture.ru</t>
+          <t>https://cdn.brandfetch.io/investfuture.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/onliner.by</t>
+          <t>https://cdn.brandfetch.io/onliner.by?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bits.media</t>
+          <t>https://cdn.brandfetch.io/bits.media?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/telegraf.news</t>
+          <t>https://cdn.brandfetch.io/telegraf.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/liter.kz</t>
+          <t>https://cdn.brandfetch.io/liter.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/orda.kz</t>
+          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dcjournal.ru</t>
+          <t>https://cdn.brandfetch.io/dcjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/telecombloger.ru</t>
+          <t>https://cdn.brandfetch.io/telecombloger.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/urbc.ru</t>
+          <t>https://cdn.brandfetch.io/urbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/haqqin.az</t>
+          <t>https://cdn.brandfetch.io/haqqin.az?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mosregion.info</t>
+          <t>https://cdn.brandfetch.io/mosregion.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sila-rf.ru</t>
+          <t>https://cdn.brandfetch.io/sila-rf.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sibmedia.ru</t>
+          <t>https://cdn.brandfetch.io/sibmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ladys.media</t>
+          <t>https://cdn.brandfetch.io/ladys.media?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/socialinform.ru</t>
+          <t>https://cdn.brandfetch.io/socialinform.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/myeconomy.ru</t>
+          <t>https://cdn.brandfetch.io/myeconomy.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ecopravda.ru</t>
+          <t>https://cdn.brandfetch.io/ecopravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/medzdrav.info</t>
+          <t>https://cdn.brandfetch.io/medzdrav.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/today.ua</t>
+          <t>https://cdn.brandfetch.io/today.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautyhunter.ru</t>
+          <t>https://cdn.brandfetch.io/beautyhunter.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/informator.ua</t>
+          <t>https://cdn.brandfetch.io/informator.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/itechua.com</t>
+          <t>https://cdn.brandfetch.io/itechua.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mignews.ua</t>
+          <t>https://cdn.brandfetch.io/mignews.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/it-world.ru</t>
+          <t>https://cdn.brandfetch.io/it-world.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gazeta.ua</t>
+          <t>https://cdn.brandfetch.io/gazeta.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/homebusinessmag.com</t>
+          <t>https://cdn.brandfetch.io/homebusinessmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/miamiherald.com</t>
+          <t>https://cdn.brandfetch.io/miamiherald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kansascity.com</t>
+          <t>https://cdn.brandfetch.io/kansascity.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techtimes.com</t>
+          <t>https://cdn.brandfetch.io/techtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/brainzmagazine.com</t>
+          <t>https://cdn.brandfetch.io/brainzmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/latinpost.com</t>
+          <t>https://cdn.brandfetch.io/latinpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/jpost.com</t>
+          <t>https://cdn.brandfetch.io/jpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thewestnews.com</t>
+          <t>https://cdn.brandfetch.io/thewestnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vinnews.com</t>
+          <t>https://cdn.brandfetch.io/vinnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fxstreet.com</t>
+          <t>https://cdn.brandfetch.io/fxstreet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/inc.com</t>
+          <t>https://cdn.brandfetch.io/inc.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/computing.co.uk</t>
+          <t>https://cdn.brandfetch.io/computing.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/crn.com</t>
+          <t>https://cdn.brandfetch.io/crn.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/intlbm.com</t>
+          <t>https://cdn.brandfetch.io/intlbm.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/adexchanger.com</t>
+          <t>https://cdn.brandfetch.io/adexchanger.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thedrum.com</t>
+          <t>https://cdn.brandfetch.io/thedrum.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/globalbankingandfinance.com</t>
+          <t>https://cdn.brandfetch.io/globalbankingandfinance.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/financedigest.com</t>
+          <t>https://cdn.brandfetch.io/financedigest.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fastcompany.com</t>
+          <t>https://cdn.brandfetch.io/fastcompany.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/technologymagazine.com</t>
+          <t>https://cdn.brandfetch.io/technologymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aimagazine.com</t>
+          <t>https://cdn.brandfetch.io/aimagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businesschief.eu</t>
+          <t>https://cdn.brandfetch.io/businesschief.eu?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/housingwire.com</t>
+          <t>https://cdn.brandfetch.io/housingwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/paymentscardsandmobile.com</t>
+          <t>https://cdn.brandfetch.io/paymentscardsandmobile.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/digitalconnectmag.com</t>
+          <t>https://cdn.brandfetch.io/digitalconnectmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/healthcarebusinesstoday.com</t>
+          <t>https://cdn.brandfetch.io/healthcarebusinesstoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/digiday.com</t>
+          <t>https://cdn.brandfetch.io/digiday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aitimejournal.com</t>
+          <t>https://cdn.brandfetch.io/aitimejournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/geekextreme.com</t>
+          <t>https://cdn.brandfetch.io/geekextreme.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/coingape.com</t>
+          <t>https://cdn.brandfetch.io/coingape.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/arabianbusiness.com</t>
+          <t>https://cdn.brandfetch.io/arabianbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businesstechnet.com</t>
+          <t>https://cdn.brandfetch.io/businesstechnet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techstacy.com</t>
+          <t>https://cdn.brandfetch.io/techstacy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/europeanbusinessreview.com</t>
+          <t>https://cdn.brandfetch.io/europeanbusinessreview.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/educationtechnologyinsights.com</t>
+          <t>https://cdn.brandfetch.io/educationtechnologyinsights.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/digitaljournal.com</t>
+          <t>https://cdn.brandfetch.io/digitaljournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ealthybyte.com</t>
+          <t>https://cdn.brandfetch.io/ealthybyte.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techinasia.com</t>
+          <t>https://cdn.brandfetch.io/techinasia.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/siliconcanals.com</t>
+          <t>https://cdn.brandfetch.io/siliconcanals.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bizfortune.com</t>
+          <t>https://cdn.brandfetch.io/bizfortune.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ciobulletin.com</t>
+          <t>https://cdn.brandfetch.io/ciobulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/abcmoney.co.uk</t>
+          <t>https://cdn.brandfetch.io/abcmoney.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ceo-review.com</t>
+          <t>https://cdn.brandfetch.io/ceo-review.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/corporatevision-news.com</t>
+          <t>https://cdn.brandfetch.io/corporatevision-news.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/startupsmagazine.co.uk</t>
+          <t>https://cdn.brandfetch.io/startupsmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lux-life.digital</t>
+          <t>https://cdn.brandfetch.io/lux-life.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/build-review.com</t>
+          <t>https://cdn.brandfetch.io/build-review.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/smenews.digital</t>
+          <t>https://cdn.brandfetch.io/smenews.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ghpnews.digital</t>
+          <t>https://cdn.brandfetch.io/ghpnews.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/acquisition-international.com</t>
+          <t>https://cdn.brandfetch.io/acquisition-international.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ealthandfinance.digital</t>
+          <t>https://cdn.brandfetch.io/ealthandfinance.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/eubusinessnews.com</t>
+          <t>https://cdn.brandfetch.io/eubusinessnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/meamarkets.digital</t>
+          <t>https://cdn.brandfetch.io/meamarkets.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/apacinsider.digital</t>
+          <t>https://cdn.brandfetch.io/apacinsider.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/coventryobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/coventryobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bromsgrovestandard.co.uk</t>
+          <t>https://cdn.brandfetch.io/bromsgrovestandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/droitwichstandard.co.uk</t>
+          <t>https://cdn.brandfetch.io/droitwichstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/eveshamobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/eveshamobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kidderminsterstandard.co.uk</t>
+          <t>https://cdn.brandfetch.io/kidderminsterstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/leamingtonobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/leamingtonobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/malvernobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/malvernobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/redditchstandard.co.uk</t>
+          <t>https://cdn.brandfetch.io/redditchstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rugbyobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/rugbyobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/solihullobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/solihullobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/stratfordobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/stratfordobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/orcesterobserver.co.uk</t>
+          <t>https://cdn.brandfetch.io/orcesterobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/richmond.com</t>
+          <t>https://cdn.brandfetch.io/richmond.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fredericksburg.com</t>
+          <t>https://cdn.brandfetch.io/fredericksburg.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/roanoke.com</t>
+          <t>https://cdn.brandfetch.io/roanoke.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newsadvance.com</t>
+          <t>https://cdn.brandfetch.io/newsadvance.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dailyprogress.com</t>
+          <t>https://cdn.brandfetch.io/dailyprogress.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/heraldcourier.com</t>
+          <t>https://cdn.brandfetch.io/heraldcourier.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/martinsvillebulletin.com</t>
+          <t>https://cdn.brandfetch.io/martinsvillebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/newsvirginian.com</t>
+          <t>https://cdn.brandfetch.io/newsvirginian.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thefranklinnewspost.com</t>
+          <t>https://cdn.brandfetch.io/thefranklinnewspost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/godanriver.com</t>
+          <t>https://cdn.brandfetch.io/godanriver.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/starexponent.com</t>
+          <t>https://cdn.brandfetch.io/starexponent.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/smithmountainlake.com</t>
+          <t>https://cdn.brandfetch.io/smithmountainlake.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/swvatoday.com</t>
+          <t>https://cdn.brandfetch.io/swvatoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/naludamagazine.com</t>
+          <t>https://cdn.brandfetch.io/naludamagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tech-critter.com</t>
+          <t>https://cdn.brandfetch.io/tech-critter.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nasilemaktech.com</t>
+          <t>https://cdn.brandfetch.io/nasilemaktech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/myeverydaytech.com</t>
+          <t>https://cdn.brandfetch.io/myeverydaytech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businessfostermagazine.com</t>
+          <t>https://cdn.brandfetch.io/businessfostermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/business-money.com</t>
+          <t>https://cdn.brandfetch.io/business-money.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businesscloud.co.uk</t>
+          <t>https://cdn.brandfetch.io/businesscloud.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gritdaily.com</t>
+          <t>https://cdn.brandfetch.io/gritdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thesiliconreview.com</t>
+          <t>https://cdn.brandfetch.io/thesiliconreview.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thestreet.com</t>
+          <t>https://cdn.brandfetch.io/thestreet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thedefiant.io</t>
+          <t>https://cdn.brandfetch.io/thedefiant.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/smartechdaily.com</t>
+          <t>https://cdn.brandfetch.io/smartechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/meditechtoday.com</t>
+          <t>https://cdn.brandfetch.io/meditechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/financialtechtimes.com</t>
+          <t>https://cdn.brandfetch.io/financialtechtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/blocktelegraph.io</t>
+          <t>https://cdn.brandfetch.io/blocktelegraph.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/transittomorrow.com</t>
+          <t>https://cdn.brandfetch.io/transittomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/highnetworthmag.com</t>
+          <t>https://cdn.brandfetch.io/highnetworthmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/pharmatechnews.com</t>
+          <t>https://cdn.brandfetch.io/pharmatechnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxurylamag.com</t>
+          <t>https://cdn.brandfetch.io/luxurylamag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxurymiamimag.com</t>
+          <t>https://cdn.brandfetch.io/luxurymiamimag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lawnewsday.com</t>
+          <t>https://cdn.brandfetch.io/lawnewsday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gametechdaily.com</t>
+          <t>https://cdn.brandfetch.io/gametechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ealthtechdaily.com</t>
+          <t>https://cdn.brandfetch.io/ealthtechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sportstechtoday.com</t>
+          <t>https://cdn.brandfetch.io/sportstechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/meditechwire.com</t>
+          <t>https://cdn.brandfetch.io/meditechwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/coinreviewnews.com</t>
+          <t>https://cdn.brandfetch.io/coinreviewnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/innotechtoday.com</t>
+          <t>https://cdn.brandfetch.io/innotechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/csq.com</t>
+          <t>https://cdn.brandfetch.io/csq.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techfundingnews.com</t>
+          <t>https://cdn.brandfetch.io/techfundingnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/millennialmagazine.com</t>
+          <t>https://cdn.brandfetch.io/millennialmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/deccanherald.com</t>
+          <t>https://cdn.brandfetch.io/deccanherald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/amazingarchitecture.com</t>
+          <t>https://cdn.brandfetch.io/amazingarchitecture.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/healthworkscollective.com</t>
+          <t>https://cdn.brandfetch.io/healthworkscollective.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/goodmenproject.com</t>
+          <t>https://cdn.brandfetch.io/goodmenproject.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gilmorehealth.com</t>
+          <t>https://cdn.brandfetch.io/gilmorehealth.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/papermag.com</t>
+          <t>https://cdn.brandfetch.io/papermag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bust.com</t>
+          <t>https://cdn.brandfetch.io/bust.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/villagevoice.com</t>
+          <t>https://cdn.brandfetch.io/villagevoice.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/irvineweekly.com</t>
+          <t>https://cdn.brandfetch.io/irvineweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/marinatimes.com</t>
+          <t>https://cdn.brandfetch.io/marinatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thecharlotteweekly.com</t>
+          <t>https://cdn.brandfetch.io/thecharlotteweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/theleadernews.com</t>
+          <t>https://cdn.brandfetch.io/theleadernews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fortbendstar.com</t>
+          <t>https://cdn.brandfetch.io/fortbendstar.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lakerlutznews.com</t>
+          <t>https://cdn.brandfetch.io/lakerlutznews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/laweekly.com</t>
+          <t>https://cdn.brandfetch.io/laweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ocweekly.com</t>
+          <t>https://cdn.brandfetch.io/ocweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/inbuzzer.com</t>
+          <t>https://cdn.brandfetch.io/inbuzzer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businessmole.com</t>
+          <t>https://cdn.brandfetch.io/businessmole.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/instrumentalfx.co</t>
+          <t>https://cdn.brandfetch.io/instrumentalfx.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fadmagazine.com</t>
+          <t>https://cdn.brandfetch.io/fadmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/eraveyou.com</t>
+          <t>https://cdn.brandfetch.io/eraveyou.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sportsgossip.com</t>
+          <t>https://cdn.brandfetch.io/sportsgossip.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sportsmedia101.com</t>
+          <t>https://cdn.brandfetch.io/sportsmedia101.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bostonsportsextra.com</t>
+          <t>https://cdn.brandfetch.io/bostonsportsextra.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fangsbites.com</t>
+          <t>https://cdn.brandfetch.io/fangsbites.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/alltechmagazine.com</t>
+          <t>https://cdn.brandfetch.io/alltechmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/architectureartdesigns.com</t>
+          <t>https://cdn.brandfetch.io/architectureartdesigns.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ceotodaymagazine.com</t>
+          <t>https://cdn.brandfetch.io/ceotodaymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/insidermonkey.com</t>
+          <t>https://cdn.brandfetch.io/insidermonkey.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/securityonline.info</t>
+          <t>https://cdn.brandfetch.io/securityonline.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/securityexpress.info</t>
+          <t>https://cdn.brandfetch.io/securityexpress.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/meterpreter.org</t>
+          <t>https://cdn.brandfetch.io/meterpreter.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techiexpert.com</t>
+          <t>https://cdn.brandfetch.io/techiexpert.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxuryhousingtrends.com</t>
+          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/iplocation.net</t>
+          <t>https://cdn.brandfetch.io/iplocation.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/opsmatters.com</t>
+          <t>https://cdn.brandfetch.io/opsmatters.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businesshonor.com</t>
+          <t>https://cdn.brandfetch.io/businesshonor.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/highways.today</t>
+          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/hometownstation.com</t>
+          <t>https://cdn.brandfetch.io/hometownstation.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/latintimes.com</t>
+          <t>https://cdn.brandfetch.io/latintimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techloy.com</t>
+          <t>https://cdn.brandfetch.io/techloy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/americancraftbeer.com</t>
+          <t>https://cdn.brandfetch.io/americancraftbeer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beerconnoisseur.com</t>
+          <t>https://cdn.brandfetch.io/beerconnoisseur.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/porchdrinking.com</t>
+          <t>https://cdn.brandfetch.io/porchdrinking.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mantelligence.com</t>
+          <t>https://cdn.brandfetch.io/mantelligence.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/brulosophy.com</t>
+          <t>https://cdn.brandfetch.io/brulosophy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ashingtonbeerblog.com</t>
+          <t>https://cdn.brandfetch.io/ashingtonbeerblog.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/breweriesinpa.com</t>
+          <t>https://cdn.brandfetch.io/breweriesinpa.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sandiegobeer.news</t>
+          <t>https://cdn.brandfetch.io/sandiegobeer.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/livemusicblog.com</t>
+          <t>https://cdn.brandfetch.io/livemusicblog.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/mybeerbuzz.com</t>
+          <t>https://cdn.brandfetch.io/mybeerbuzz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/highways.today</t>
+          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxuryhousingtrends.com</t>
+          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/timesla.com</t>
+          <t>https://cdn.brandfetch.io/timesla.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gearrice.com</t>
+          <t>https://cdn.brandfetch.io/gearrice.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/inkl.com</t>
+          <t>https://cdn.brandfetch.io/inkl.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nyweekly.com</t>
+          <t>https://cdn.brandfetch.io/nyweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/artistweekly.com</t>
+          <t>https://cdn.brandfetch.io/artistweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ceoweekly.com</t>
+          <t>https://cdn.brandfetch.io/ceoweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/atlwire.com</t>
+          <t>https://cdn.brandfetch.io/atlwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thechicagojournal.com</t>
+          <t>https://cdn.brandfetch.io/thechicagojournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/emonthlynews.com</t>
+          <t>https://cdn.brandfetch.io/emonthlynews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lawire.com</t>
+          <t>https://cdn.brandfetch.io/lawire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/beautyscene.net</t>
+          <t>https://cdn.brandfetch.io/beautyscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/londonlovesproperty.com</t>
+          <t>https://cdn.brandfetch.io/londonlovesproperty.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/londonlovestech.com</t>
+          <t>https://cdn.brandfetch.io/londonlovestech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nimvo.com</t>
+          <t>https://cdn.brandfetch.io/nimvo.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/chaospin.com</t>
+          <t>https://cdn.brandfetch.io/chaospin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/malemodelscene.net</t>
+          <t>https://cdn.brandfetch.io/malemodelscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thebusinesswomanmedia.com</t>
+          <t>https://cdn.brandfetch.io/thebusinesswomanmedia.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techbullion.com</t>
+          <t>https://cdn.brandfetch.io/techbullion.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fashionuer.com</t>
+          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/moneyinc.com</t>
+          <t>https://cdn.brandfetch.io/moneyinc.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/londonlovesbusiness.com</t>
+          <t>https://cdn.brandfetch.io/londonlovesbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bmmagazine.co.uk</t>
+          <t>https://cdn.brandfetch.io/bmmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/designscene.net</t>
+          <t>https://cdn.brandfetch.io/designscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fashionuer.com</t>
+          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/entrepreneurhandbook.co.uk</t>
+          <t>https://cdn.brandfetch.io/entrepreneurhandbook.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/notorious-mag.com</t>
+          <t>https://cdn.brandfetch.io/notorious-mag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thelondoneconomic.com</t>
+          <t>https://cdn.brandfetch.io/thelondoneconomic.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techstartups.com</t>
+          <t>https://cdn.brandfetch.io/techstartups.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/swaggermagazine.com</t>
+          <t>https://cdn.brandfetch.io/swaggermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aijourn.com</t>
+          <t>https://cdn.brandfetch.io/aijourn.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/financefeeds.com</t>
+          <t>https://cdn.brandfetch.io/financefeeds.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sciencetimes.com</t>
+          <t>https://cdn.brandfetch.io/sciencetimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/itechpost.com</t>
+          <t>https://cdn.brandfetch.io/itechpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/plainenglish.io</t>
+          <t>https://cdn.brandfetch.io/plainenglish.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techround.co.uk</t>
+          <t>https://cdn.brandfetch.io/techround.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/eureporter.co</t>
+          <t>https://cdn.brandfetch.io/eureporter.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dataconomy.com</t>
+          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ceoworld.biz</t>
+          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/allwomenstalk.com</t>
+          <t>https://cdn.brandfetch.io/allwomenstalk.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ceoworld.biz</t>
+          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/u.today</t>
+          <t>https://cdn.brandfetch.io/u.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/esternjournal.com</t>
+          <t>https://cdn.brandfetch.io/esternjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techworm.net</t>
+          <t>https://cdn.brandfetch.io/techworm.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ibtimes.com</t>
+          <t>https://cdn.brandfetch.io/ibtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/theubj.com</t>
+          <t>https://cdn.brandfetch.io/theubj.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/archiscene.net</t>
+          <t>https://cdn.brandfetch.io/archiscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/largest.org</t>
+          <t>https://cdn.brandfetch.io/largest.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dailycivil.com</t>
+          <t>https://cdn.brandfetch.io/dailycivil.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tidtiltech.dk</t>
+          <t>https://cdn.brandfetch.io/tidtiltech.dk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/asianatimes.com</t>
+          <t>https://cdn.brandfetch.io/asianatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/musicraiser.net</t>
+          <t>https://cdn.brandfetch.io/musicraiser.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/utilizewindows.com</t>
+          <t>https://cdn.brandfetch.io/utilizewindows.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thetvjunkies.com</t>
+          <t>https://cdn.brandfetch.io/thetvjunkies.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tu.tv</t>
+          <t>https://cdn.brandfetch.io/tu.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/networthrant.com</t>
+          <t>https://cdn.brandfetch.io/networthrant.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/jewelbeat.com</t>
+          <t>https://cdn.brandfetch.io/jewelbeat.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/desksgram.net</t>
+          <t>https://cdn.brandfetch.io/desksgram.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/vxchnge.com</t>
+          <t>https://cdn.brandfetch.io/vxchnge.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/liberalco.org</t>
+          <t>https://cdn.brandfetch.io/liberalco.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kiwibox.com</t>
+          <t>https://cdn.brandfetch.io/kiwibox.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ebsta.me</t>
+          <t>https://cdn.brandfetch.io/ebsta.me?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techktimes.co.uk</t>
+          <t>https://cdn.brandfetch.io/techktimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/koreaittimes.com</t>
+          <t>https://cdn.brandfetch.io/koreaittimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/breakingac.com</t>
+          <t>https://cdn.brandfetch.io/breakingac.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/maryberryrecipes.co.uk</t>
+          <t>https://cdn.brandfetch.io/maryberryrecipes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/londontime.co</t>
+          <t>https://cdn.brandfetch.io/londontime.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/theluxurylifestylemagazine.com</t>
+          <t>https://cdn.brandfetch.io/theluxurylifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxurylifestylemag.co.uk</t>
+          <t>https://cdn.brandfetch.io/luxurylifestylemag.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxurialifestyle.com</t>
+          <t>https://cdn.brandfetch.io/luxurialifestyle.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/spacedaily.com</t>
+          <t>https://cdn.brandfetch.io/spacedaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/racinecountyeye.com</t>
+          <t>https://cdn.brandfetch.io/racinecountyeye.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/timesofisrael.com</t>
+          <t>https://cdn.brandfetch.io/timesofisrael.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/hardreset.info</t>
+          <t>https://cdn.brandfetch.io/hardreset.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/imei.info</t>
+          <t>https://cdn.brandfetch.io/imei.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/applesn.info</t>
+          <t>https://cdn.brandfetch.io/applesn.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dataconomy.com</t>
+          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/radaronline.com</t>
+          <t>https://cdn.brandfetch.io/radaronline.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/okmagazine.com</t>
+          <t>https://cdn.brandfetch.io/okmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/onderwall.com</t>
+          <t>https://cdn.brandfetch.io/onderwall.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/knewz.com</t>
+          <t>https://cdn.brandfetch.io/knewz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/frontpagedetectives.com</t>
+          <t>https://cdn.brandfetch.io/frontpagedetectives.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/omensgolfjournal.com</t>
+          <t>https://cdn.brandfetch.io/omensgolfjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/morninghoney.com</t>
+          <t>https://cdn.brandfetch.io/morninghoney.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/dailycoin.com</t>
+          <t>https://cdn.brandfetch.io/dailycoin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bestforandroid.com</t>
+          <t>https://cdn.brandfetch.io/bestforandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/esthawaiitoday.com</t>
+          <t>https://cdn.brandfetch.io/esthawaiitoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/midweek.com</t>
+          <t>https://cdn.brandfetch.io/midweek.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/hawaiitribune-herald.com</t>
+          <t>https://cdn.brandfetch.io/hawaiitribune-herald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/thegardenisland.com</t>
+          <t>https://cdn.brandfetch.io/thegardenisland.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/staradvertiser.com</t>
+          <t>https://cdn.brandfetch.io/staradvertiser.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ustimesnow.com</t>
+          <t>https://cdn.brandfetch.io/ustimesnow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/homecrux.com</t>
+          <t>https://cdn.brandfetch.io/homecrux.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/modelifestylemagazine.com</t>
+          <t>https://cdn.brandfetch.io/modelifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aiworldtoday.net</t>
+          <t>https://cdn.brandfetch.io/aiworldtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/digitalconvey.com</t>
+          <t>https://cdn.brandfetch.io/digitalconvey.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/trillmag.com</t>
+          <t>https://cdn.brandfetch.io/trillmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businessoutstanders.com</t>
+          <t>https://cdn.brandfetch.io/businessoutstanders.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/metapress.com</t>
+          <t>https://cdn.brandfetch.io/metapress.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/geeky-gadgets.com</t>
+          <t>https://cdn.brandfetch.io/geeky-gadgets.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gizchina.com</t>
+          <t>https://cdn.brandfetch.io/gizchina.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/coinprwire.com</t>
+          <t>https://cdn.brandfetch.io/coinprwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/psbios.me</t>
+          <t>https://cdn.brandfetch.io/psbios.me?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/timebulletin.com</t>
+          <t>https://cdn.brandfetch.io/timebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/cyberpress.org</t>
+          <t>https://cdn.brandfetch.io/cyberpress.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gbhackers.com</t>
+          <t>https://cdn.brandfetch.io/gbhackers.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/cybersecuritynews.com</t>
+          <t>https://cdn.brandfetch.io/cybersecuritynews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/analyticsinsight.net</t>
+          <t>https://cdn.brandfetch.io/analyticsinsight.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/secureblitz.com</t>
+          <t>https://cdn.brandfetch.io/secureblitz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techdee.com</t>
+          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/talkandroid.com</t>
+          <t>https://cdn.brandfetch.io/talkandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/technology.org</t>
+          <t>https://cdn.brandfetch.io/technology.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/kalilinuxtutorials.com</t>
+          <t>https://cdn.brandfetch.io/kalilinuxtutorials.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/startup.info</t>
+          <t>https://cdn.brandfetch.io/startup.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fontsarena.com</t>
+          <t>https://cdn.brandfetch.io/fontsarena.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/applegazette.com</t>
+          <t>https://cdn.brandfetch.io/applegazette.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bonjouridee.com</t>
+          <t>https://cdn.brandfetch.io/bonjouridee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/hardwaresecrets.com</t>
+          <t>https://cdn.brandfetch.io/hardwaresecrets.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/fontmirror.com</t>
+          <t>https://cdn.brandfetch.io/fontmirror.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/technochops.com</t>
+          <t>https://cdn.brandfetch.io/technochops.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/socialnewsdaily.com</t>
+          <t>https://cdn.brandfetch.io/socialnewsdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/cssbasics.com</t>
+          <t>https://cdn.brandfetch.io/cssbasics.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tubetorial.com</t>
+          <t>https://cdn.brandfetch.io/tubetorial.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/apps.uk</t>
+          <t>https://cdn.brandfetch.io/apps.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/paktales.com</t>
+          <t>https://cdn.brandfetch.io/paktales.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/только</t>
+          <t>https://cdn.brandfetch.io/только?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techdee.com</t>
+          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/technoroll.org</t>
+          <t>https://cdn.brandfetch.io/technoroll.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techstrange.com</t>
+          <t>https://cdn.brandfetch.io/techstrange.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techrado.com</t>
+          <t>https://cdn.brandfetch.io/techrado.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35801,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/travellingforbusiness.co.uk</t>
+          <t>https://cdn.brandfetch.io/travellingforbusiness.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35873,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/evpowered.co.uk</t>
+          <t>https://cdn.brandfetch.io/evpowered.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/electrichome.uk</t>
+          <t>https://cdn.brandfetch.io/electrichome.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/propertyportfolioinvestor.co.uk</t>
+          <t>https://cdn.brandfetch.io/propertyportfolioinvestor.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techzeel.net</t>
+          <t>https://cdn.brandfetch.io/techzeel.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/learningtoday.net</t>
+          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/allinsider.net</t>
+          <t>https://cdn.brandfetch.io/allinsider.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36305,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sportzbuzz.net</t>
+          <t>https://cdn.brandfetch.io/sportzbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36377,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/nextluxury.com</t>
+          <t>https://cdn.brandfetch.io/nextluxury.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/stepbystepbusiness.com</t>
+          <t>https://cdn.brandfetch.io/stepbystepbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36521,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/jt.org</t>
+          <t>https://cdn.brandfetch.io/jt.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36593,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/blueandgreentomorrow.com</t>
+          <t>https://cdn.brandfetch.io/blueandgreentomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techspotty.com</t>
+          <t>https://cdn.brandfetch.io/techspotty.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/aboutchromebooks.com</t>
+          <t>https://cdn.brandfetch.io/aboutchromebooks.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/digitaledge.org</t>
+          <t>https://cdn.brandfetch.io/digitaledge.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/connectioncafe.com</t>
+          <t>https://cdn.brandfetch.io/connectioncafe.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tabletmonkeys.com</t>
+          <t>https://cdn.brandfetch.io/tabletmonkeys.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/quantumrun.com</t>
+          <t>https://cdn.brandfetch.io/quantumrun.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/gadgetfreeks.com</t>
+          <t>https://cdn.brandfetch.io/gadgetfreeks.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/hatsontech.co.uk</t>
+          <t>https://cdn.brandfetch.io/hatsontech.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/voddler.co.uk</t>
+          <t>https://cdn.brandfetch.io/voddler.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/citybiz.co</t>
+          <t>https://cdn.brandfetch.io/citybiz.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/insiderpaper.com</t>
+          <t>https://cdn.brandfetch.io/insiderpaper.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37457,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/onlinebizbooster.net</t>
+          <t>https://cdn.brandfetch.io/onlinebizbooster.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businessandpower.com</t>
+          <t>https://cdn.brandfetch.io/businessandpower.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37601,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/solidsmack.com</t>
+          <t>https://cdn.brandfetch.io/solidsmack.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37673,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/jguru.com</t>
+          <t>https://cdn.brandfetch.io/jguru.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/alltechbuzz.net</t>
+          <t>https://cdn.brandfetch.io/alltechbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/baycitizen.org</t>
+          <t>https://cdn.brandfetch.io/baycitizen.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/silicon</t>
+          <t>https://cdn.brandfetch.io/silicon?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/triphippies.com</t>
+          <t>https://cdn.brandfetch.io/triphippies.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/learningtoday.net</t>
+          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38105,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ecommercefastlane.com</t>
+          <t>https://cdn.brandfetch.io/ecommercefastlane.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/netizensreport.com</t>
+          <t>https://cdn.brandfetch.io/netizensreport.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/startup</t>
+          <t>https://cdn.brandfetch.io/startup?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/guruhitech.com</t>
+          <t>https://cdn.brandfetch.io/guruhitech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/britishwire.com</t>
+          <t>https://cdn.brandfetch.io/britishwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/investing.com</t>
+          <t>https://cdn.brandfetch.io/investing.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/the-tech-trend.com</t>
+          <t>https://cdn.brandfetch.io/the-tech-trend.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38609,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/arrington-worldwide.co.uk</t>
+          <t>https://cdn.brandfetch.io/arrington-worldwide.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/archeyes.com</t>
+          <t>https://cdn.brandfetch.io/archeyes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38753,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/sportswane.com</t>
+          <t>https://cdn.brandfetch.io/sportswane.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/techwalls.com</t>
+          <t>https://cdn.brandfetch.io/techwalls.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38897,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/lawbhoomi.com</t>
+          <t>https://cdn.brandfetch.io/lawbhoomi.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38969,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/businessnewsthisweek.com</t>
+          <t>https://cdn.brandfetch.io/businessnewsthisweek.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/guardian.ng</t>
+          <t>https://cdn.brandfetch.io/guardian.ng?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/londondaily.news</t>
+          <t>https://cdn.brandfetch.io/londondaily.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/london-post.co.uk</t>
+          <t>https://cdn.brandfetch.io/london-post.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/omenontopp.com</t>
+          <t>https://cdn.brandfetch.io/omenontopp.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/impactwealth.org</t>
+          <t>https://cdn.brandfetch.io/impactwealth.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/africa.businessinsider.com</t>
+          <t>https://cdn.brandfetch.io/africa.businessinsider.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39473,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/measurescopez.com</t>
+          <t>https://cdn.brandfetch.io/measurescopez.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ukbusinesstimes.co.uk</t>
+          <t>https://cdn.brandfetch.io/ukbusinesstimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/londoninsider.co.uk</t>
+          <t>https://cdn.brandfetch.io/londoninsider.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/ibusiness.news</t>
+          <t>https://cdn.brandfetch.io/ibusiness.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/theluxauthority.com</t>
+          <t>https://cdn.brandfetch.io/theluxauthority.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/congress.net</t>
+          <t>https://cdn.brandfetch.io/congress.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/bitzuma.com</t>
+          <t>https://cdn.brandfetch.io/bitzuma.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39977,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/asiapresswire.com</t>
+          <t>https://cdn.brandfetch.io/asiapresswire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/grazia.si</t>
+          <t>https://cdn.brandfetch.io/grazia.si?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/luxuo.com</t>
+          <t>https://cdn.brandfetch.io/luxuo.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40193,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/glamour.bg</t>
+          <t>https://cdn.brandfetch.io/glamour.bg?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/digitalbusiness.kz</t>
+          <t>https://cdn.brandfetch.io/digitalbusiness.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/zakon.kz</t>
+          <t>https://cdn.brandfetch.io/zakon.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40490,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/informburo.kz</t>
+          <t>https://cdn.brandfetch.io/informburo.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/rasdaily.kz</t>
+          <t>https://cdn.brandfetch.io/rasdaily.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/caravan.kz</t>
+          <t>https://cdn.brandfetch.io/caravan.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/tengrinews.kz</t>
+          <t>https://cdn.brandfetch.io/tengrinews.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/centralmedia24.kz</t>
+          <t>https://cdn.brandfetch.io/centralmedia24.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logos.hunter.io/orda.kz</t>
+          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/srrb.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/srrb.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/apni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tvkinoradio.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tvkinoradio.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/politnavigator.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/politnavigator.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bloknot.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bloknot.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/delovoymir.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/delovoymir.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business-magazine.online?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/business-magazine.online?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/garant.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/garant.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/prophotos.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/prophotos.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/peopletalk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/peopletalk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/versia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/versia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/infox.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/infox.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/samag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/samag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/itweek.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/itweek.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/1sept.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/1sept.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/finversia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/finversia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mir24.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mir24.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/7days.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/7days.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fedpress.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fedpress.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/securitylab.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/securitylab.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/osnmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/osnmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/snob.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/snob.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/comnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/comnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tproger.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tproger.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/cnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/iz.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/iz.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sport-express.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sport-express.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newdaynews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/newdaynews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gazetametro.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gazetametro.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/5-tv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/5-tv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/strategyjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/strategyjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/retailer.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/retailer.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aif.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aif.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vedomosti.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vedomosti.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ng.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ng.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/business.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kom-dir.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kom-dir.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/glavbukh.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/glavbukh.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/26-2.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/26-2.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/buhsoft.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/buhsoft.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pro-personal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/pro-personal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kdelo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kdelo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tass.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tass.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vm.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vm.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/news.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/news.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/profile.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/profile.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/oilcapital.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/oilcapital.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business-gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/business-gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ko.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ko.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/popmech.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/popmech.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/svpressa.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/svpressa.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ridus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ridus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/utro.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/utro.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kleo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kleo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newizv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/newizv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rosbalt.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/rosbalt.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/monocle.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/monocle.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rg.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/rg.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/runews24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/runews24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/angi.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/angi.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/naked-science.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/naked-science.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/globalcio.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/globalcio.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesstory.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businesstory.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ict-online.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ict-online.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/logirus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/logirus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/24gadget.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/24gadget.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/marieclaire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/marieclaire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/3dnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/3dnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/servernews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/servernews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/new-retail.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/new-retail.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nakanune.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nakanune.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/telecomdaily.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/telecomdaily.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bigpicture.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bigpicture.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kommersant.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kommersant.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eadaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/eadaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sostav.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sostav.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ura.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ura.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/seonews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/seonews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/likeni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/likeni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/life.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/life.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportmk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sportmk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/omanhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/omanhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/avtovzglyad.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/avtovzglyad.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ohotniki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ohotniki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mperspektiva.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mperspektiva.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautyhack.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/beautyhack.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/forbes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/forbes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/stroygaz.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/stroygaz.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/regnum.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/regnum.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/topcor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/topcor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sfera.fm?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sfera.fm?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/brl.mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/brl.mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/novate.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/novate.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautycarteblanche.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/beautycarteblanche.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vokrugsveta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vokrugsveta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/oman.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/oman.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/day.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/day.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thegirl.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thegirl.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/starhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/starhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/parents.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/parents.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mydecor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mydecor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/doctorpiter.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/doctorpiter.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/the-day.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/the-day.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/maximonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/maximonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/psychologies.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/psychologies.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fashiontime.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fashiontime.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/oane.ws?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/oane.ws?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/terrnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/terrnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kadara.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kadara.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/monavista.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/monavista.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vestnik.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vestnik.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nvspost.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nvspost.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/spb.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/spb.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/belarus.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/belarus.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/—?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/—?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/news-24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/news-24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smi24.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/smi24.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/obzor-gazet.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/obzor-gazet.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/allmosnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/allmosnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/promgoverment.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/promgoverment.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hotrs.su?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/hotrs.su?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mirwiki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mirwiki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/news-bank.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/news-bank.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/frequentflyers.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/frequentflyers.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/adindex.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/adindex.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/artagmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/artagmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sport24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sport24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/prufy.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/prufy.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/schoolotzyv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/schoolotzyv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moneytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/moneytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/english.pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/english.pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/medpulse.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/medpulse.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsinfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/newsinfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/politonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/politonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/greatlove.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/greatlove.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/yoki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/yoki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ecosever.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ecosever.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nationaljournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nationaljournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rusday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/rusday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/electorat.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/electorat.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mostimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mostimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pora.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/pora.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/glavtema.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/glavtema.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/prbn.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/prbn.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bigness.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bigness.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/militarytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/militarytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fizcultprivet.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fizcultprivet.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/poplawok.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/poplawok.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/autokolonka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/autokolonka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/repairshome.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/repairshome.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailyshow.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dailyshow.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/missus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/missus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bigcaucasus.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bigcaucasus.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/georgiatimes.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/georgiatimes.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aviation21.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aviation21.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/isguru.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/isguru.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/asninfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/asninfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/78.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/78.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thevoicemag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thevoicemag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moskvichmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/moskvichmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/rbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moslenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/moslenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kapital.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kapital.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lsm.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lsm.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsmaker.md?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/newsmaker.md?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/akipress.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/akipress.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/24.kg?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/24.kg?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/noi.md?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/noi.md?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/uzdaily.uz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/uzdaily.uz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inform.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/inform.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/remedium.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/remedium.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/medvestnik.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/medvestnik.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/incrussia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/incrussia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apptractor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/apptractor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/investfuture.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/investfuture.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/onliner.by?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/onliner.by?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bits.media?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bits.media?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/telegraf.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/telegraf.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/liter.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/liter.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dcjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dcjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/telecombloger.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/telecombloger.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/urbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/urbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/haqqin.az?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/haqqin.az?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mosregion.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mosregion.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sila-rf.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sila-rf.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sibmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sibmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ladys.media?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ladys.media?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/socialinform.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/socialinform.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/myeconomy.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/myeconomy.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ecopravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ecopravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/medzdrav.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/medzdrav.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/today.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/today.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautyhunter.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/beautyhunter.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/informator.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/informator.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/itechua.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/itechua.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mignews.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mignews.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/it-world.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/it-world.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gazeta.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gazeta.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/homebusinessmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/homebusinessmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/miamiherald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/miamiherald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kansascity.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kansascity.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/brainzmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/brainzmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/latinpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/latinpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/jpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thewestnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thewestnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vinnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vinnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fxstreet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fxstreet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inc.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/inc.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/computing.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/computing.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/crn.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/crn.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/intlbm.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/intlbm.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/adexchanger.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/adexchanger.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thedrum.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thedrum.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/globalbankingandfinance.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/globalbankingandfinance.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/financedigest.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/financedigest.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fastcompany.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fastcompany.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technologymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/technologymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aimagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aimagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesschief.eu?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businesschief.eu?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/housingwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/housingwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/paymentscardsandmobile.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/paymentscardsandmobile.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitalconnectmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/digitalconnectmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/healthcarebusinesstoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/healthcarebusinesstoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digiday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/digiday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aitimejournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aitimejournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/geekextreme.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/geekextreme.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coingape.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/coingape.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/arabianbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/arabianbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesstechnet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businesstechnet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techstacy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techstacy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/europeanbusinessreview.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/europeanbusinessreview.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/educationtechnologyinsights.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/educationtechnologyinsights.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitaljournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/digitaljournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ealthybyte.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ealthybyte.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techinasia.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techinasia.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/siliconcanals.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/siliconcanals.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bizfortune.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bizfortune.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ciobulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ciobulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/abcmoney.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/abcmoney.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceo-review.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ceo-review.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/corporatevision-news.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/corporatevision-news.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/startupsmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/startupsmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lux-life.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lux-life.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/build-review.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/build-review.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smenews.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/smenews.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ghpnews.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ghpnews.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/acquisition-international.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/acquisition-international.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ealthandfinance.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ealthandfinance.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eubusinessnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/eubusinessnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meamarkets.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/meamarkets.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apacinsider.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/apacinsider.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coventryobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/coventryobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bromsgrovestandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bromsgrovestandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/droitwichstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/droitwichstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eveshamobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/eveshamobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kidderminsterstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kidderminsterstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/leamingtonobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/leamingtonobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/malvernobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/malvernobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/redditchstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/redditchstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rugbyobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/rugbyobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/solihullobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/solihullobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/stratfordobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/stratfordobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/orcesterobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/orcesterobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/richmond.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/richmond.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fredericksburg.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fredericksburg.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/roanoke.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/roanoke.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsadvance.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/newsadvance.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailyprogress.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dailyprogress.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/heraldcourier.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/heraldcourier.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/martinsvillebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/martinsvillebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsvirginian.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/newsvirginian.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thefranklinnewspost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thefranklinnewspost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/godanriver.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/godanriver.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/starexponent.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/starexponent.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smithmountainlake.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/smithmountainlake.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/swvatoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/swvatoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/naludamagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/naludamagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tech-critter.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tech-critter.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nasilemaktech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nasilemaktech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/myeverydaytech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/myeverydaytech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessfostermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businessfostermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business-money.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/business-money.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesscloud.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businesscloud.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gritdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gritdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thesiliconreview.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thesiliconreview.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thestreet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thestreet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thedefiant.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thedefiant.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smartechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/smartechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meditechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/meditechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/financialtechtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/financialtechtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/blocktelegraph.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/blocktelegraph.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/transittomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/transittomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/highnetworthmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/highnetworthmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pharmatechnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/pharmatechnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurylamag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxurylamag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurymiamimag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxurymiamimag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lawnewsday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lawnewsday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gametechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gametechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ealthtechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ealthtechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportstechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sportstechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meditechwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/meditechwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coinreviewnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/coinreviewnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/innotechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/innotechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/csq.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/csq.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techfundingnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techfundingnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/millennialmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/millennialmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/deccanherald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/deccanherald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/amazingarchitecture.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/amazingarchitecture.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/healthworkscollective.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/healthworkscollective.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/goodmenproject.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/goodmenproject.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gilmorehealth.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gilmorehealth.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/papermag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/papermag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bust.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bust.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/villagevoice.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/villagevoice.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/irvineweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/irvineweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/marinatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/marinatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thecharlotteweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thecharlotteweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theleadernews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/theleadernews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fortbendstar.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fortbendstar.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lakerlutznews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lakerlutznews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/laweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/laweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ocweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ocweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inbuzzer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/inbuzzer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessmole.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businessmole.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/instrumentalfx.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/instrumentalfx.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fadmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fadmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eraveyou.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/eraveyou.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportsgossip.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sportsgossip.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportsmedia101.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sportsmedia101.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bostonsportsextra.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bostonsportsextra.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fangsbites.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fangsbites.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/alltechmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/alltechmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/architectureartdesigns.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/architectureartdesigns.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceotodaymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ceotodaymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/insidermonkey.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/insidermonkey.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/securityonline.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/securityonline.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/securityexpress.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/securityexpress.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meterpreter.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/meterpreter.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techiexpert.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techiexpert.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/iplocation.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/iplocation.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/opsmatters.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/opsmatters.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesshonor.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businesshonor.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hometownstation.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/hometownstation.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/latintimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/latintimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techloy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techloy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/americancraftbeer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/americancraftbeer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beerconnoisseur.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/beerconnoisseur.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/porchdrinking.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/porchdrinking.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mantelligence.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mantelligence.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/brulosophy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/brulosophy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ashingtonbeerblog.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ashingtonbeerblog.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/breweriesinpa.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/breweriesinpa.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sandiegobeer.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sandiegobeer.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/livemusicblog.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/livemusicblog.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mybeerbuzz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/mybeerbuzz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/timesla.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/timesla.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gearrice.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gearrice.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inkl.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/inkl.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nyweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nyweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/artistweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/artistweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceoweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ceoweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/atlwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/atlwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thechicagojournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thechicagojournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/emonthlynews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/emonthlynews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lawire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lawire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautyscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/beautyscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londonlovesproperty.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/londonlovesproperty.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londonlovestech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/londonlovestech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nimvo.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nimvo.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/chaospin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/chaospin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/malemodelscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/malemodelscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thebusinesswomanmedia.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thebusinesswomanmedia.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techbullion.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techbullion.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moneyinc.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/moneyinc.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londonlovesbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/londonlovesbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bmmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bmmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/designscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/designscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/entrepreneurhandbook.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/entrepreneurhandbook.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/notorious-mag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/notorious-mag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thelondoneconomic.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thelondoneconomic.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techstartups.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techstartups.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/swaggermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/swaggermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aijourn.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aijourn.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/financefeeds.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/financefeeds.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sciencetimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sciencetimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/itechpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/itechpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/plainenglish.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/plainenglish.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techround.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techround.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eureporter.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/eureporter.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/allwomenstalk.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/allwomenstalk.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/u.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/u.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/esternjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/esternjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techworm.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techworm.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ibtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ibtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theubj.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/theubj.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/archiscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/archiscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/largest.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/largest.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailycivil.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dailycivil.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tidtiltech.dk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tidtiltech.dk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/asianatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/asianatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/musicraiser.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/musicraiser.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/utilizewindows.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/utilizewindows.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thetvjunkies.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thetvjunkies.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tu.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tu.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/networthrant.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/networthrant.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jewelbeat.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/jewelbeat.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/desksgram.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/desksgram.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vxchnge.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/vxchnge.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/liberalco.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/liberalco.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kiwibox.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kiwibox.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ebsta.me?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ebsta.me?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techktimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techktimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/koreaittimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/koreaittimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/breakingac.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/breakingac.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/maryberryrecipes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/maryberryrecipes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londontime.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/londontime.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theluxurylifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/theluxurylifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurylifestylemag.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxurylifestylemag.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurialifestyle.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxurialifestyle.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/spacedaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/spacedaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/racinecountyeye.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/racinecountyeye.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/timesofisrael.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/timesofisrael.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hardreset.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/hardreset.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/imei.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/imei.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/applesn.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/applesn.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/radaronline.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/radaronline.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/okmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/okmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/onderwall.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/onderwall.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/knewz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/knewz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/frontpagedetectives.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/frontpagedetectives.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/omensgolfjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/omensgolfjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/morninghoney.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/morninghoney.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailycoin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/dailycoin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bestforandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bestforandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/esthawaiitoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/esthawaiitoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/midweek.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/midweek.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hawaiitribune-herald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/hawaiitribune-herald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thegardenisland.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/thegardenisland.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/staradvertiser.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/staradvertiser.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ustimesnow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ustimesnow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/homecrux.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/homecrux.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/modelifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/modelifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aiworldtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aiworldtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitalconvey.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/digitalconvey.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/trillmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/trillmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessoutstanders.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businessoutstanders.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/metapress.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/metapress.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/geeky-gadgets.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/geeky-gadgets.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gizchina.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gizchina.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coinprwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/coinprwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/psbios.me?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/psbios.me?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/timebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/timebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cyberpress.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/cyberpress.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gbhackers.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gbhackers.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cybersecuritynews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/cybersecuritynews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/analyticsinsight.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/analyticsinsight.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/secureblitz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/secureblitz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/talkandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/talkandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technology.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/technology.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kalilinuxtutorials.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/kalilinuxtutorials.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/startup.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/startup.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fontsarena.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fontsarena.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/applegazette.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/applegazette.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bonjouridee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bonjouridee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hardwaresecrets.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/hardwaresecrets.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fontmirror.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/fontmirror.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technochops.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/technochops.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/socialnewsdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/socialnewsdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cssbasics.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/cssbasics.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tubetorial.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tubetorial.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apps.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/apps.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/paktales.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/paktales.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/только?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/только?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technoroll.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/technoroll.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techstrange.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techstrange.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techrado.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techrado.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35801,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/travellingforbusiness.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/travellingforbusiness.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35873,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/evpowered.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/evpowered.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/electrichome.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/electrichome.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/propertyportfolioinvestor.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/propertyportfolioinvestor.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techzeel.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techzeel.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/allinsider.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/allinsider.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36305,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportzbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sportzbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36377,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nextluxury.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/nextluxury.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/stepbystepbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/stepbystepbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36521,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jt.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/jt.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36593,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/blueandgreentomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/blueandgreentomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techspotty.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techspotty.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aboutchromebooks.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/aboutchromebooks.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitaledge.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/digitaledge.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/connectioncafe.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/connectioncafe.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tabletmonkeys.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tabletmonkeys.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/quantumrun.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/quantumrun.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gadgetfreeks.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/gadgetfreeks.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hatsontech.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/hatsontech.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/voddler.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/voddler.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/citybiz.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/citybiz.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/insiderpaper.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/insiderpaper.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37457,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/onlinebizbooster.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/onlinebizbooster.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessandpower.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businessandpower.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37601,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/solidsmack.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/solidsmack.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37673,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jguru.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/jguru.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/alltechbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/alltechbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/baycitizen.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/baycitizen.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/silicon?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/silicon?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/triphippies.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/triphippies.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38105,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ecommercefastlane.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ecommercefastlane.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/netizensreport.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/netizensreport.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/startup?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/startup?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/guruhitech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/guruhitech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/britishwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/britishwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/investing.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/investing.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/the-tech-trend.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/the-tech-trend.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38609,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/arrington-worldwide.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/arrington-worldwide.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/archeyes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/archeyes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38753,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportswane.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/sportswane.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techwalls.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/techwalls.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38897,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lawbhoomi.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/lawbhoomi.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38969,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessnewsthisweek.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/businessnewsthisweek.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/guardian.ng?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/guardian.ng?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londondaily.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/londondaily.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/london-post.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/london-post.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/omenontopp.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/omenontopp.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/impactwealth.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/impactwealth.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/africa.businessinsider.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/africa.businessinsider.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39473,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/measurescopez.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/measurescopez.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ukbusinesstimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ukbusinesstimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londoninsider.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/londoninsider.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ibusiness.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/ibusiness.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theluxauthority.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/theluxauthority.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/congress.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/congress.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bitzuma.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/bitzuma.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39977,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/asiapresswire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/asiapresswire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/grazia.si?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/grazia.si?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxuo.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/luxuo.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40193,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/glamour.bg?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/glamour.bg?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitalbusiness.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/digitalbusiness.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/zakon.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/zakon.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40490,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/informburo.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/informburo.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rasdaily.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/rasdaily.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/caravan.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/caravan.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tengrinews.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/tengrinews.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/centralmedia24.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/centralmedia24.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/domain/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/srrb.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/srrb.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/apni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/apni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tvkinoradio.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tvkinoradio.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/politnavigator.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/politnavigator.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bloknot.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bloknot.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/delovoymir.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/delovoymir.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/business-magazine.online?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/business-magazine.online?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/garant.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/garant.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/prophotos.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/prophotos.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/peopletalk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/peopletalk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/versia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/versia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/infox.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/infox.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/samag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/samag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/itweek.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/itweek.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/1sept.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/1sept.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/finversia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/finversia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mir24.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mir24.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/7days.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/7days.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fedpress.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fedpress.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/securitylab.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/securitylab.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/osnmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/osnmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/snob.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/snob.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/comnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/comnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tproger.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tproger.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/cnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/cnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/iz.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/iz.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sport-express.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sport-express.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/newdaynews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/newdaynews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gazetametro.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gazetametro.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/5-tv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/5-tv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/strategyjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/strategyjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/retailer.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/retailer.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aif.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aif.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vedomosti.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vedomosti.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ng.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ng.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/business.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/business.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kom-dir.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kom-dir.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/glavbukh.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/glavbukh.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/26-2.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/26-2.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/buhsoft.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/buhsoft.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/pro-personal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/pro-personal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kdelo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kdelo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tass.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tass.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vm.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vm.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/news.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/news.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/profile.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/profile.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/oilcapital.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/oilcapital.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/business-gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/business-gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ko.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ko.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/popmech.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/popmech.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/svpressa.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/svpressa.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ridus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ridus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/utro.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/utro.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kleo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kleo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/newizv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/newizv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/rosbalt.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/rosbalt.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/monocle.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/monocle.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/rg.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/rg.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/runews24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/runews24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/angi.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/angi.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/naked-science.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/naked-science.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/globalcio.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/globalcio.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businesstory.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businesstory.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ict-online.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ict-online.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/logirus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/logirus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/24gadget.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/24gadget.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/marieclaire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/marieclaire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/3dnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/3dnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/servernews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/servernews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/new-retail.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/new-retail.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nakanune.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nakanune.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/telecomdaily.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/telecomdaily.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bigpicture.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bigpicture.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kommersant.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kommersant.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/eadaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/eadaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sostav.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sostav.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ura.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ura.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/seonews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/seonews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/likeni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/likeni.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/life.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/life.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sportmk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sportmk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/omanhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/omanhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/avtovzglyad.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/avtovzglyad.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ohotniki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ohotniki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mperspektiva.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mperspektiva.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/beautyhack.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/beautyhack.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/forbes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/forbes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/stroygaz.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/stroygaz.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/regnum.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/regnum.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/topcor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/topcor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sfera.fm?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sfera.fm?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/brl.mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/brl.mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/novate.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/novate.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/beautycarteblanche.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/beautycarteblanche.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vokrugsveta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vokrugsveta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/oman.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/oman.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/day.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/day.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thegirl.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thegirl.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/starhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/starhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/parents.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/parents.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mydecor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mydecor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/doctorpiter.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/doctorpiter.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/the-day.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/the-day.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/maximonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/maximonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/psychologies.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/psychologies.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fashiontime.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fashiontime.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/oane.ws?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/oane.ws?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/terrnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/terrnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kadara.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kadara.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/monavista.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/monavista.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vestnik.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vestnik.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nvspost.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nvspost.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/spb.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/spb.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/belarus.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/belarus.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/—?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/—?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/news-24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/news-24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/smi24.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/smi24.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/obzor-gazet.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/obzor-gazet.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/allmosnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/allmosnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/promgoverment.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/promgoverment.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/hotrs.su?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/hotrs.su?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mirwiki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mirwiki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/news-bank.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/news-bank.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/frequentflyers.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/frequentflyers.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/adindex.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/adindex.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/artagmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/artagmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sport24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sport24.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/prufy.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/prufy.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/schoolotzyv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/schoolotzyv.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/moneytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/moneytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/english.pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/english.pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/medpulse.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/medpulse.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/newsinfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/newsinfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/politonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/politonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/greatlove.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/greatlove.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/yoki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/yoki.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ecosever.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ecosever.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nationaljournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nationaljournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/rusday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/rusday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/electorat.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/electorat.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mostimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mostimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/pora.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/pora.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/glavtema.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/glavtema.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/prbn.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/prbn.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bigness.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bigness.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/militarytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/militarytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fizcultprivet.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fizcultprivet.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/poplawok.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/poplawok.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/autokolonka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/autokolonka.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/repairshome.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/repairshome.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dailyshow.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dailyshow.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/missus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/missus.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bigcaucasus.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bigcaucasus.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/georgiatimes.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/georgiatimes.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aviation21.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aviation21.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/isguru.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/isguru.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/asninfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/asninfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/78.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/78.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thevoicemag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thevoicemag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/moskvichmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/moskvichmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/rbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/rbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/moslenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/moslenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kapital.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kapital.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lsm.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lsm.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/newsmaker.md?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/newsmaker.md?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/akipress.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/akipress.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/24.kg?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/24.kg?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/noi.md?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/noi.md?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/uzdaily.uz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/uzdaily.uz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/inform.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/inform.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/remedium.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/remedium.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/medvestnik.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/medvestnik.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/incrussia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/incrussia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/apptractor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/apptractor.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/investfuture.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/investfuture.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/onliner.by?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/onliner.by?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bits.media?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bits.media?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/telegraf.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/telegraf.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/liter.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/liter.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dcjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dcjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/telecombloger.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/telecombloger.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/urbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/urbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/haqqin.az?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/haqqin.az?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mosregion.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mosregion.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sila-rf.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sila-rf.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sibmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sibmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ladys.media?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ladys.media?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/socialinform.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/socialinform.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/myeconomy.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/myeconomy.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ecopravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ecopravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/medzdrav.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/medzdrav.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/today.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/today.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/beautyhunter.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/beautyhunter.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/informator.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/informator.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/itechua.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/itechua.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mignews.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mignews.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/it-world.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/it-world.ru?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gazeta.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gazeta.ua?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/homebusinessmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/homebusinessmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/miamiherald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/miamiherald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kansascity.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kansascity.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/brainzmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/brainzmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/latinpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/latinpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/jpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/jpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thewestnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thewestnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vinnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vinnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fxstreet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fxstreet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/inc.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/inc.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/computing.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/computing.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/crn.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/crn.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/intlbm.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/intlbm.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/adexchanger.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/adexchanger.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thedrum.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thedrum.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/globalbankingandfinance.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/globalbankingandfinance.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/financedigest.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/financedigest.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fastcompany.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fastcompany.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/technologymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/technologymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aimagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aimagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businesschief.eu?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businesschief.eu?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/housingwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/housingwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/paymentscardsandmobile.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/paymentscardsandmobile.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/digitalconnectmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/digitalconnectmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/healthcarebusinesstoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/healthcarebusinesstoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/digiday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/digiday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aitimejournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aitimejournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/geekextreme.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/geekextreme.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/coingape.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/coingape.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/arabianbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/arabianbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businesstechnet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businesstechnet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techstacy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techstacy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/europeanbusinessreview.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/europeanbusinessreview.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/educationtechnologyinsights.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/educationtechnologyinsights.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/digitaljournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/digitaljournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ealthybyte.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ealthybyte.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techinasia.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techinasia.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/siliconcanals.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/siliconcanals.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bizfortune.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bizfortune.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ciobulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ciobulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/abcmoney.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/abcmoney.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ceo-review.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ceo-review.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/corporatevision-news.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/corporatevision-news.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/startupsmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/startupsmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lux-life.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lux-life.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/build-review.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/build-review.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/smenews.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/smenews.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ghpnews.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ghpnews.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/acquisition-international.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/acquisition-international.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ealthandfinance.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ealthandfinance.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/eubusinessnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/eubusinessnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/meamarkets.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/meamarkets.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/apacinsider.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/apacinsider.digital?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/coventryobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/coventryobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bromsgrovestandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bromsgrovestandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/droitwichstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/droitwichstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/eveshamobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/eveshamobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kidderminsterstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kidderminsterstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/leamingtonobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/leamingtonobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/malvernobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/malvernobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/redditchstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/redditchstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/rugbyobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/rugbyobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/solihullobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/solihullobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/stratfordobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/stratfordobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/orcesterobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/orcesterobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/richmond.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/richmond.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fredericksburg.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fredericksburg.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/roanoke.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/roanoke.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/newsadvance.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/newsadvance.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dailyprogress.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dailyprogress.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/heraldcourier.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/heraldcourier.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/martinsvillebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/martinsvillebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/newsvirginian.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/newsvirginian.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thefranklinnewspost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thefranklinnewspost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/godanriver.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/godanriver.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/starexponent.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/starexponent.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/smithmountainlake.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/smithmountainlake.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/swvatoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/swvatoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/naludamagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/naludamagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tech-critter.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tech-critter.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nasilemaktech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nasilemaktech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/myeverydaytech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/myeverydaytech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businessfostermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businessfostermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/business-money.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/business-money.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businesscloud.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businesscloud.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gritdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gritdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thesiliconreview.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thesiliconreview.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thestreet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thestreet.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thedefiant.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thedefiant.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/smartechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/smartechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/meditechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/meditechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/financialtechtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/financialtechtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/blocktelegraph.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/blocktelegraph.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/transittomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/transittomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/highnetworthmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/highnetworthmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/pharmatechnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/pharmatechnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxurylamag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxurylamag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxurymiamimag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxurymiamimag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lawnewsday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lawnewsday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gametechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gametechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ealthtechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ealthtechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sportstechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sportstechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/meditechwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/meditechwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/coinreviewnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/coinreviewnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/innotechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/innotechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/csq.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/csq.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techfundingnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techfundingnews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/millennialmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/millennialmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/deccanherald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/deccanherald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/amazingarchitecture.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/amazingarchitecture.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/healthworkscollective.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/healthworkscollective.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/goodmenproject.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/goodmenproject.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gilmorehealth.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gilmorehealth.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/papermag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/papermag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bust.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bust.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/villagevoice.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/villagevoice.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/irvineweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/irvineweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/marinatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/marinatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thecharlotteweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thecharlotteweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/theleadernews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/theleadernews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fortbendstar.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fortbendstar.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lakerlutznews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lakerlutznews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/laweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/laweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ocweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ocweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/inbuzzer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/inbuzzer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businessmole.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businessmole.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/instrumentalfx.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/instrumentalfx.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fadmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fadmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/eraveyou.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/eraveyou.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sportsgossip.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sportsgossip.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sportsmedia101.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sportsmedia101.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bostonsportsextra.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bostonsportsextra.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fangsbites.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fangsbites.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/alltechmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/alltechmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/architectureartdesigns.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/architectureartdesigns.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ceotodaymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ceotodaymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/insidermonkey.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/insidermonkey.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/securityonline.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/securityonline.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/securityexpress.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/securityexpress.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/meterpreter.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/meterpreter.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techiexpert.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techiexpert.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/iplocation.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/iplocation.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/opsmatters.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/opsmatters.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businesshonor.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businesshonor.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/hometownstation.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/hometownstation.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/latintimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/latintimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techloy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techloy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/americancraftbeer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/americancraftbeer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/beerconnoisseur.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/beerconnoisseur.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/porchdrinking.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/porchdrinking.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mantelligence.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mantelligence.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/brulosophy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/brulosophy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ashingtonbeerblog.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ashingtonbeerblog.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/breweriesinpa.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/breweriesinpa.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sandiegobeer.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sandiegobeer.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/livemusicblog.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/livemusicblog.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/mybeerbuzz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/mybeerbuzz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/timesla.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/timesla.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gearrice.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gearrice.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/inkl.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/inkl.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nyweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nyweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/artistweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/artistweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ceoweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ceoweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/atlwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/atlwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thechicagojournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thechicagojournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/emonthlynews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/emonthlynews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lawire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lawire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/beautyscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/beautyscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/londonlovesproperty.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/londonlovesproperty.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/londonlovestech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/londonlovestech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nimvo.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nimvo.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/chaospin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/chaospin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/malemodelscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/malemodelscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thebusinesswomanmedia.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thebusinesswomanmedia.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techbullion.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techbullion.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/moneyinc.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/moneyinc.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/londonlovesbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/londonlovesbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bmmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bmmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/designscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/designscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/entrepreneurhandbook.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/entrepreneurhandbook.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/notorious-mag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/notorious-mag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thelondoneconomic.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thelondoneconomic.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techstartups.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techstartups.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/swaggermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/swaggermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aijourn.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aijourn.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/financefeeds.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/financefeeds.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sciencetimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sciencetimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/itechpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/itechpost.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/plainenglish.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/plainenglish.io?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techround.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techround.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/eureporter.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/eureporter.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/allwomenstalk.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/allwomenstalk.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/u.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/u.today?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/esternjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/esternjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techworm.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techworm.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ibtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ibtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/theubj.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/theubj.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/archiscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/archiscene.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/largest.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/largest.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dailycivil.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dailycivil.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tidtiltech.dk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tidtiltech.dk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/asianatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/asianatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/musicraiser.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/musicraiser.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/utilizewindows.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/utilizewindows.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thetvjunkies.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thetvjunkies.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tu.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tu.tv?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/networthrant.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/networthrant.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/jewelbeat.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/jewelbeat.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/desksgram.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/desksgram.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/vxchnge.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/vxchnge.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/liberalco.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/liberalco.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kiwibox.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kiwibox.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ebsta.me?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ebsta.me?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techktimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techktimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/koreaittimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/koreaittimes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/breakingac.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/breakingac.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/maryberryrecipes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/maryberryrecipes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/londontime.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/londontime.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/theluxurylifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/theluxurylifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxurylifestylemag.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxurylifestylemag.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxurialifestyle.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxurialifestyle.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/spacedaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/spacedaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/racinecountyeye.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/racinecountyeye.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/timesofisrael.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/timesofisrael.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/hardreset.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/hardreset.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/imei.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/imei.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/applesn.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/applesn.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/radaronline.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/radaronline.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/okmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/okmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/onderwall.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/onderwall.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/knewz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/knewz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/frontpagedetectives.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/frontpagedetectives.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/omensgolfjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/omensgolfjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/morninghoney.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/morninghoney.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/dailycoin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/dailycoin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bestforandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bestforandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/esthawaiitoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/esthawaiitoday.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/midweek.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/midweek.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/hawaiitribune-herald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/hawaiitribune-herald.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/thegardenisland.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/thegardenisland.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/staradvertiser.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/staradvertiser.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ustimesnow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ustimesnow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/homecrux.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/homecrux.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/modelifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/modelifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aiworldtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aiworldtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/digitalconvey.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/digitalconvey.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/trillmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/trillmag.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businessoutstanders.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businessoutstanders.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/metapress.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/metapress.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/geeky-gadgets.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/geeky-gadgets.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gizchina.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gizchina.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/coinprwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/coinprwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/psbios.me?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/psbios.me?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/timebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/timebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/cyberpress.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/cyberpress.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gbhackers.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gbhackers.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/cybersecuritynews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/cybersecuritynews.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/analyticsinsight.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/analyticsinsight.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/secureblitz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/secureblitz.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/talkandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/talkandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/technology.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/technology.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/kalilinuxtutorials.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/kalilinuxtutorials.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/startup.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/startup.info?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fontsarena.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fontsarena.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/applegazette.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/applegazette.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bonjouridee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bonjouridee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/hardwaresecrets.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/hardwaresecrets.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/fontmirror.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/fontmirror.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/technochops.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/technochops.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/socialnewsdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/socialnewsdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/cssbasics.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/cssbasics.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tubetorial.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tubetorial.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/apps.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/apps.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/paktales.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/paktales.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/только?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/только?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/technoroll.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/technoroll.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techstrange.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techstrange.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techrado.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techrado.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35801,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/travellingforbusiness.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/travellingforbusiness.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35873,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/evpowered.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/evpowered.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/electrichome.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/electrichome.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/propertyportfolioinvestor.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/propertyportfolioinvestor.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techzeel.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techzeel.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/allinsider.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/allinsider.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36305,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sportzbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sportzbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36377,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/nextluxury.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/nextluxury.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/stepbystepbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/stepbystepbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36521,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/jt.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/jt.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36593,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/blueandgreentomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/blueandgreentomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techspotty.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techspotty.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/aboutchromebooks.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/aboutchromebooks.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/digitaledge.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/digitaledge.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/connectioncafe.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/connectioncafe.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tabletmonkeys.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tabletmonkeys.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/quantumrun.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/quantumrun.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/gadgetfreeks.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/gadgetfreeks.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/hatsontech.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/hatsontech.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/voddler.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/voddler.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/citybiz.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/citybiz.co?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/insiderpaper.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/insiderpaper.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37457,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/onlinebizbooster.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/onlinebizbooster.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businessandpower.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businessandpower.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37601,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/solidsmack.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/solidsmack.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37673,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/jguru.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/jguru.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/alltechbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/alltechbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/baycitizen.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/baycitizen.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/silicon?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/silicon?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/triphippies.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/triphippies.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38105,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ecommercefastlane.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ecommercefastlane.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/netizensreport.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/netizensreport.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/startup?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/startup?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/guruhitech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/guruhitech.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/britishwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/britishwire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/investing.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/investing.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/the-tech-trend.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/the-tech-trend.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38609,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/arrington-worldwide.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/arrington-worldwide.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/archeyes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/archeyes.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38753,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/sportswane.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/sportswane.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/techwalls.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/techwalls.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38897,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/lawbhoomi.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/lawbhoomi.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38969,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/businessnewsthisweek.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/businessnewsthisweek.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/guardian.ng?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/guardian.ng?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/londondaily.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/londondaily.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/london-post.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/london-post.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/omenontopp.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/omenontopp.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/impactwealth.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/impactwealth.org?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/africa.businessinsider.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/africa.businessinsider.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39473,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/measurescopez.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/measurescopez.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ukbusinesstimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ukbusinesstimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/londoninsider.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/londoninsider.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/ibusiness.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/ibusiness.news?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/theluxauthority.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/theluxauthority.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/congress.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/congress.net?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/bitzuma.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/bitzuma.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39977,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/asiapresswire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/asiapresswire.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/grazia.si?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/grazia.si?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/luxuo.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/luxuo.com?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40193,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/glamour.bg?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/glamour.bg?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/digitalbusiness.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/digitalbusiness.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/zakon.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/zakon.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40490,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/informburo.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/informburo.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/rasdaily.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/rasdaily.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/caravan.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/caravan.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/tengrinews.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/tengrinews.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/centralmedia24.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/centralmedia24.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/domain/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/srrb.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/srrb.ru</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/apni.ru</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tvkinoradio.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tvkinoradio.ru</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/politnavigator.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/politnavigator.net</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bloknot.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bloknot.ru</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/delovoymir.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/delovoymir.biz</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business-magazine.online?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/business-magazine.online</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/garant.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/garant.ru</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/prophotos.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/prophotos.ru</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/peopletalk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/peopletalk.ru</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/versia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/versia.ru</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/infox.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/infox.ru</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/samag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/samag.ru</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/itweek.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/itweek.ru</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/1sept.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/1sept.ru</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/finversia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/finversia.ru</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mir24.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mir24.tv</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lenta.ru</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/7days.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/7days.ru</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fedpress.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fedpress.ru</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/securitylab.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/securitylab.ru</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/osnmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/osnmedia.ru</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/snob.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/snob.ru</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/comnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/comnews.ru</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tproger.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tproger.ru</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/cnews.ru</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/iz.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/iz.ru</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sport-express.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sport-express.ru</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newdaynews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/newdaynews.ru</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gazetametro.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gazetametro.ru</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/5-tv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/5-tv.ru</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dk.ru</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/strategyjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/strategyjournal.ru</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/retailer.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/retailer.ru</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mk.ru</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aif.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aif.ru</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vedomosti.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vedomosti.ru</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ng.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ng.ru</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/business.ru</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kom-dir.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kom-dir.ru</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/glavbukh.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/glavbukh.ru</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/26-2.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/26-2.ru</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/buhsoft.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/buhsoft.ru</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pro-personal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/pro-personal.ru</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kdelo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kdelo.ru</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tass.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tass.ru</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vm.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vm.ru</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/news.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/news.ru</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/profile.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/profile.ru</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/oilcapital.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/oilcapital.ru</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business-gazeta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/business-gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ko.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ko.ru</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dp.ru</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/popmech.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/popmech.ru</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/svpressa.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/svpressa.ru</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ridus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ridus.ru</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dni.ru</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/utro.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/utro.ru</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kleo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kleo.ru</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newizv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/newizv.ru</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rosbalt.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/rosbalt.ru</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/monocle.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/monocle.ru</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rg.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/rg.ru</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/runews24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/runews24.ru</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/angi.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/angi.ru</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/naked-science.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/naked-science.ru</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/globalcio.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/globalcio.ru</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesstory.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businesstory.ru</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ict-online.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ict-online.ru</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/logirus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/logirus.ru</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/24gadget.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/24gadget.ru</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/marieclaire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/marieclaire.com</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/3dnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/3dnews.ru</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/servernews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/servernews.ru</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/new-retail.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/new-retail.ru</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nakanune.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nakanune.ru</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/telecomdaily.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/telecomdaily.ru</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bigpicture.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bigpicture.ru</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kommersant.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kommersant.ru</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eadaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/eadaily.com</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sostav.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sostav.ru</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ura.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ura.news</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/seonews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/seonews.ru</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/likeni.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/likeni.ru</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/life.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/life.ru</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportmk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sportmk.ru</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/omanhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/omanhit.ru</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/avtovzglyad.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/avtovzglyad.ru</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ohotniki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ohotniki.ru</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mperspektiva.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mperspektiva.ru</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautyhack.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/beautyhack.ru</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sobaka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/forbes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/forbes.ru</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/stroygaz.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/stroygaz.ru</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/regnum.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/regnum.ru</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/topcor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/topcor.ru</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sfera.fm?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sfera.fm</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/brl.mk.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/brl.mk.ru</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/novate.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/novate.ru</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautycarteblanche.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/beautycarteblanche.ru</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vokrug.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vokrugsveta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vokrugsveta.ru</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/oman.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/oman.ru</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/day.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/day.ru</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thegirl.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thegirl.ru</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/starhit.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/starhit.ru</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/parents.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/parents.ru</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mydecor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mydecor.ru</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/doctorpiter.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/doctorpiter.ru</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/the-day.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/the-day.ru</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/maximonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/maximonline.ru</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/psychologies.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/psychologies.ru</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fashiontime.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fashiontime.ru</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/oane.ws?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/oane.ws</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/terrnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/terrnews.com</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kadara.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kadara.ru</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/monavista.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/monavista.ru</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vestnik.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vestnik.net</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nvspost.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nvspost.ru</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/spb.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/spb.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/belarus.kp.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/belarus.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/—?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/—</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/news-24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/news-24.ru</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smi24.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/smi24.news</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/obzor-gazet.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/obzor-gazet.ru</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/allmosnews.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/allmosnews.ru</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/promgoverment.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/promgoverment.ru</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hotrs.su?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/hotrs.su</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mirwiki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mirwiki.ru</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/news-bank.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/news-bank.ru</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/frequentflyers.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/frequentflyers.ru</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/adindex.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/adindex.ru</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/artagmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/artagmag.ru</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sport24.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sport24.ru</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/prufy.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/prufy.ru</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/schoolotzyv.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/schoolotzyv.ru</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moneytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/moneytimes.ru</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/english.pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/english.pravda.ru</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/medpulse.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/medpulse.ru</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsinfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/newsinfo.ru</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/politonline.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/politonline.ru</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/greatlove.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/greatlove.ru</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/yoki.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/yoki.ru</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ecosever.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ecosever.ru</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nationaljournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nationaljournal.ru</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rusday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/rusday.com</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/electorat.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/electorat.info</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mostimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mostimes.com</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pora.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/pora.ru</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/glavtema.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/glavtema.ru</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/prbn.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/prbn.ru</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bigness.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bigness.ru</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/militarytimes.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/militarytimes.ru</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fizcultprivet.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fizcultprivet.ru</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/poplawok.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/poplawok.ru</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/autokolonka.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/autokolonka.ru</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/repairshome.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/repairshome.ru</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailyshow.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dailyshow.ru</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/missus.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/missus.ru</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bigcaucasus.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bigcaucasus.com</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/georgiatimes.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/georgiatimes.info</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/pravda.ru</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aviation21.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aviation21.ru</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/isguru.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/isguru.ru</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/asninfo.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/asninfo.ru</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/78.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/78.ru</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thevoicemag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thevoicemag.ru</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moskvichmag.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/moskvichmag.ru</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/rbc.ru</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moslenta.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/moslenta.ru</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kapital.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kapital.kz</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lsm.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lsm.kz</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsmaker.md?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/newsmaker.md</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/akipress.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/akipress.org</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/24.kg?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/24.kg</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/noi.md?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/noi.md</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/uzdaily.uz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/uzdaily.uz</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inform.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/inform.kz</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/remedium.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/remedium.ru</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/medvestnik.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/medvestnik.ru</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/incrussia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/incrussia.ru</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apptractor.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/apptractor.ru</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/investfuture.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/investfuture.ru</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/onliner.by?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/onliner.by</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bits.media?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bits.media</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/telegraf.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/telegraf.news</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/liter.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/liter.kz</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/orda.kz</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dcjournal.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dcjournal.ru</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/telecombloger.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/telecombloger.ru</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/urbc.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/urbc.ru</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/haqqin.az?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/haqqin.az</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mosregion.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mosregion.info</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sila-rf.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sila-rf.ru</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sibmedia.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sibmedia.ru</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ladys.media?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ladys.media</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/socialinform.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/socialinform.ru</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/myeconomy.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/myeconomy.ru</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ecopravda.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ecopravda.ru</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/medzdrav.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/medzdrav.info</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/today.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/today.ua</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautyhunter.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/beautyhunter.ru</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/informator.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/informator.ua</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/itechua.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/itechua.com</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mignews.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mignews.ua</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/it-world.ru?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/it-world.ru</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gazeta.ua?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gazeta.ua</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/homebusinessmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/homebusinessmag.com</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/miamiherald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/miamiherald.com</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kansascity.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kansascity.com</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techtimes.com</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/brainzmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/brainzmagazine.com</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/latinpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/latinpost.com</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/jpost.com</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thewestnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thewestnews.com</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vinnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vinnews.com</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fxstreet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fxstreet.com</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inc.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/inc.com</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/computing.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/computing.co.uk</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/crn.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/crn.com</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/intlbm.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/intlbm.com</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/adexchanger.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/adexchanger.com</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thedrum.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thedrum.com</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/globalbankingandfinance.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/globalbankingandfinance.com</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/financedigest.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/financedigest.com</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fastcompany.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fastcompany.com</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technologymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/technologymagazine.com</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aimagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aimagazine.com</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesschief.eu?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businesschief.eu</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/housingwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/housingwire.com</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/paymentscardsandmobile.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/paymentscardsandmobile.com</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitalconnectmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/digitalconnectmag.com</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/healthcarebusinesstoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/healthcarebusinesstoday.com</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digiday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/digiday.com</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aitimejournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aitimejournal.com</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/geekextreme.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/geekextreme.com</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coingape.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/coingape.com</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/arabianbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/arabianbusiness.com</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesstechnet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businesstechnet.com</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techstacy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techstacy.com</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/europeanbusinessreview.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/europeanbusinessreview.com</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/educationtechnologyinsights.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/educationtechnologyinsights.com</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitaljournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/digitaljournal.com</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ealthybyte.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ealthybyte.com</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techinasia.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techinasia.com</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/siliconcanals.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/siliconcanals.com</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bizfortune.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bizfortune.com</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ciobulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ciobulletin.com</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/abcmoney.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/abcmoney.co.uk</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceo-review.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ceo-review.com</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/corporatevision-news.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/corporatevision-news.com</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/startupsmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/startupsmagazine.co.uk</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lux-life.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lux-life.digital</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/build-review.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/build-review.com</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smenews.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/smenews.digital</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ghpnews.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ghpnews.digital</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/acquisition-international.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/acquisition-international.com</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ealthandfinance.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ealthandfinance.digital</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eubusinessnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/eubusinessnews.com</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meamarkets.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/meamarkets.digital</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apacinsider.digital?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/apacinsider.digital</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coventryobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/coventryobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bromsgrovestandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bromsgrovestandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/droitwichstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/droitwichstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eveshamobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/eveshamobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kidderminsterstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kidderminsterstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/leamingtonobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/leamingtonobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/malvernobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/malvernobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/redditchstandard.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/redditchstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rugbyobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/rugbyobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/solihullobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/solihullobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/stratfordobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/stratfordobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/orcesterobserver.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/orcesterobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/richmond.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/richmond.com</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fredericksburg.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fredericksburg.com</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/roanoke.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/roanoke.com</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsadvance.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/newsadvance.com</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailyprogress.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dailyprogress.com</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/heraldcourier.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/heraldcourier.com</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/martinsvillebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/martinsvillebulletin.com</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/newsvirginian.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/newsvirginian.com</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thefranklinnewspost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thefranklinnewspost.com</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/godanriver.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/godanriver.com</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/starexponent.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/starexponent.com</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smithmountainlake.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/smithmountainlake.com</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/swvatoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/swvatoday.com</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/naludamagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/naludamagazine.com</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tech-critter.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tech-critter.com</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nasilemaktech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nasilemaktech.com</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/myeverydaytech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/myeverydaytech.com</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessfostermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businessfostermagazine.com</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/business-money.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/business-money.com</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesscloud.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businesscloud.co.uk</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gritdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gritdaily.com</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thesiliconreview.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thesiliconreview.com</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thestreet.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thestreet.com</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thedefiant.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thedefiant.io</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/smartechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/smartechdaily.com</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meditechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/meditechtoday.com</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/financialtechtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/financialtechtimes.com</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/blocktelegraph.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/blocktelegraph.io</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/transittomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/transittomorrow.com</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/highnetworthmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/highnetworthmag.com</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/pharmatechnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/pharmatechnews.com</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurylamag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxurylamag.com</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurymiamimag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxurymiamimag.com</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lawnewsday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lawnewsday.com</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gametechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gametechdaily.com</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ealthtechdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ealthtechdaily.com</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportstechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sportstechtoday.com</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meditechwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/meditechwire.com</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coinreviewnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/coinreviewnews.com</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/innotechtoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/innotechtoday.com</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/csq.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/csq.com</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techfundingnews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techfundingnews.com</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/millennialmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/millennialmagazine.com</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/deccanherald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/deccanherald.com</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/amazingarchitecture.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/amazingarchitecture.com</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/healthworkscollective.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/healthworkscollective.com</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/goodmenproject.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/goodmenproject.com</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gilmorehealth.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gilmorehealth.com</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/papermag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/papermag.com</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bust.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bust.com</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/villagevoice.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/villagevoice.com</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/irvineweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/irvineweekly.com</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/marinatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/marinatimes.com</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thecharlotteweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thecharlotteweekly.com</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theleadernews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/theleadernews.com</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fortbendstar.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fortbendstar.com</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lakerlutznews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lakerlutznews.com</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/laweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/laweekly.com</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ocweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ocweekly.com</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inbuzzer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/inbuzzer.com</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessmole.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businessmole.com</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/instrumentalfx.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/instrumentalfx.co</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fadmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fadmagazine.com</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eraveyou.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/eraveyou.com</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportsgossip.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sportsgossip.com</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportsmedia101.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sportsmedia101.com</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bostonsportsextra.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bostonsportsextra.com</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fangsbites.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fangsbites.com</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/alltechmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/alltechmagazine.com</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/architectureartdesigns.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/architectureartdesigns.com</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceotodaymagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ceotodaymagazine.com</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/insidermonkey.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/insidermonkey.com</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/securityonline.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/securityonline.info</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/securityexpress.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/securityexpress.info</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/meterpreter.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/meterpreter.org</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techiexpert.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techiexpert.com</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxuryhousingtrends.com</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/iplocation.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/iplocation.net</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/opsmatters.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/opsmatters.com</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businesshonor.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businesshonor.com</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/highways.today</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hometownstation.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/hometownstation.com</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/latintimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/latintimes.com</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techloy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techloy.com</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/americancraftbeer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/americancraftbeer.com</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beerconnoisseur.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/beerconnoisseur.com</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/porchdrinking.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/porchdrinking.com</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mantelligence.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mantelligence.com</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/brulosophy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/brulosophy.com</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ashingtonbeerblog.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ashingtonbeerblog.com</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/breweriesinpa.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/breweriesinpa.com</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sandiegobeer.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sandiegobeer.news</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/livemusicblog.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/livemusicblog.com</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/mybeerbuzz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/mybeerbuzz.com</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/highways.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/highways.today</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxuryhousingtrends.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxuryhousingtrends.com</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/timesla.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/timesla.com</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gearrice.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gearrice.com</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/inkl.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/inkl.com</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nyweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nyweekly.com</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/artistweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/artistweekly.com</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceoweekly.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ceoweekly.com</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/atlwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/atlwire.com</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thechicagojournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thechicagojournal.com</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/emonthlynews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/emonthlynews.com</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lawire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lawire.com</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/beautyscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/beautyscene.net</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londonlovesproperty.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/londonlovesproperty.com</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londonlovestech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/londonlovestech.com</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nimvo.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nimvo.com</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/chaospin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/chaospin.com</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/malemodelscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/malemodelscene.net</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thebusinesswomanmedia.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thebusinesswomanmedia.com</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techbullion.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techbullion.com</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fashionuer.com</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/moneyinc.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/moneyinc.com</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londonlovesbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/londonlovesbusiness.com</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bmmagazine.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bmmagazine.co.uk</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/designscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/designscene.net</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fashionuer.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fashionuer.com</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/entrepreneurhandbook.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/entrepreneurhandbook.co.uk</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/notorious-mag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/notorious-mag.com</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thelondoneconomic.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thelondoneconomic.com</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techstartups.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techstartups.com</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/swaggermagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/swaggermagazine.com</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aijourn.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aijourn.com</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/financefeeds.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/financefeeds.com</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sciencetimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sciencetimes.com</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/itechpost.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/itechpost.com</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/plainenglish.io?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/plainenglish.io</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techround.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techround.co.uk</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/eureporter.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/eureporter.co</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dataconomy.com</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ceoworld.biz</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/allwomenstalk.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/allwomenstalk.com</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ceoworld.biz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ceoworld.biz</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/u.today?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/u.today</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/esternjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/esternjournal.com</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techworm.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techworm.net</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ibtimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ibtimes.com</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theubj.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/theubj.com</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/archiscene.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/archiscene.net</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/largest.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/largest.org</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailycivil.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dailycivil.com</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tidtiltech.dk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tidtiltech.dk</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/asianatimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/asianatimes.com</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/musicraiser.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/musicraiser.net</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/utilizewindows.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/utilizewindows.com</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thetvjunkies.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thetvjunkies.com</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tu.tv?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tu.tv</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/networthrant.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/networthrant.com</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jewelbeat.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/jewelbeat.com</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/desksgram.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/desksgram.net</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/vxchnge.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/vxchnge.com</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/liberalco.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/liberalco.org</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kiwibox.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kiwibox.com</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ebsta.me?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ebsta.me</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techktimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techktimes.co.uk</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/koreaittimes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/koreaittimes.com</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/breakingac.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/breakingac.com</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/maryberryrecipes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/maryberryrecipes.co.uk</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londontime.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/londontime.co</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theluxurylifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/theluxurylifestylemagazine.com</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurylifestylemag.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxurylifestylemag.co.uk</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxurialifestyle.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxurialifestyle.com</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/spacedaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/spacedaily.com</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/racinecountyeye.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/racinecountyeye.com</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/timesofisrael.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/timesofisrael.com</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hardreset.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/hardreset.info</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/imei.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/imei.info</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/applesn.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/applesn.info</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dataconomy.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dataconomy.com</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/radaronline.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/radaronline.com</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/okmagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/okmagazine.com</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/onderwall.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/onderwall.com</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/knewz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/knewz.com</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/frontpagedetectives.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/frontpagedetectives.com</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/omensgolfjournal.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/omensgolfjournal.com</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/morninghoney.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/morninghoney.com</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/dailycoin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/dailycoin.com</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bestforandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bestforandroid.com</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/esthawaiitoday.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/esthawaiitoday.com</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/midweek.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/midweek.com</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hawaiitribune-herald.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/hawaiitribune-herald.com</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/thegardenisland.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/thegardenisland.com</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/staradvertiser.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/staradvertiser.com</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ustimesnow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ustimesnow.com</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/homecrux.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/homecrux.com</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/modelifestylemagazine.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/modelifestylemagazine.com</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aiworldtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aiworldtoday.net</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitalconvey.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/digitalconvey.com</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/trillmag.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/trillmag.com</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessoutstanders.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businessoutstanders.com</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/metapress.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/metapress.com</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/geeky-gadgets.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/geeky-gadgets.com</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gizchina.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gizchina.com</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/coinprwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/coinprwire.com</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/psbios.me?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/psbios.me</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/timebulletin.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/timebulletin.com</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cyberpress.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/cyberpress.org</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gbhackers.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gbhackers.com</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cybersecuritynews.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/cybersecuritynews.com</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/analyticsinsight.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/analyticsinsight.net</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/secureblitz.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/secureblitz.com</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techdee.com</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/talkandroid.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/talkandroid.com</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technology.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/technology.org</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/kalilinuxtutorials.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/kalilinuxtutorials.com</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/startup.info?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/startup.info</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fontsarena.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fontsarena.com</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/applegazette.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/applegazette.com</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bonjouridee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bonjouridee.com</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hardwaresecrets.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/hardwaresecrets.com</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/fontmirror.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/fontmirror.com</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technochops.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/technochops.com</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/socialnewsdaily.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/socialnewsdaily.com</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/cssbasics.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/cssbasics.com</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tubetorial.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tubetorial.com</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/apps.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/apps.uk</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/paktales.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/paktales.com</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/только?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/только</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techdee.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techdee.com</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/technoroll.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/technoroll.org</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techstrange.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techstrange.com</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techrado.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techrado.com</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35801,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/travellingforbusiness.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/travellingforbusiness.co.uk</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35873,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/evpowered.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/evpowered.co.uk</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/electrichome.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/electrichome.uk</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/propertyportfolioinvestor.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/propertyportfolioinvestor.co.uk</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techzeel.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techzeel.net</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/learningtoday.net</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/allinsider.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/allinsider.net</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36305,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportzbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sportzbuzz.net</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36377,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/nextluxury.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/nextluxury.com</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/stepbystepbusiness.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/stepbystepbusiness.com</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36521,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jt.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/jt.org</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36593,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/blueandgreentomorrow.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/blueandgreentomorrow.com</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techspotty.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techspotty.com</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/aboutchromebooks.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/aboutchromebooks.com</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitaledge.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/digitaledge.org</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/connectioncafe.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/connectioncafe.com</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tabletmonkeys.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tabletmonkeys.com</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/quantumrun.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/quantumrun.com</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/gadgetfreeks.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/gadgetfreeks.com</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/hatsontech.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/hatsontech.co.uk</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/voddler.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/voddler.co.uk</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/citybiz.co?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/citybiz.co</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/insiderpaper.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/insiderpaper.com</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37457,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/onlinebizbooster.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/onlinebizbooster.net</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessandpower.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businessandpower.com</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37601,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/solidsmack.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/solidsmack.com</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37673,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/jguru.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/jguru.com</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/alltechbuzz.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/alltechbuzz.net</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/baycitizen.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/baycitizen.org</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/silicon?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/silicon</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/triphippies.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/triphippies.com</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/learningtoday.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/learningtoday.net</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38105,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ecommercefastlane.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ecommercefastlane.com</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/netizensreport.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/netizensreport.com</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/startup?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/startup</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/guruhitech.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/guruhitech.com</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/britishwire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/britishwire.com</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/investing.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/investing.com</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/the-tech-trend.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/the-tech-trend.com</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38609,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/arrington-worldwide.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/arrington-worldwide.co.uk</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/archeyes.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/archeyes.com</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38753,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/sportswane.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/sportswane.com</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/techwalls.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/techwalls.com</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38897,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/lawbhoomi.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/lawbhoomi.com</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38969,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/businessnewsthisweek.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/businessnewsthisweek.com</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/guardian.ng?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/guardian.ng</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londondaily.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/londondaily.news</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/london-post.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/london-post.co.uk</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/omenontopp.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/omenontopp.com</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/impactwealth.org?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/impactwealth.org</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/africa.businessinsider.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/africa.businessinsider.com</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39473,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/measurescopez.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/measurescopez.com</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ukbusinesstimes.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ukbusinesstimes.co.uk</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/londoninsider.co.uk?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/londoninsider.co.uk</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/ibusiness.news?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/ibusiness.news</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/theluxauthority.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/theluxauthority.com</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/congress.net?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/congress.net</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/bitzuma.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/bitzuma.com</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39977,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/asiapresswire.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/asiapresswire.com</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/grazia.si?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/grazia.si</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/luxuo.com?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/luxuo.com</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40193,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/glamour.bg?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/glamour.bg</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/digitalbusiness.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/digitalbusiness.kz</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/zakon.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/zakon.kz</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40490,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/informburo.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/informburo.kz</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/rasdaily.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/rasdaily.kz</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/caravan.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/caravan.kz</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/tengrinews.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/tengrinews.kz</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/centralmedia24.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/centralmedia24.kz</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://cdn.brandfetch.io/orda.kz?c=1idF1Fj7KzTGO52xbKN</t>
+          <t>https://logo.debounce.com/orda.kz</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/srrb.ru</t>
+          <t>https://machibo.github.io/-/?d=srrb.ru</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/apni.ru</t>
+          <t>https://machibo.github.io/-/?d=apni.ru</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tvkinoradio.ru</t>
+          <t>https://machibo.github.io/-/?d=tvkinoradio.ru</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/politnavigator.net</t>
+          <t>https://machibo.github.io/-/?d=politnavigator.net</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bloknot.ru</t>
+          <t>https://machibo.github.io/-/?d=bloknot.ru</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/delovoymir.biz</t>
+          <t>https://machibo.github.io/-/?d=delovoymir.biz</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/business-magazine.online</t>
+          <t>https://machibo.github.io/-/?d=business-magazine.online</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/garant.ru</t>
+          <t>https://machibo.github.io/-/?d=garant.ru</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/prophotos.ru</t>
+          <t>https://machibo.github.io/-/?d=prophotos.ru</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/peopletalk.ru</t>
+          <t>https://machibo.github.io/-/?d=peopletalk.ru</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/versia.ru</t>
+          <t>https://machibo.github.io/-/?d=versia.ru</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/infox.ru</t>
+          <t>https://machibo.github.io/-/?d=infox.ru</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/samag.ru</t>
+          <t>https://machibo.github.io/-/?d=samag.ru</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/itweek.ru</t>
+          <t>https://machibo.github.io/-/?d=itweek.ru</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/1sept.ru</t>
+          <t>https://machibo.github.io/-/?d=1sept.ru</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/finversia.ru</t>
+          <t>https://machibo.github.io/-/?d=finversia.ru</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mir24.tv</t>
+          <t>https://machibo.github.io/-/?d=mir24.tv</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lenta.ru</t>
+          <t>https://machibo.github.io/-/?d=lenta.ru</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/7days.ru</t>
+          <t>https://machibo.github.io/-/?d=7days.ru</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vokrug.tv</t>
+          <t>https://machibo.github.io/-/?d=vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fedpress.ru</t>
+          <t>https://machibo.github.io/-/?d=fedpress.ru</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/securitylab.ru</t>
+          <t>https://machibo.github.io/-/?d=securitylab.ru</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/osnmedia.ru</t>
+          <t>https://machibo.github.io/-/?d=osnmedia.ru</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/snob.ru</t>
+          <t>https://machibo.github.io/-/?d=snob.ru</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/comnews.ru</t>
+          <t>https://machibo.github.io/-/?d=comnews.ru</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tproger.ru</t>
+          <t>https://machibo.github.io/-/?d=tproger.ru</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/cnews.ru</t>
+          <t>https://machibo.github.io/-/?d=cnews.ru</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/iz.ru</t>
+          <t>https://machibo.github.io/-/?d=iz.ru</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sport-express.ru</t>
+          <t>https://machibo.github.io/-/?d=sport-express.ru</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/newdaynews.ru</t>
+          <t>https://machibo.github.io/-/?d=newdaynews.ru</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gazetametro.ru</t>
+          <t>https://machibo.github.io/-/?d=gazetametro.ru</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/5-tv.ru</t>
+          <t>https://machibo.github.io/-/?d=5-tv.ru</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dk.ru</t>
+          <t>https://machibo.github.io/-/?d=dk.ru</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/strategyjournal.ru</t>
+          <t>https://machibo.github.io/-/?d=strategyjournal.ru</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/retailer.ru</t>
+          <t>https://machibo.github.io/-/?d=retailer.ru</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mk.ru</t>
+          <t>https://machibo.github.io/-/?d=mk.ru</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aif.ru</t>
+          <t>https://machibo.github.io/-/?d=aif.ru</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vedomosti.ru</t>
+          <t>https://machibo.github.io/-/?d=vedomosti.ru</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ng.ru</t>
+          <t>https://machibo.github.io/-/?d=ng.ru</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/business.ru</t>
+          <t>https://machibo.github.io/-/?d=business.ru</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kom-dir.ru</t>
+          <t>https://machibo.github.io/-/?d=kom-dir.ru</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/glavbukh.ru</t>
+          <t>https://machibo.github.io/-/?d=glavbukh.ru</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/26-2.ru</t>
+          <t>https://machibo.github.io/-/?d=26-2.ru</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/buhsoft.ru</t>
+          <t>https://machibo.github.io/-/?d=buhsoft.ru</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/pro-personal.ru</t>
+          <t>https://machibo.github.io/-/?d=pro-personal.ru</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kdelo.ru</t>
+          <t>https://machibo.github.io/-/?d=kdelo.ru</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tass.ru</t>
+          <t>https://machibo.github.io/-/?d=tass.ru</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gazeta.ru</t>
+          <t>https://machibo.github.io/-/?d=gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vm.ru</t>
+          <t>https://machibo.github.io/-/?d=vm.ru</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/news.ru</t>
+          <t>https://machibo.github.io/-/?d=news.ru</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/profile.ru</t>
+          <t>https://machibo.github.io/-/?d=profile.ru</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/oilcapital.ru</t>
+          <t>https://machibo.github.io/-/?d=oilcapital.ru</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/business-gazeta.ru</t>
+          <t>https://machibo.github.io/-/?d=business-gazeta.ru</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ko.ru</t>
+          <t>https://machibo.github.io/-/?d=ko.ru</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dp.ru</t>
+          <t>https://machibo.github.io/-/?d=dp.ru</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/popmech.ru</t>
+          <t>https://machibo.github.io/-/?d=popmech.ru</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/svpressa.ru</t>
+          <t>https://machibo.github.io/-/?d=svpressa.ru</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ridus.ru</t>
+          <t>https://machibo.github.io/-/?d=ridus.ru</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dni.ru</t>
+          <t>https://machibo.github.io/-/?d=dni.ru</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/utro.ru</t>
+          <t>https://machibo.github.io/-/?d=utro.ru</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kleo.ru</t>
+          <t>https://machibo.github.io/-/?d=kleo.ru</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/newizv.ru</t>
+          <t>https://machibo.github.io/-/?d=newizv.ru</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/rosbalt.ru</t>
+          <t>https://machibo.github.io/-/?d=rosbalt.ru</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/monocle.ru</t>
+          <t>https://machibo.github.io/-/?d=monocle.ru</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/rg.ru</t>
+          <t>https://machibo.github.io/-/?d=rg.ru</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/runews24.ru</t>
+          <t>https://machibo.github.io/-/?d=runews24.ru</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/angi.ru</t>
+          <t>https://machibo.github.io/-/?d=angi.ru</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/naked-science.ru</t>
+          <t>https://machibo.github.io/-/?d=naked-science.ru</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/globalcio.ru</t>
+          <t>https://machibo.github.io/-/?d=globalcio.ru</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businesstory.ru</t>
+          <t>https://machibo.github.io/-/?d=businesstory.ru</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ict-online.ru</t>
+          <t>https://machibo.github.io/-/?d=ict-online.ru</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/logirus.ru</t>
+          <t>https://machibo.github.io/-/?d=logirus.ru</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/24gadget.ru</t>
+          <t>https://machibo.github.io/-/?d=24gadget.ru</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/marieclaire.com</t>
+          <t>https://machibo.github.io/-/?d=marieclaire.com</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/3dnews.ru</t>
+          <t>https://machibo.github.io/-/?d=3dnews.ru</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/servernews.ru</t>
+          <t>https://machibo.github.io/-/?d=servernews.ru</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/new-retail.ru</t>
+          <t>https://machibo.github.io/-/?d=new-retail.ru</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nakanune.ru</t>
+          <t>https://machibo.github.io/-/?d=nakanune.ru</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/telecomdaily.ru</t>
+          <t>https://machibo.github.io/-/?d=telecomdaily.ru</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bigpicture.ru</t>
+          <t>https://machibo.github.io/-/?d=bigpicture.ru</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kommersant.ru</t>
+          <t>https://machibo.github.io/-/?d=kommersant.ru</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/eadaily.com</t>
+          <t>https://machibo.github.io/-/?d=eadaily.com</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sostav.ru</t>
+          <t>https://machibo.github.io/-/?d=sostav.ru</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ura.news</t>
+          <t>https://machibo.github.io/-/?d=ura.news</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/seonews.ru</t>
+          <t>https://machibo.github.io/-/?d=seonews.ru</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/likeni.ru</t>
+          <t>https://machibo.github.io/-/?d=likeni.ru</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/life.ru</t>
+          <t>https://machibo.github.io/-/?d=life.ru</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sportmk.ru</t>
+          <t>https://machibo.github.io/-/?d=sportmk.ru</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/omanhit.ru</t>
+          <t>https://machibo.github.io/-/?d=omanhit.ru</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/avtovzglyad.ru</t>
+          <t>https://machibo.github.io/-/?d=avtovzglyad.ru</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ohotniki.ru</t>
+          <t>https://machibo.github.io/-/?d=ohotniki.ru</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mperspektiva.ru</t>
+          <t>https://machibo.github.io/-/?d=mperspektiva.ru</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/beautyhack.ru</t>
+          <t>https://machibo.github.io/-/?d=beautyhack.ru</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sobaka.ru</t>
+          <t>https://machibo.github.io/-/?d=sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sobaka.ru</t>
+          <t>https://machibo.github.io/-/?d=sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sobaka.ru</t>
+          <t>https://machibo.github.io/-/?d=sobaka.ru</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/forbes.ru</t>
+          <t>https://machibo.github.io/-/?d=forbes.ru</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/stroygaz.ru</t>
+          <t>https://machibo.github.io/-/?d=stroygaz.ru</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/regnum.ru</t>
+          <t>https://machibo.github.io/-/?d=regnum.ru</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/topcor.ru</t>
+          <t>https://machibo.github.io/-/?d=topcor.ru</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sfera.fm</t>
+          <t>https://machibo.github.io/-/?d=sfera.fm</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/brl.mk.ru</t>
+          <t>https://machibo.github.io/-/?d=brl.mk.ru</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/novate.ru</t>
+          <t>https://machibo.github.io/-/?d=novate.ru</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/beautycarteblanche.ru</t>
+          <t>https://machibo.github.io/-/?d=beautycarteblanche.ru</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vokrug.tv</t>
+          <t>https://machibo.github.io/-/?d=vokrug.tv</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vokrugsveta.ru</t>
+          <t>https://machibo.github.io/-/?d=vokrugsveta.ru</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/oman.ru</t>
+          <t>https://machibo.github.io/-/?d=oman.ru</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/day.ru</t>
+          <t>https://machibo.github.io/-/?d=day.ru</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thegirl.ru</t>
+          <t>https://machibo.github.io/-/?d=thegirl.ru</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/starhit.ru</t>
+          <t>https://machibo.github.io/-/?d=starhit.ru</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/parents.ru</t>
+          <t>https://machibo.github.io/-/?d=parents.ru</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mydecor.ru</t>
+          <t>https://machibo.github.io/-/?d=mydecor.ru</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/doctorpiter.ru</t>
+          <t>https://machibo.github.io/-/?d=doctorpiter.ru</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/the-day.ru</t>
+          <t>https://machibo.github.io/-/?d=the-day.ru</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/maximonline.ru</t>
+          <t>https://machibo.github.io/-/?d=maximonline.ru</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/psychologies.ru</t>
+          <t>https://machibo.github.io/-/?d=psychologies.ru</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fashiontime.ru</t>
+          <t>https://machibo.github.io/-/?d=fashiontime.ru</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/oane.ws</t>
+          <t>https://machibo.github.io/-/?d=oane.ws</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/terrnews.com</t>
+          <t>https://machibo.github.io/-/?d=terrnews.com</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kadara.ru</t>
+          <t>https://machibo.github.io/-/?d=kadara.ru</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/monavista.ru</t>
+          <t>https://machibo.github.io/-/?d=monavista.ru</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vestnik.net</t>
+          <t>https://machibo.github.io/-/?d=vestnik.net</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nvspost.ru</t>
+          <t>https://machibo.github.io/-/?d=nvspost.ru</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/spb.kp.ru</t>
+          <t>https://machibo.github.io/-/?d=spb.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/belarus.kp.ru</t>
+          <t>https://machibo.github.io/-/?d=belarus.kp.ru</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/—</t>
+          <t>https://machibo.github.io/-/?d=—</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/news-24.ru</t>
+          <t>https://machibo.github.io/-/?d=news-24.ru</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/smi24.news</t>
+          <t>https://machibo.github.io/-/?d=smi24.news</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/obzor-gazet.ru</t>
+          <t>https://machibo.github.io/-/?d=obzor-gazet.ru</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/allmosnews.ru</t>
+          <t>https://machibo.github.io/-/?d=allmosnews.ru</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/promgoverment.ru</t>
+          <t>https://machibo.github.io/-/?d=promgoverment.ru</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/hotrs.su</t>
+          <t>https://machibo.github.io/-/?d=hotrs.su</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mirwiki.ru</t>
+          <t>https://machibo.github.io/-/?d=mirwiki.ru</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/news-bank.ru</t>
+          <t>https://machibo.github.io/-/?d=news-bank.ru</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/frequentflyers.ru</t>
+          <t>https://machibo.github.io/-/?d=frequentflyers.ru</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/adindex.ru</t>
+          <t>https://machibo.github.io/-/?d=adindex.ru</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/artagmag.ru</t>
+          <t>https://machibo.github.io/-/?d=artagmag.ru</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sport24.ru</t>
+          <t>https://machibo.github.io/-/?d=sport24.ru</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/prufy.ru</t>
+          <t>https://machibo.github.io/-/?d=prufy.ru</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/schoolotzyv.ru</t>
+          <t>https://machibo.github.io/-/?d=schoolotzyv.ru</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/moneytimes.ru</t>
+          <t>https://machibo.github.io/-/?d=moneytimes.ru</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/english.pravda.ru</t>
+          <t>https://machibo.github.io/-/?d=english.pravda.ru</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/medpulse.ru</t>
+          <t>https://machibo.github.io/-/?d=medpulse.ru</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/newsinfo.ru</t>
+          <t>https://machibo.github.io/-/?d=newsinfo.ru</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/politonline.ru</t>
+          <t>https://machibo.github.io/-/?d=politonline.ru</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/greatlove.ru</t>
+          <t>https://machibo.github.io/-/?d=greatlove.ru</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/yoki.ru</t>
+          <t>https://machibo.github.io/-/?d=yoki.ru</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ecosever.ru</t>
+          <t>https://machibo.github.io/-/?d=ecosever.ru</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nationaljournal.ru</t>
+          <t>https://machibo.github.io/-/?d=nationaljournal.ru</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/rusday.com</t>
+          <t>https://machibo.github.io/-/?d=rusday.com</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/electorat.info</t>
+          <t>https://machibo.github.io/-/?d=electorat.info</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mostimes.com</t>
+          <t>https://machibo.github.io/-/?d=mostimes.com</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/pora.ru</t>
+          <t>https://machibo.github.io/-/?d=pora.ru</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/glavtema.ru</t>
+          <t>https://machibo.github.io/-/?d=glavtema.ru</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/prbn.ru</t>
+          <t>https://machibo.github.io/-/?d=prbn.ru</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bigness.ru</t>
+          <t>https://machibo.github.io/-/?d=bigness.ru</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/militarytimes.ru</t>
+          <t>https://machibo.github.io/-/?d=militarytimes.ru</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fizcultprivet.ru</t>
+          <t>https://machibo.github.io/-/?d=fizcultprivet.ru</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/poplawok.ru</t>
+          <t>https://machibo.github.io/-/?d=poplawok.ru</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/autokolonka.ru</t>
+          <t>https://machibo.github.io/-/?d=autokolonka.ru</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/repairshome.ru</t>
+          <t>https://machibo.github.io/-/?d=repairshome.ru</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dailyshow.ru</t>
+          <t>https://machibo.github.io/-/?d=dailyshow.ru</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/missus.ru</t>
+          <t>https://machibo.github.io/-/?d=missus.ru</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bigcaucasus.com</t>
+          <t>https://machibo.github.io/-/?d=bigcaucasus.com</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/georgiatimes.info</t>
+          <t>https://machibo.github.io/-/?d=georgiatimes.info</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/pravda.ru</t>
+          <t>https://machibo.github.io/-/?d=pravda.ru</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aviation21.ru</t>
+          <t>https://machibo.github.io/-/?d=aviation21.ru</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/isguru.ru</t>
+          <t>https://machibo.github.io/-/?d=isguru.ru</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/asninfo.ru</t>
+          <t>https://machibo.github.io/-/?d=asninfo.ru</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/78.ru</t>
+          <t>https://machibo.github.io/-/?d=78.ru</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thevoicemag.ru</t>
+          <t>https://machibo.github.io/-/?d=thevoicemag.ru</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/moskvichmag.ru</t>
+          <t>https://machibo.github.io/-/?d=moskvichmag.ru</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/rbc.ru</t>
+          <t>https://machibo.github.io/-/?d=rbc.ru</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/moslenta.ru</t>
+          <t>https://machibo.github.io/-/?d=moslenta.ru</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kapital.kz</t>
+          <t>https://machibo.github.io/-/?d=kapital.kz</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lsm.kz</t>
+          <t>https://machibo.github.io/-/?d=lsm.kz</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/newsmaker.md</t>
+          <t>https://machibo.github.io/-/?d=newsmaker.md</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/akipress.org</t>
+          <t>https://machibo.github.io/-/?d=akipress.org</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/24.kg</t>
+          <t>https://machibo.github.io/-/?d=24.kg</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/noi.md</t>
+          <t>https://machibo.github.io/-/?d=noi.md</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/uzdaily.uz</t>
+          <t>https://machibo.github.io/-/?d=uzdaily.uz</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/inform.kz</t>
+          <t>https://machibo.github.io/-/?d=inform.kz</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/remedium.ru</t>
+          <t>https://machibo.github.io/-/?d=remedium.ru</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/medvestnik.ru</t>
+          <t>https://machibo.github.io/-/?d=medvestnik.ru</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/incrussia.ru</t>
+          <t>https://machibo.github.io/-/?d=incrussia.ru</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/apptractor.ru</t>
+          <t>https://machibo.github.io/-/?d=apptractor.ru</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/investfuture.ru</t>
+          <t>https://machibo.github.io/-/?d=investfuture.ru</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/onliner.by</t>
+          <t>https://machibo.github.io/-/?d=onliner.by</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bits.media</t>
+          <t>https://machibo.github.io/-/?d=bits.media</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/telegraf.news</t>
+          <t>https://machibo.github.io/-/?d=telegraf.news</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/liter.kz</t>
+          <t>https://machibo.github.io/-/?d=liter.kz</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/orda.kz</t>
+          <t>https://machibo.github.io/-/?d=orda.kz</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dcjournal.ru</t>
+          <t>https://machibo.github.io/-/?d=dcjournal.ru</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/telecombloger.ru</t>
+          <t>https://machibo.github.io/-/?d=telecombloger.ru</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/urbc.ru</t>
+          <t>https://machibo.github.io/-/?d=urbc.ru</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/haqqin.az</t>
+          <t>https://machibo.github.io/-/?d=haqqin.az</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mosregion.info</t>
+          <t>https://machibo.github.io/-/?d=mosregion.info</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sila-rf.ru</t>
+          <t>https://machibo.github.io/-/?d=sila-rf.ru</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sibmedia.ru</t>
+          <t>https://machibo.github.io/-/?d=sibmedia.ru</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ladys.media</t>
+          <t>https://machibo.github.io/-/?d=ladys.media</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/socialinform.ru</t>
+          <t>https://machibo.github.io/-/?d=socialinform.ru</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/myeconomy.ru</t>
+          <t>https://machibo.github.io/-/?d=myeconomy.ru</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ecopravda.ru</t>
+          <t>https://machibo.github.io/-/?d=ecopravda.ru</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/medzdrav.info</t>
+          <t>https://machibo.github.io/-/?d=medzdrav.info</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/today.ua</t>
+          <t>https://machibo.github.io/-/?d=today.ua</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/beautyhunter.ru</t>
+          <t>https://machibo.github.io/-/?d=beautyhunter.ru</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/informator.ua</t>
+          <t>https://machibo.github.io/-/?d=informator.ua</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/itechua.com</t>
+          <t>https://machibo.github.io/-/?d=itechua.com</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mignews.ua</t>
+          <t>https://machibo.github.io/-/?d=mignews.ua</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/it-world.ru</t>
+          <t>https://machibo.github.io/-/?d=it-world.ru</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gazeta.ua</t>
+          <t>https://machibo.github.io/-/?d=gazeta.ua</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/homebusinessmag.com</t>
+          <t>https://machibo.github.io/-/?d=homebusinessmag.com</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/miamiherald.com</t>
+          <t>https://machibo.github.io/-/?d=miamiherald.com</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kansascity.com</t>
+          <t>https://machibo.github.io/-/?d=kansascity.com</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techtimes.com</t>
+          <t>https://machibo.github.io/-/?d=techtimes.com</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/brainzmagazine.com</t>
+          <t>https://machibo.github.io/-/?d=brainzmagazine.com</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/latinpost.com</t>
+          <t>https://machibo.github.io/-/?d=latinpost.com</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/jpost.com</t>
+          <t>https://machibo.github.io/-/?d=jpost.com</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thewestnews.com</t>
+          <t>https://machibo.github.io/-/?d=thewestnews.com</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vinnews.com</t>
+          <t>https://machibo.github.io/-/?d=vinnews.com</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fxstreet.com</t>
+          <t>https://machibo.github.io/-/?d=fxstreet.com</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/inc.com</t>
+          <t>https://machibo.github.io/-/?d=inc.com</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/computing.co.uk</t>
+          <t>https://machibo.github.io/-/?d=computing.co.uk</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/crn.com</t>
+          <t>https://machibo.github.io/-/?d=crn.com</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/intlbm.com</t>
+          <t>https://machibo.github.io/-/?d=intlbm.com</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/adexchanger.com</t>
+          <t>https://machibo.github.io/-/?d=adexchanger.com</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thedrum.com</t>
+          <t>https://machibo.github.io/-/?d=thedrum.com</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/globalbankingandfinance.com</t>
+          <t>https://machibo.github.io/-/?d=globalbankingandfinance.com</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/financedigest.com</t>
+          <t>https://machibo.github.io/-/?d=financedigest.com</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fastcompany.com</t>
+          <t>https://machibo.github.io/-/?d=fastcompany.com</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/technologymagazine.com</t>
+          <t>https://machibo.github.io/-/?d=technologymagazine.com</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aimagazine.com</t>
+          <t>https://machibo.github.io/-/?d=aimagazine.com</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businesschief.eu</t>
+          <t>https://machibo.github.io/-/?d=businesschief.eu</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/housingwire.com</t>
+          <t>https://machibo.github.io/-/?d=housingwire.com</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/paymentscardsandmobile.com</t>
+          <t>https://machibo.github.io/-/?d=paymentscardsandmobile.com</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/digitalconnectmag.com</t>
+          <t>https://machibo.github.io/-/?d=digitalconnectmag.com</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/healthcarebusinesstoday.com</t>
+          <t>https://machibo.github.io/-/?d=healthcarebusinesstoday.com</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/digiday.com</t>
+          <t>https://machibo.github.io/-/?d=digiday.com</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aitimejournal.com</t>
+          <t>https://machibo.github.io/-/?d=aitimejournal.com</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/geekextreme.com</t>
+          <t>https://machibo.github.io/-/?d=geekextreme.com</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/coingape.com</t>
+          <t>https://machibo.github.io/-/?d=coingape.com</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/arabianbusiness.com</t>
+          <t>https://machibo.github.io/-/?d=arabianbusiness.com</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businesstechnet.com</t>
+          <t>https://machibo.github.io/-/?d=businesstechnet.com</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techstacy.com</t>
+          <t>https://machibo.github.io/-/?d=techstacy.com</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/europeanbusinessreview.com</t>
+          <t>https://machibo.github.io/-/?d=europeanbusinessreview.com</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/educationtechnologyinsights.com</t>
+          <t>https://machibo.github.io/-/?d=educationtechnologyinsights.com</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/digitaljournal.com</t>
+          <t>https://machibo.github.io/-/?d=digitaljournal.com</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ealthybyte.com</t>
+          <t>https://machibo.github.io/-/?d=ealthybyte.com</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techinasia.com</t>
+          <t>https://machibo.github.io/-/?d=techinasia.com</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/siliconcanals.com</t>
+          <t>https://machibo.github.io/-/?d=siliconcanals.com</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bizfortune.com</t>
+          <t>https://machibo.github.io/-/?d=bizfortune.com</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ciobulletin.com</t>
+          <t>https://machibo.github.io/-/?d=ciobulletin.com</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/abcmoney.co.uk</t>
+          <t>https://machibo.github.io/-/?d=abcmoney.co.uk</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ceo-review.com</t>
+          <t>https://machibo.github.io/-/?d=ceo-review.com</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/corporatevision-news.com</t>
+          <t>https://machibo.github.io/-/?d=corporatevision-news.com</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/startupsmagazine.co.uk</t>
+          <t>https://machibo.github.io/-/?d=startupsmagazine.co.uk</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lux-life.digital</t>
+          <t>https://machibo.github.io/-/?d=lux-life.digital</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/build-review.com</t>
+          <t>https://machibo.github.io/-/?d=build-review.com</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/smenews.digital</t>
+          <t>https://machibo.github.io/-/?d=smenews.digital</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ghpnews.digital</t>
+          <t>https://machibo.github.io/-/?d=ghpnews.digital</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/acquisition-international.com</t>
+          <t>https://machibo.github.io/-/?d=acquisition-international.com</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ealthandfinance.digital</t>
+          <t>https://machibo.github.io/-/?d=ealthandfinance.digital</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/eubusinessnews.com</t>
+          <t>https://machibo.github.io/-/?d=eubusinessnews.com</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/meamarkets.digital</t>
+          <t>https://machibo.github.io/-/?d=meamarkets.digital</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/apacinsider.digital</t>
+          <t>https://machibo.github.io/-/?d=apacinsider.digital</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/coventryobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=coventryobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bromsgrovestandard.co.uk</t>
+          <t>https://machibo.github.io/-/?d=bromsgrovestandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/droitwichstandard.co.uk</t>
+          <t>https://machibo.github.io/-/?d=droitwichstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/eveshamobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=eveshamobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kidderminsterstandard.co.uk</t>
+          <t>https://machibo.github.io/-/?d=kidderminsterstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/leamingtonobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=leamingtonobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/malvernobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=malvernobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/redditchstandard.co.uk</t>
+          <t>https://machibo.github.io/-/?d=redditchstandard.co.uk</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/rugbyobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=rugbyobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/solihullobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=solihullobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/stratfordobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=stratfordobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/orcesterobserver.co.uk</t>
+          <t>https://machibo.github.io/-/?d=orcesterobserver.co.uk</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/richmond.com</t>
+          <t>https://machibo.github.io/-/?d=richmond.com</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fredericksburg.com</t>
+          <t>https://machibo.github.io/-/?d=fredericksburg.com</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/roanoke.com</t>
+          <t>https://machibo.github.io/-/?d=roanoke.com</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/newsadvance.com</t>
+          <t>https://machibo.github.io/-/?d=newsadvance.com</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dailyprogress.com</t>
+          <t>https://machibo.github.io/-/?d=dailyprogress.com</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/heraldcourier.com</t>
+          <t>https://machibo.github.io/-/?d=heraldcourier.com</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/martinsvillebulletin.com</t>
+          <t>https://machibo.github.io/-/?d=martinsvillebulletin.com</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/newsvirginian.com</t>
+          <t>https://machibo.github.io/-/?d=newsvirginian.com</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thefranklinnewspost.com</t>
+          <t>https://machibo.github.io/-/?d=thefranklinnewspost.com</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/godanriver.com</t>
+          <t>https://machibo.github.io/-/?d=godanriver.com</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/starexponent.com</t>
+          <t>https://machibo.github.io/-/?d=starexponent.com</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/smithmountainlake.com</t>
+          <t>https://machibo.github.io/-/?d=smithmountainlake.com</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/swvatoday.com</t>
+          <t>https://machibo.github.io/-/?d=swvatoday.com</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/naludamagazine.com</t>
+          <t>https://machibo.github.io/-/?d=naludamagazine.com</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tech-critter.com</t>
+          <t>https://machibo.github.io/-/?d=tech-critter.com</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nasilemaktech.com</t>
+          <t>https://machibo.github.io/-/?d=nasilemaktech.com</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/myeverydaytech.com</t>
+          <t>https://machibo.github.io/-/?d=myeverydaytech.com</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businessfostermagazine.com</t>
+          <t>https://machibo.github.io/-/?d=businessfostermagazine.com</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/business-money.com</t>
+          <t>https://machibo.github.io/-/?d=business-money.com</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businesscloud.co.uk</t>
+          <t>https://machibo.github.io/-/?d=businesscloud.co.uk</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gritdaily.com</t>
+          <t>https://machibo.github.io/-/?d=gritdaily.com</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thesiliconreview.com</t>
+          <t>https://machibo.github.io/-/?d=thesiliconreview.com</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thestreet.com</t>
+          <t>https://machibo.github.io/-/?d=thestreet.com</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thedefiant.io</t>
+          <t>https://machibo.github.io/-/?d=thedefiant.io</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/smartechdaily.com</t>
+          <t>https://machibo.github.io/-/?d=smartechdaily.com</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/meditechtoday.com</t>
+          <t>https://machibo.github.io/-/?d=meditechtoday.com</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/financialtechtimes.com</t>
+          <t>https://machibo.github.io/-/?d=financialtechtimes.com</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/blocktelegraph.io</t>
+          <t>https://machibo.github.io/-/?d=blocktelegraph.io</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/transittomorrow.com</t>
+          <t>https://machibo.github.io/-/?d=transittomorrow.com</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/highnetworthmag.com</t>
+          <t>https://machibo.github.io/-/?d=highnetworthmag.com</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/pharmatechnews.com</t>
+          <t>https://machibo.github.io/-/?d=pharmatechnews.com</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxurylamag.com</t>
+          <t>https://machibo.github.io/-/?d=luxurylamag.com</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxurymiamimag.com</t>
+          <t>https://machibo.github.io/-/?d=luxurymiamimag.com</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lawnewsday.com</t>
+          <t>https://machibo.github.io/-/?d=lawnewsday.com</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gametechdaily.com</t>
+          <t>https://machibo.github.io/-/?d=gametechdaily.com</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ealthtechdaily.com</t>
+          <t>https://machibo.github.io/-/?d=ealthtechdaily.com</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sportstechtoday.com</t>
+          <t>https://machibo.github.io/-/?d=sportstechtoday.com</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/meditechwire.com</t>
+          <t>https://machibo.github.io/-/?d=meditechwire.com</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/coinreviewnews.com</t>
+          <t>https://machibo.github.io/-/?d=coinreviewnews.com</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/innotechtoday.com</t>
+          <t>https://machibo.github.io/-/?d=innotechtoday.com</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/csq.com</t>
+          <t>https://machibo.github.io/-/?d=csq.com</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techfundingnews.com</t>
+          <t>https://machibo.github.io/-/?d=techfundingnews.com</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/millennialmagazine.com</t>
+          <t>https://machibo.github.io/-/?d=millennialmagazine.com</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/deccanherald.com</t>
+          <t>https://machibo.github.io/-/?d=deccanherald.com</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/amazingarchitecture.com</t>
+          <t>https://machibo.github.io/-/?d=amazingarchitecture.com</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/healthworkscollective.com</t>
+          <t>https://machibo.github.io/-/?d=healthworkscollective.com</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/goodmenproject.com</t>
+          <t>https://machibo.github.io/-/?d=goodmenproject.com</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gilmorehealth.com</t>
+          <t>https://machibo.github.io/-/?d=gilmorehealth.com</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/papermag.com</t>
+          <t>https://machibo.github.io/-/?d=papermag.com</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bust.com</t>
+          <t>https://machibo.github.io/-/?d=bust.com</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/villagevoice.com</t>
+          <t>https://machibo.github.io/-/?d=villagevoice.com</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/irvineweekly.com</t>
+          <t>https://machibo.github.io/-/?d=irvineweekly.com</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/marinatimes.com</t>
+          <t>https://machibo.github.io/-/?d=marinatimes.com</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thecharlotteweekly.com</t>
+          <t>https://machibo.github.io/-/?d=thecharlotteweekly.com</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/theleadernews.com</t>
+          <t>https://machibo.github.io/-/?d=theleadernews.com</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fortbendstar.com</t>
+          <t>https://machibo.github.io/-/?d=fortbendstar.com</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lakerlutznews.com</t>
+          <t>https://machibo.github.io/-/?d=lakerlutznews.com</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/laweekly.com</t>
+          <t>https://machibo.github.io/-/?d=laweekly.com</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ocweekly.com</t>
+          <t>https://machibo.github.io/-/?d=ocweekly.com</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/inbuzzer.com</t>
+          <t>https://machibo.github.io/-/?d=inbuzzer.com</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businessmole.com</t>
+          <t>https://machibo.github.io/-/?d=businessmole.com</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/instrumentalfx.co</t>
+          <t>https://machibo.github.io/-/?d=instrumentalfx.co</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fadmagazine.com</t>
+          <t>https://machibo.github.io/-/?d=fadmagazine.com</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/eraveyou.com</t>
+          <t>https://machibo.github.io/-/?d=eraveyou.com</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sportsgossip.com</t>
+          <t>https://machibo.github.io/-/?d=sportsgossip.com</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sportsmedia101.com</t>
+          <t>https://machibo.github.io/-/?d=sportsmedia101.com</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bostonsportsextra.com</t>
+          <t>https://machibo.github.io/-/?d=bostonsportsextra.com</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fangsbites.com</t>
+          <t>https://machibo.github.io/-/?d=fangsbites.com</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/alltechmagazine.com</t>
+          <t>https://machibo.github.io/-/?d=alltechmagazine.com</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/architectureartdesigns.com</t>
+          <t>https://machibo.github.io/-/?d=architectureartdesigns.com</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ceotodaymagazine.com</t>
+          <t>https://machibo.github.io/-/?d=ceotodaymagazine.com</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/insidermonkey.com</t>
+          <t>https://machibo.github.io/-/?d=insidermonkey.com</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/securityonline.info</t>
+          <t>https://machibo.github.io/-/?d=securityonline.info</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/securityexpress.info</t>
+          <t>https://machibo.github.io/-/?d=securityexpress.info</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/meterpreter.org</t>
+          <t>https://machibo.github.io/-/?d=meterpreter.org</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techiexpert.com</t>
+          <t>https://machibo.github.io/-/?d=techiexpert.com</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxuryhousingtrends.com</t>
+          <t>https://machibo.github.io/-/?d=luxuryhousingtrends.com</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/iplocation.net</t>
+          <t>https://machibo.github.io/-/?d=iplocation.net</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/opsmatters.com</t>
+          <t>https://machibo.github.io/-/?d=opsmatters.com</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businesshonor.com</t>
+          <t>https://machibo.github.io/-/?d=businesshonor.com</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/highways.today</t>
+          <t>https://machibo.github.io/-/?d=highways.today</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/hometownstation.com</t>
+          <t>https://machibo.github.io/-/?d=hometownstation.com</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/latintimes.com</t>
+          <t>https://machibo.github.io/-/?d=latintimes.com</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techloy.com</t>
+          <t>https://machibo.github.io/-/?d=techloy.com</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/americancraftbeer.com</t>
+          <t>https://machibo.github.io/-/?d=americancraftbeer.com</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/beerconnoisseur.com</t>
+          <t>https://machibo.github.io/-/?d=beerconnoisseur.com</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/porchdrinking.com</t>
+          <t>https://machibo.github.io/-/?d=porchdrinking.com</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mantelligence.com</t>
+          <t>https://machibo.github.io/-/?d=mantelligence.com</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/brulosophy.com</t>
+          <t>https://machibo.github.io/-/?d=brulosophy.com</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ashingtonbeerblog.com</t>
+          <t>https://machibo.github.io/-/?d=ashingtonbeerblog.com</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/breweriesinpa.com</t>
+          <t>https://machibo.github.io/-/?d=breweriesinpa.com</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sandiegobeer.news</t>
+          <t>https://machibo.github.io/-/?d=sandiegobeer.news</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/livemusicblog.com</t>
+          <t>https://machibo.github.io/-/?d=livemusicblog.com</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/mybeerbuzz.com</t>
+          <t>https://machibo.github.io/-/?d=mybeerbuzz.com</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/highways.today</t>
+          <t>https://machibo.github.io/-/?d=highways.today</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxuryhousingtrends.com</t>
+          <t>https://machibo.github.io/-/?d=luxuryhousingtrends.com</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/timesla.com</t>
+          <t>https://machibo.github.io/-/?d=timesla.com</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gearrice.com</t>
+          <t>https://machibo.github.io/-/?d=gearrice.com</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/inkl.com</t>
+          <t>https://machibo.github.io/-/?d=inkl.com</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nyweekly.com</t>
+          <t>https://machibo.github.io/-/?d=nyweekly.com</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/artistweekly.com</t>
+          <t>https://machibo.github.io/-/?d=artistweekly.com</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ceoweekly.com</t>
+          <t>https://machibo.github.io/-/?d=ceoweekly.com</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/atlwire.com</t>
+          <t>https://machibo.github.io/-/?d=atlwire.com</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thechicagojournal.com</t>
+          <t>https://machibo.github.io/-/?d=thechicagojournal.com</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/emonthlynews.com</t>
+          <t>https://machibo.github.io/-/?d=emonthlynews.com</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lawire.com</t>
+          <t>https://machibo.github.io/-/?d=lawire.com</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/beautyscene.net</t>
+          <t>https://machibo.github.io/-/?d=beautyscene.net</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/londonlovesproperty.com</t>
+          <t>https://machibo.github.io/-/?d=londonlovesproperty.com</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/londonlovestech.com</t>
+          <t>https://machibo.github.io/-/?d=londonlovestech.com</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nimvo.com</t>
+          <t>https://machibo.github.io/-/?d=nimvo.com</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/chaospin.com</t>
+          <t>https://machibo.github.io/-/?d=chaospin.com</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/malemodelscene.net</t>
+          <t>https://machibo.github.io/-/?d=malemodelscene.net</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thebusinesswomanmedia.com</t>
+          <t>https://machibo.github.io/-/?d=thebusinesswomanmedia.com</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techbullion.com</t>
+          <t>https://machibo.github.io/-/?d=techbullion.com</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fashionuer.com</t>
+          <t>https://machibo.github.io/-/?d=fashionuer.com</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/moneyinc.com</t>
+          <t>https://machibo.github.io/-/?d=moneyinc.com</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/londonlovesbusiness.com</t>
+          <t>https://machibo.github.io/-/?d=londonlovesbusiness.com</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bmmagazine.co.uk</t>
+          <t>https://machibo.github.io/-/?d=bmmagazine.co.uk</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/designscene.net</t>
+          <t>https://machibo.github.io/-/?d=designscene.net</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fashionuer.com</t>
+          <t>https://machibo.github.io/-/?d=fashionuer.com</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/entrepreneurhandbook.co.uk</t>
+          <t>https://machibo.github.io/-/?d=entrepreneurhandbook.co.uk</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/notorious-mag.com</t>
+          <t>https://machibo.github.io/-/?d=notorious-mag.com</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thelondoneconomic.com</t>
+          <t>https://machibo.github.io/-/?d=thelondoneconomic.com</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techstartups.com</t>
+          <t>https://machibo.github.io/-/?d=techstartups.com</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/swaggermagazine.com</t>
+          <t>https://machibo.github.io/-/?d=swaggermagazine.com</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aijourn.com</t>
+          <t>https://machibo.github.io/-/?d=aijourn.com</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/financefeeds.com</t>
+          <t>https://machibo.github.io/-/?d=financefeeds.com</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sciencetimes.com</t>
+          <t>https://machibo.github.io/-/?d=sciencetimes.com</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/itechpost.com</t>
+          <t>https://machibo.github.io/-/?d=itechpost.com</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/plainenglish.io</t>
+          <t>https://machibo.github.io/-/?d=plainenglish.io</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techround.co.uk</t>
+          <t>https://machibo.github.io/-/?d=techround.co.uk</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/eureporter.co</t>
+          <t>https://machibo.github.io/-/?d=eureporter.co</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dataconomy.com</t>
+          <t>https://machibo.github.io/-/?d=dataconomy.com</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ceoworld.biz</t>
+          <t>https://machibo.github.io/-/?d=ceoworld.biz</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/allwomenstalk.com</t>
+          <t>https://machibo.github.io/-/?d=allwomenstalk.com</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ceoworld.biz</t>
+          <t>https://machibo.github.io/-/?d=ceoworld.biz</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/u.today</t>
+          <t>https://machibo.github.io/-/?d=u.today</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/esternjournal.com</t>
+          <t>https://machibo.github.io/-/?d=esternjournal.com</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techworm.net</t>
+          <t>https://machibo.github.io/-/?d=techworm.net</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ibtimes.com</t>
+          <t>https://machibo.github.io/-/?d=ibtimes.com</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/theubj.com</t>
+          <t>https://machibo.github.io/-/?d=theubj.com</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/archiscene.net</t>
+          <t>https://machibo.github.io/-/?d=archiscene.net</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/largest.org</t>
+          <t>https://machibo.github.io/-/?d=largest.org</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dailycivil.com</t>
+          <t>https://machibo.github.io/-/?d=dailycivil.com</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tidtiltech.dk</t>
+          <t>https://machibo.github.io/-/?d=tidtiltech.dk</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/asianatimes.com</t>
+          <t>https://machibo.github.io/-/?d=asianatimes.com</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/musicraiser.net</t>
+          <t>https://machibo.github.io/-/?d=musicraiser.net</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/utilizewindows.com</t>
+          <t>https://machibo.github.io/-/?d=utilizewindows.com</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thetvjunkies.com</t>
+          <t>https://machibo.github.io/-/?d=thetvjunkies.com</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tu.tv</t>
+          <t>https://machibo.github.io/-/?d=tu.tv</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/networthrant.com</t>
+          <t>https://machibo.github.io/-/?d=networthrant.com</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/jewelbeat.com</t>
+          <t>https://machibo.github.io/-/?d=jewelbeat.com</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/desksgram.net</t>
+          <t>https://machibo.github.io/-/?d=desksgram.net</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/vxchnge.com</t>
+          <t>https://machibo.github.io/-/?d=vxchnge.com</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/liberalco.org</t>
+          <t>https://machibo.github.io/-/?d=liberalco.org</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kiwibox.com</t>
+          <t>https://machibo.github.io/-/?d=kiwibox.com</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ebsta.me</t>
+          <t>https://machibo.github.io/-/?d=ebsta.me</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techktimes.co.uk</t>
+          <t>https://machibo.github.io/-/?d=techktimes.co.uk</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/koreaittimes.com</t>
+          <t>https://machibo.github.io/-/?d=koreaittimes.com</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/breakingac.com</t>
+          <t>https://machibo.github.io/-/?d=breakingac.com</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/maryberryrecipes.co.uk</t>
+          <t>https://machibo.github.io/-/?d=maryberryrecipes.co.uk</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/londontime.co</t>
+          <t>https://machibo.github.io/-/?d=londontime.co</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/theluxurylifestylemagazine.com</t>
+          <t>https://machibo.github.io/-/?d=theluxurylifestylemagazine.com</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxurylifestylemag.co.uk</t>
+          <t>https://machibo.github.io/-/?d=luxurylifestylemag.co.uk</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxurialifestyle.com</t>
+          <t>https://machibo.github.io/-/?d=luxurialifestyle.com</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/spacedaily.com</t>
+          <t>https://machibo.github.io/-/?d=spacedaily.com</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/racinecountyeye.com</t>
+          <t>https://machibo.github.io/-/?d=racinecountyeye.com</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/timesofisrael.com</t>
+          <t>https://machibo.github.io/-/?d=timesofisrael.com</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/hardreset.info</t>
+          <t>https://machibo.github.io/-/?d=hardreset.info</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/imei.info</t>
+          <t>https://machibo.github.io/-/?d=imei.info</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/applesn.info</t>
+          <t>https://machibo.github.io/-/?d=applesn.info</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dataconomy.com</t>
+          <t>https://machibo.github.io/-/?d=dataconomy.com</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/radaronline.com</t>
+          <t>https://machibo.github.io/-/?d=radaronline.com</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/okmagazine.com</t>
+          <t>https://machibo.github.io/-/?d=okmagazine.com</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/onderwall.com</t>
+          <t>https://machibo.github.io/-/?d=onderwall.com</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/knewz.com</t>
+          <t>https://machibo.github.io/-/?d=knewz.com</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/frontpagedetectives.com</t>
+          <t>https://machibo.github.io/-/?d=frontpagedetectives.com</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/omensgolfjournal.com</t>
+          <t>https://machibo.github.io/-/?d=omensgolfjournal.com</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/morninghoney.com</t>
+          <t>https://machibo.github.io/-/?d=morninghoney.com</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/dailycoin.com</t>
+          <t>https://machibo.github.io/-/?d=dailycoin.com</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bestforandroid.com</t>
+          <t>https://machibo.github.io/-/?d=bestforandroid.com</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/esthawaiitoday.com</t>
+          <t>https://machibo.github.io/-/?d=esthawaiitoday.com</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/midweek.com</t>
+          <t>https://machibo.github.io/-/?d=midweek.com</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/hawaiitribune-herald.com</t>
+          <t>https://machibo.github.io/-/?d=hawaiitribune-herald.com</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/thegardenisland.com</t>
+          <t>https://machibo.github.io/-/?d=thegardenisland.com</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/staradvertiser.com</t>
+          <t>https://machibo.github.io/-/?d=staradvertiser.com</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ustimesnow.com</t>
+          <t>https://machibo.github.io/-/?d=ustimesnow.com</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/homecrux.com</t>
+          <t>https://machibo.github.io/-/?d=homecrux.com</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/modelifestylemagazine.com</t>
+          <t>https://machibo.github.io/-/?d=modelifestylemagazine.com</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aiworldtoday.net</t>
+          <t>https://machibo.github.io/-/?d=aiworldtoday.net</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/digitalconvey.com</t>
+          <t>https://machibo.github.io/-/?d=digitalconvey.com</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/trillmag.com</t>
+          <t>https://machibo.github.io/-/?d=trillmag.com</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businessoutstanders.com</t>
+          <t>https://machibo.github.io/-/?d=businessoutstanders.com</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/metapress.com</t>
+          <t>https://machibo.github.io/-/?d=metapress.com</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/geeky-gadgets.com</t>
+          <t>https://machibo.github.io/-/?d=geeky-gadgets.com</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gizchina.com</t>
+          <t>https://machibo.github.io/-/?d=gizchina.com</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/coinprwire.com</t>
+          <t>https://machibo.github.io/-/?d=coinprwire.com</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/psbios.me</t>
+          <t>https://machibo.github.io/-/?d=psbios.me</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/timebulletin.com</t>
+          <t>https://machibo.github.io/-/?d=timebulletin.com</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/cyberpress.org</t>
+          <t>https://machibo.github.io/-/?d=cyberpress.org</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gbhackers.com</t>
+          <t>https://machibo.github.io/-/?d=gbhackers.com</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/cybersecuritynews.com</t>
+          <t>https://machibo.github.io/-/?d=cybersecuritynews.com</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/analyticsinsight.net</t>
+          <t>https://machibo.github.io/-/?d=analyticsinsight.net</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/secureblitz.com</t>
+          <t>https://machibo.github.io/-/?d=secureblitz.com</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techdee.com</t>
+          <t>https://machibo.github.io/-/?d=techdee.com</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/talkandroid.com</t>
+          <t>https://machibo.github.io/-/?d=talkandroid.com</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/technology.org</t>
+          <t>https://machibo.github.io/-/?d=technology.org</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/kalilinuxtutorials.com</t>
+          <t>https://machibo.github.io/-/?d=kalilinuxtutorials.com</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/startup.info</t>
+          <t>https://machibo.github.io/-/?d=startup.info</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fontsarena.com</t>
+          <t>https://machibo.github.io/-/?d=fontsarena.com</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/applegazette.com</t>
+          <t>https://machibo.github.io/-/?d=applegazette.com</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bonjouridee.com</t>
+          <t>https://machibo.github.io/-/?d=bonjouridee.com</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/hardwaresecrets.com</t>
+          <t>https://machibo.github.io/-/?d=hardwaresecrets.com</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/fontmirror.com</t>
+          <t>https://machibo.github.io/-/?d=fontmirror.com</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/technochops.com</t>
+          <t>https://machibo.github.io/-/?d=technochops.com</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/socialnewsdaily.com</t>
+          <t>https://machibo.github.io/-/?d=socialnewsdaily.com</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/cssbasics.com</t>
+          <t>https://machibo.github.io/-/?d=cssbasics.com</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tubetorial.com</t>
+          <t>https://machibo.github.io/-/?d=tubetorial.com</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/apps.uk</t>
+          <t>https://machibo.github.io/-/?d=apps.uk</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/paktales.com</t>
+          <t>https://machibo.github.io/-/?d=paktales.com</t>
         </is>
       </c>
     </row>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/только</t>
+          <t>https://machibo.github.io/-/?d=только</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techdee.com</t>
+          <t>https://machibo.github.io/-/?d=techdee.com</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/technoroll.org</t>
+          <t>https://machibo.github.io/-/?d=technoroll.org</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35657,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techstrange.com</t>
+          <t>https://machibo.github.io/-/?d=techstrange.com</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35729,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techrado.com</t>
+          <t>https://machibo.github.io/-/?d=techrado.com</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35801,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/travellingforbusiness.co.uk</t>
+          <t>https://machibo.github.io/-/?d=travellingforbusiness.co.uk</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35873,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/evpowered.co.uk</t>
+          <t>https://machibo.github.io/-/?d=evpowered.co.uk</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/electrichome.uk</t>
+          <t>https://machibo.github.io/-/?d=electrichome.uk</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/propertyportfolioinvestor.co.uk</t>
+          <t>https://machibo.github.io/-/?d=propertyportfolioinvestor.co.uk</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techzeel.net</t>
+          <t>https://machibo.github.io/-/?d=techzeel.net</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/learningtoday.net</t>
+          <t>https://machibo.github.io/-/?d=learningtoday.net</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/allinsider.net</t>
+          <t>https://machibo.github.io/-/?d=allinsider.net</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36305,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sportzbuzz.net</t>
+          <t>https://machibo.github.io/-/?d=sportzbuzz.net</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36377,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/nextluxury.com</t>
+          <t>https://machibo.github.io/-/?d=nextluxury.com</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/stepbystepbusiness.com</t>
+          <t>https://machibo.github.io/-/?d=stepbystepbusiness.com</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36521,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/jt.org</t>
+          <t>https://machibo.github.io/-/?d=jt.org</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36593,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/blueandgreentomorrow.com</t>
+          <t>https://machibo.github.io/-/?d=blueandgreentomorrow.com</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techspotty.com</t>
+          <t>https://machibo.github.io/-/?d=techspotty.com</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/aboutchromebooks.com</t>
+          <t>https://machibo.github.io/-/?d=aboutchromebooks.com</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/digitaledge.org</t>
+          <t>https://machibo.github.io/-/?d=digitaledge.org</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/connectioncafe.com</t>
+          <t>https://machibo.github.io/-/?d=connectioncafe.com</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tabletmonkeys.com</t>
+          <t>https://machibo.github.io/-/?d=tabletmonkeys.com</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/quantumrun.com</t>
+          <t>https://machibo.github.io/-/?d=quantumrun.com</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/gadgetfreeks.com</t>
+          <t>https://machibo.github.io/-/?d=gadgetfreeks.com</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/hatsontech.co.uk</t>
+          <t>https://machibo.github.io/-/?d=hatsontech.co.uk</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37241,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/voddler.co.uk</t>
+          <t>https://machibo.github.io/-/?d=voddler.co.uk</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/citybiz.co</t>
+          <t>https://machibo.github.io/-/?d=citybiz.co</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/insiderpaper.com</t>
+          <t>https://machibo.github.io/-/?d=insiderpaper.com</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37457,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/onlinebizbooster.net</t>
+          <t>https://machibo.github.io/-/?d=onlinebizbooster.net</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37529,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businessandpower.com</t>
+          <t>https://machibo.github.io/-/?d=businessandpower.com</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37601,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/solidsmack.com</t>
+          <t>https://machibo.github.io/-/?d=solidsmack.com</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37673,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/jguru.com</t>
+          <t>https://machibo.github.io/-/?d=jguru.com</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37745,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/alltechbuzz.net</t>
+          <t>https://machibo.github.io/-/?d=alltechbuzz.net</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/baycitizen.org</t>
+          <t>https://machibo.github.io/-/?d=baycitizen.org</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/silicon</t>
+          <t>https://machibo.github.io/-/?d=silicon</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/triphippies.com</t>
+          <t>https://machibo.github.io/-/?d=triphippies.com</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/learningtoday.net</t>
+          <t>https://machibo.github.io/-/?d=learningtoday.net</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38105,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ecommercefastlane.com</t>
+          <t>https://machibo.github.io/-/?d=ecommercefastlane.com</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/netizensreport.com</t>
+          <t>https://machibo.github.io/-/?d=netizensreport.com</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/startup</t>
+          <t>https://machibo.github.io/-/?d=startup</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/guruhitech.com</t>
+          <t>https://machibo.github.io/-/?d=guruhitech.com</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38393,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/britishwire.com</t>
+          <t>https://machibo.github.io/-/?d=britishwire.com</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/investing.com</t>
+          <t>https://machibo.github.io/-/?d=investing.com</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/the-tech-trend.com</t>
+          <t>https://machibo.github.io/-/?d=the-tech-trend.com</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38609,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/arrington-worldwide.co.uk</t>
+          <t>https://machibo.github.io/-/?d=arrington-worldwide.co.uk</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/archeyes.com</t>
+          <t>https://machibo.github.io/-/?d=archeyes.com</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38753,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/sportswane.com</t>
+          <t>https://machibo.github.io/-/?d=sportswane.com</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/techwalls.com</t>
+          <t>https://machibo.github.io/-/?d=techwalls.com</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38897,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/lawbhoomi.com</t>
+          <t>https://machibo.github.io/-/?d=lawbhoomi.com</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38969,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/businessnewsthisweek.com</t>
+          <t>https://machibo.github.io/-/?d=businessnewsthisweek.com</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/guardian.ng</t>
+          <t>https://machibo.github.io/-/?d=guardian.ng</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/londondaily.news</t>
+          <t>https://machibo.github.io/-/?d=londondaily.news</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/london-post.co.uk</t>
+          <t>https://machibo.github.io/-/?d=london-post.co.uk</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/omenontopp.com</t>
+          <t>https://machibo.github.io/-/?d=omenontopp.com</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39329,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/impactwealth.org</t>
+          <t>https://machibo.github.io/-/?d=impactwealth.org</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/africa.businessinsider.com</t>
+          <t>https://machibo.github.io/-/?d=africa.businessinsider.com</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39473,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/measurescopez.com</t>
+          <t>https://machibo.github.io/-/?d=measurescopez.com</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ukbusinesstimes.co.uk</t>
+          <t>https://machibo.github.io/-/?d=ukbusinesstimes.co.uk</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/londoninsider.co.uk</t>
+          <t>https://machibo.github.io/-/?d=londoninsider.co.uk</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/ibusiness.news</t>
+          <t>https://machibo.github.io/-/?d=ibusiness.news</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39761,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/theluxauthority.com</t>
+          <t>https://machibo.github.io/-/?d=theluxauthority.com</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/congress.net</t>
+          <t>https://machibo.github.io/-/?d=congress.net</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/bitzuma.com</t>
+          <t>https://machibo.github.io/-/?d=bitzuma.com</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39977,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/asiapresswire.com</t>
+          <t>https://machibo.github.io/-/?d=asiapresswire.com</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/grazia.si</t>
+          <t>https://machibo.github.io/-/?d=grazia.si</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/luxuo.com</t>
+          <t>https://machibo.github.io/-/?d=luxuo.com</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40193,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/glamour.bg</t>
+          <t>https://machibo.github.io/-/?d=glamour.bg</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/digitalbusiness.kz</t>
+          <t>https://machibo.github.io/-/?d=digitalbusiness.kz</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/zakon.kz</t>
+          <t>https://machibo.github.io/-/?d=zakon.kz</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40490,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/informburo.kz</t>
+          <t>https://machibo.github.io/-/?d=informburo.kz</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/rasdaily.kz</t>
+          <t>https://machibo.github.io/-/?d=rasdaily.kz</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/caravan.kz</t>
+          <t>https://machibo.github.io/-/?d=caravan.kz</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/tengrinews.kz</t>
+          <t>https://machibo.github.io/-/?d=tengrinews.kz</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/centralmedia24.kz</t>
+          <t>https://machibo.github.io/-/?d=centralmedia24.kz</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://logo.debounce.com/orda.kz</t>
+          <t>https://machibo.github.io/-/?d=orda.kz</t>
         </is>
       </c>
     </row>

--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=srrb.ru</t>
+          <t>https://machibo.github.io/-/logos/srrb.ru.webp</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=apni.ru</t>
+          <t>https://machibo.github.io/-/logos/apni.ru.webp</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tvkinoradio.ru</t>
+          <t>https://machibo.github.io/-/logos/tvkinoradio.ru.webp</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=politnavigator.net</t>
+          <t>https://machibo.github.io/-/logos/politnavigator.net.webp</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bloknot.ru</t>
+          <t>https://machibo.github.io/-/logos/bloknot.ru.webp</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=delovoymir.biz</t>
+          <t>https://machibo.github.io/-/logos/delovoymir.biz.webp</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=business-magazine.online</t>
+          <t>https://machibo.github.io/-/logos/business-magazine.online.webp</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=garant.ru</t>
+          <t>https://machibo.github.io/-/logos/garant.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=prophotos.ru</t>
+          <t>https://machibo.github.io/-/logos/prophotos.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=peopletalk.ru</t>
+          <t>https://machibo.github.io/-/logos/peopletalk.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=versia.ru</t>
+          <t>https://machibo.github.io/-/logos/versia.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=infox.ru</t>
+          <t>https://machibo.github.io/-/logos/infox.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=samag.ru</t>
+          <t>https://machibo.github.io/-/logos/samag.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=itweek.ru</t>
+          <t>https://machibo.github.io/-/logos/itweek.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=1sept.ru</t>
+          <t>https://machibo.github.io/-/logos/1sept.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=finversia.ru</t>
+          <t>https://machibo.github.io/-/logos/finversia.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mir24.tv</t>
+          <t>https://machibo.github.io/-/logos/mir24.tv.webp</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lenta.ru</t>
+          <t>https://machibo.github.io/-/logos/lenta.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=7days.ru</t>
+          <t>https://machibo.github.io/-/logos/7days.ru.webp</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vokrug.tv</t>
+          <t>https://machibo.github.io/-/logos/vokrug.tv.webp</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fedpress.ru</t>
+          <t>https://machibo.github.io/-/logos/fedpress.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=securitylab.ru</t>
+          <t>https://machibo.github.io/-/logos/securitylab.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=osnmedia.ru</t>
+          <t>https://machibo.github.io/-/logos/osnmedia.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=snob.ru</t>
+          <t>https://machibo.github.io/-/logos/snob.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=comnews.ru</t>
+          <t>https://machibo.github.io/-/logos/comnews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tproger.ru</t>
+          <t>https://machibo.github.io/-/logos/tproger.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=cnews.ru</t>
+          <t>https://machibo.github.io/-/logos/cnews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=iz.ru</t>
+          <t>https://machibo.github.io/-/logos/iz.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sport-express.ru</t>
+          <t>https://machibo.github.io/-/logos/sport-express.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=newdaynews.ru</t>
+          <t>https://machibo.github.io/-/logos/newdaynews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gazetametro.ru</t>
+          <t>https://machibo.github.io/-/logos/gazetametro.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=5-tv.ru</t>
+          <t>https://machibo.github.io/-/logos/5-tv.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dk.ru</t>
+          <t>https://machibo.github.io/-/logos/dk.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=strategyjournal.ru</t>
+          <t>https://machibo.github.io/-/logos/strategyjournal.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=retailer.ru</t>
+          <t>https://machibo.github.io/-/logos/retailer.ru.webp</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mk.ru</t>
+          <t>https://machibo.github.io/-/logos/mk.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aif.ru</t>
+          <t>https://machibo.github.io/-/logos/aif.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vedomosti.ru</t>
+          <t>https://machibo.github.io/-/logos/vedomosti.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ng.ru</t>
+          <t>https://machibo.github.io/-/logos/ng.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=business.ru</t>
+          <t>https://machibo.github.io/-/logos/business.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kom-dir.ru</t>
+          <t>https://machibo.github.io/-/logos/kom-dir.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=glavbukh.ru</t>
+          <t>https://machibo.github.io/-/logos/glavbukh.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=26-2.ru</t>
+          <t>https://machibo.github.io/-/logos/26-2.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=buhsoft.ru</t>
+          <t>https://machibo.github.io/-/logos/buhsoft.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=pro-personal.ru</t>
+          <t>https://machibo.github.io/-/logos/pro-personal.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kdelo.ru</t>
+          <t>https://machibo.github.io/-/logos/kdelo.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tass.ru</t>
+          <t>https://machibo.github.io/-/logos/tass.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gazeta.ru</t>
+          <t>https://machibo.github.io/-/logos/gazeta.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vm.ru</t>
+          <t>https://machibo.github.io/-/logos/vm.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=news.ru</t>
+          <t>https://machibo.github.io/-/logos/news.ru.webp</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=profile.ru</t>
+          <t>https://machibo.github.io/-/logos/profile.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=oilcapital.ru</t>
+          <t>https://machibo.github.io/-/logos/oilcapital.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=business-gazeta.ru</t>
+          <t>https://machibo.github.io/-/logos/business-gazeta.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ko.ru</t>
+          <t>https://machibo.github.io/-/logos/ko.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dp.ru</t>
+          <t>https://machibo.github.io/-/logos/dp.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=popmech.ru</t>
+          <t>https://machibo.github.io/-/logos/popmech.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=svpressa.ru</t>
+          <t>https://machibo.github.io/-/logos/svpressa.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ridus.ru</t>
+          <t>https://machibo.github.io/-/logos/ridus.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dni.ru</t>
+          <t>https://machibo.github.io/-/logos/dni.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=utro.ru</t>
+          <t>https://machibo.github.io/-/logos/utro.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kleo.ru</t>
+          <t>https://machibo.github.io/-/logos/kleo.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=newizv.ru</t>
+          <t>https://machibo.github.io/-/logos/newizv.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=rosbalt.ru</t>
+          <t>https://machibo.github.io/-/logos/rosbalt.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=monocle.ru</t>
+          <t>https://machibo.github.io/-/logos/monocle.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=rg.ru</t>
+          <t>https://machibo.github.io/-/logos/rg.ru.webp</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=runews24.ru</t>
+          <t>https://machibo.github.io/-/logos/runews24.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=angi.ru</t>
+          <t>https://machibo.github.io/-/logos/angi.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=naked-science.ru</t>
+          <t>https://machibo.github.io/-/logos/naked-science.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=globalcio.ru</t>
+          <t>https://machibo.github.io/-/logos/globalcio.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businesstory.ru</t>
+          <t>https://machibo.github.io/-/logos/businesstory.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ict-online.ru</t>
+          <t>https://machibo.github.io/-/logos/ict-online.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=logirus.ru</t>
+          <t>https://machibo.github.io/-/logos/logirus.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=24gadget.ru</t>
+          <t>https://machibo.github.io/-/logos/24gadget.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=marieclaire.com</t>
+          <t>https://machibo.github.io/-/logos/marieclaire.com.webp</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=3dnews.ru</t>
+          <t>https://machibo.github.io/-/logos/3dnews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=servernews.ru</t>
+          <t>https://machibo.github.io/-/logos/servernews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=new-retail.ru</t>
+          <t>https://machibo.github.io/-/logos/new-retail.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nakanune.ru</t>
+          <t>https://machibo.github.io/-/logos/nakanune.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=telecomdaily.ru</t>
+          <t>https://machibo.github.io/-/logos/telecomdaily.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bigpicture.ru</t>
+          <t>https://machibo.github.io/-/logos/bigpicture.ru.webp</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kommersant.ru</t>
+          <t>https://machibo.github.io/-/logos/kommersant.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=eadaily.com</t>
+          <t>https://machibo.github.io/-/logos/eadaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sostav.ru</t>
+          <t>https://machibo.github.io/-/logos/sostav.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ura.news</t>
+          <t>https://machibo.github.io/-/logos/ura.news.webp</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=seonews.ru</t>
+          <t>https://machibo.github.io/-/logos/seonews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=likeni.ru</t>
+          <t>https://machibo.github.io/-/logos/likeni.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=life.ru</t>
+          <t>https://machibo.github.io/-/logos/life.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sportmk.ru</t>
+          <t>https://machibo.github.io/-/logos/sportmk.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=omanhit.ru</t>
+          <t>https://machibo.github.io/-/logos/omanhit.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=avtovzglyad.ru</t>
+          <t>https://machibo.github.io/-/logos/avtovzglyad.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ohotniki.ru</t>
+          <t>https://machibo.github.io/-/logos/ohotniki.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mperspektiva.ru</t>
+          <t>https://machibo.github.io/-/logos/mperspektiva.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=beautyhack.ru</t>
+          <t>https://machibo.github.io/-/logos/beautyhack.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sobaka.ru</t>
+          <t>https://machibo.github.io/-/logos/sobaka.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sobaka.ru</t>
+          <t>https://machibo.github.io/-/logos/sobaka.ru.webp</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sobaka.ru</t>
+          <t>https://machibo.github.io/-/logos/sobaka.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=forbes.ru</t>
+          <t>https://machibo.github.io/-/logos/forbes.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=stroygaz.ru</t>
+          <t>https://machibo.github.io/-/logos/stroygaz.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=regnum.ru</t>
+          <t>https://machibo.github.io/-/logos/regnum.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=topcor.ru</t>
+          <t>https://machibo.github.io/-/logos/topcor.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sfera.fm</t>
+          <t>https://machibo.github.io/-/logos/sfera.fm.webp</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=brl.mk.ru</t>
+          <t>https://machibo.github.io/-/logos/brl.mk.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=novate.ru</t>
+          <t>https://machibo.github.io/-/logos/novate.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=beautycarteblanche.ru</t>
+          <t>https://machibo.github.io/-/logos/beautycarteblanche.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vokrug.tv</t>
+          <t>https://machibo.github.io/-/logos/vokrug.tv.webp</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vokrugsveta.ru</t>
+          <t>https://machibo.github.io/-/logos/vokrugsveta.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=oman.ru</t>
+          <t>https://machibo.github.io/-/logos/oman.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=day.ru</t>
+          <t>https://machibo.github.io/-/logos/day.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thegirl.ru</t>
+          <t>https://machibo.github.io/-/logos/thegirl.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=starhit.ru</t>
+          <t>https://machibo.github.io/-/logos/starhit.ru.webp</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=parents.ru</t>
+          <t>https://machibo.github.io/-/logos/parents.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mydecor.ru</t>
+          <t>https://machibo.github.io/-/logos/mydecor.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=doctorpiter.ru</t>
+          <t>https://machibo.github.io/-/logos/doctorpiter.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=the-day.ru</t>
+          <t>https://machibo.github.io/-/logos/the-day.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=maximonline.ru</t>
+          <t>https://machibo.github.io/-/logos/maximonline.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=psychologies.ru</t>
+          <t>https://machibo.github.io/-/logos/psychologies.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fashiontime.ru</t>
+          <t>https://machibo.github.io/-/logos/fashiontime.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=oane.ws</t>
+          <t>https://machibo.github.io/-/logos/oane.ws.webp</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=terrnews.com</t>
+          <t>https://machibo.github.io/-/logos/terrnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kadara.ru</t>
+          <t>https://machibo.github.io/-/logos/kadara.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=monavista.ru</t>
+          <t>https://machibo.github.io/-/logos/monavista.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vestnik.net</t>
+          <t>https://machibo.github.io/-/logos/vestnik.net.webp</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nvspost.ru</t>
+          <t>https://machibo.github.io/-/logos/nvspost.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=spb.kp.ru</t>
+          <t>https://machibo.github.io/-/logos/spb.kp.ru.webp</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=belarus.kp.ru</t>
+          <t>https://machibo.github.io/-/logos/belarus.kp.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=news-24.ru</t>
+          <t>https://machibo.github.io/-/logos/news-24.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=smi24.news</t>
+          <t>https://machibo.github.io/-/logos/smi24.news.webp</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=obzor-gazet.ru</t>
+          <t>https://machibo.github.io/-/logos/obzor-gazet.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=allmosnews.ru</t>
+          <t>https://machibo.github.io/-/logos/allmosnews.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=promgoverment.ru</t>
+          <t>https://machibo.github.io/-/logos/promgoverment.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=hotrs.su</t>
+          <t>https://machibo.github.io/-/logos/hotrs.su.webp</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mirwiki.ru</t>
+          <t>https://machibo.github.io/-/logos/mirwiki.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=news-bank.ru</t>
+          <t>https://machibo.github.io/-/logos/news-bank.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=frequentflyers.ru</t>
+          <t>https://machibo.github.io/-/logos/frequentflyers.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=adindex.ru</t>
+          <t>https://machibo.github.io/-/logos/adindex.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=artagmag.ru</t>
+          <t>https://machibo.github.io/-/logos/artagmag.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sport24.ru</t>
+          <t>https://machibo.github.io/-/logos/sport24.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=prufy.ru</t>
+          <t>https://machibo.github.io/-/logos/prufy.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=schoolotzyv.ru</t>
+          <t>https://machibo.github.io/-/logos/schoolotzyv.ru.webp</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=moneytimes.ru</t>
+          <t>https://machibo.github.io/-/logos/moneytimes.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=english.pravda.ru</t>
+          <t>https://machibo.github.io/-/logos/english.pravda.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=medpulse.ru</t>
+          <t>https://machibo.github.io/-/logos/medpulse.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=newsinfo.ru</t>
+          <t>https://machibo.github.io/-/logos/newsinfo.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=politonline.ru</t>
+          <t>https://machibo.github.io/-/logos/politonline.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=greatlove.ru</t>
+          <t>https://machibo.github.io/-/logos/greatlove.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=yoki.ru</t>
+          <t>https://machibo.github.io/-/logos/yoki.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ecosever.ru</t>
+          <t>https://machibo.github.io/-/logos/ecosever.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nationaljournal.ru</t>
+          <t>https://machibo.github.io/-/logos/nationaljournal.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=rusday.com</t>
+          <t>https://machibo.github.io/-/logos/rusday.com.webp</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=electorat.info</t>
+          <t>https://machibo.github.io/-/logos/electorat.info.webp</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mostimes.com</t>
+          <t>https://machibo.github.io/-/logos/mostimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=pora.ru</t>
+          <t>https://machibo.github.io/-/logos/pora.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=glavtema.ru</t>
+          <t>https://machibo.github.io/-/logos/glavtema.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=prbn.ru</t>
+          <t>https://machibo.github.io/-/logos/prbn.ru.webp</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bigness.ru</t>
+          <t>https://machibo.github.io/-/logos/bigness.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=militarytimes.ru</t>
+          <t>https://machibo.github.io/-/logos/militarytimes.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fizcultprivet.ru</t>
+          <t>https://machibo.github.io/-/logos/fizcultprivet.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=poplawok.ru</t>
+          <t>https://machibo.github.io/-/logos/poplawok.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=autokolonka.ru</t>
+          <t>https://machibo.github.io/-/logos/autokolonka.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=repairshome.ru</t>
+          <t>https://machibo.github.io/-/logos/repairshome.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dailyshow.ru</t>
+          <t>https://machibo.github.io/-/logos/dailyshow.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=missus.ru</t>
+          <t>https://machibo.github.io/-/logos/missus.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bigcaucasus.com</t>
+          <t>https://machibo.github.io/-/logos/bigcaucasus.com.webp</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=georgiatimes.info</t>
+          <t>https://machibo.github.io/-/logos/georgiatimes.info.webp</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=pravda.ru</t>
+          <t>https://machibo.github.io/-/logos/pravda.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aviation21.ru</t>
+          <t>https://machibo.github.io/-/logos/aviation21.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=isguru.ru</t>
+          <t>https://machibo.github.io/-/logos/isguru.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=asninfo.ru</t>
+          <t>https://machibo.github.io/-/logos/asninfo.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=78.ru</t>
+          <t>https://machibo.github.io/-/logos/78.ru.webp</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thevoicemag.ru</t>
+          <t>https://machibo.github.io/-/logos/thevoicemag.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=moskvichmag.ru</t>
+          <t>https://machibo.github.io/-/logos/moskvichmag.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=rbc.ru</t>
+          <t>https://machibo.github.io/-/logos/rbc.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=moslenta.ru</t>
+          <t>https://machibo.github.io/-/logos/moslenta.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kapital.kz</t>
+          <t>https://machibo.github.io/-/logos/kapital.kz.webp</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lsm.kz</t>
+          <t>https://machibo.github.io/-/logos/lsm.kz.webp</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=newsmaker.md</t>
+          <t>https://machibo.github.io/-/logos/newsmaker.md.webp</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=akipress.org</t>
+          <t>https://machibo.github.io/-/logos/akipress.org.webp</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=24.kg</t>
+          <t>https://machibo.github.io/-/logos/24.kg.webp</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=noi.md</t>
+          <t>https://machibo.github.io/-/logos/noi.md.webp</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=uzdaily.uz</t>
+          <t>https://machibo.github.io/-/logos/uzdaily.uz.webp</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=inform.kz</t>
+          <t>https://machibo.github.io/-/logos/inform.kz.webp</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=remedium.ru</t>
+          <t>https://machibo.github.io/-/logos/remedium.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=medvestnik.ru</t>
+          <t>https://machibo.github.io/-/logos/medvestnik.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=incrussia.ru</t>
+          <t>https://machibo.github.io/-/logos/incrussia.ru.webp</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=apptractor.ru</t>
+          <t>https://machibo.github.io/-/logos/apptractor.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=investfuture.ru</t>
+          <t>https://machibo.github.io/-/logos/investfuture.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=onliner.by</t>
+          <t>https://machibo.github.io/-/logos/onliner.by.webp</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bits.media</t>
+          <t>https://machibo.github.io/-/logos/bits.media.webp</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=telegraf.news</t>
+          <t>https://machibo.github.io/-/logos/telegraf.news.webp</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=liter.kz</t>
+          <t>https://machibo.github.io/-/logos/liter.kz.webp</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=orda.kz</t>
+          <t>https://machibo.github.io/-/logos/orda.kz.webp</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dcjournal.ru</t>
+          <t>https://machibo.github.io/-/logos/dcjournal.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=telecombloger.ru</t>
+          <t>https://machibo.github.io/-/logos/telecombloger.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=urbc.ru</t>
+          <t>https://machibo.github.io/-/logos/urbc.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=haqqin.az</t>
+          <t>https://machibo.github.io/-/logos/haqqin.az.webp</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mosregion.info</t>
+          <t>https://machibo.github.io/-/logos/mosregion.info.webp</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sila-rf.ru</t>
+          <t>https://machibo.github.io/-/logos/sila-rf.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sibmedia.ru</t>
+          <t>https://machibo.github.io/-/logos/sibmedia.ru.webp</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ladys.media</t>
+          <t>https://machibo.github.io/-/logos/ladys.media.webp</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=socialinform.ru</t>
+          <t>https://machibo.github.io/-/logos/socialinform.ru.webp</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=myeconomy.ru</t>
+          <t>https://machibo.github.io/-/logos/myeconomy.ru.webp</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ecopravda.ru</t>
+          <t>https://machibo.github.io/-/logos/ecopravda.ru.webp</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=medzdrav.info</t>
+          <t>https://machibo.github.io/-/logos/medzdrav.info.webp</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=today.ua</t>
+          <t>https://machibo.github.io/-/logos/today.ua.webp</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=beautyhunter.ru</t>
+          <t>https://machibo.github.io/-/logos/beautyhunter.ru.webp</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=informator.ua</t>
+          <t>https://machibo.github.io/-/logos/informator.ua.webp</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=itechua.com</t>
+          <t>https://machibo.github.io/-/logos/itechua.com.webp</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mignews.ua</t>
+          <t>https://machibo.github.io/-/logos/mignews.ua.webp</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=it-world.ru</t>
+          <t>https://machibo.github.io/-/logos/it-world.ru.webp</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gazeta.ua</t>
+          <t>https://machibo.github.io/-/logos/gazeta.ua.webp</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=homebusinessmag.com</t>
+          <t>https://machibo.github.io/-/logos/homebusinessmag.com.webp</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=miamiherald.com</t>
+          <t>https://machibo.github.io/-/logos/miamiherald.com.webp</t>
         </is>
       </c>
     </row>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kansascity.com</t>
+          <t>https://machibo.github.io/-/logos/kansascity.com.webp</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techtimes.com</t>
+          <t>https://machibo.github.io/-/logos/techtimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=brainzmagazine.com</t>
+          <t>https://machibo.github.io/-/logos/brainzmagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=latinpost.com</t>
+          <t>https://machibo.github.io/-/logos/latinpost.com.webp</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=jpost.com</t>
+          <t>https://machibo.github.io/-/logos/jpost.com.webp</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thewestnews.com</t>
+          <t>https://machibo.github.io/-/logos/thewestnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vinnews.com</t>
+          <t>https://machibo.github.io/-/logos/vinnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fxstreet.com</t>
+          <t>https://machibo.github.io/-/logos/fxstreet.com.webp</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=inc.com</t>
+          <t>https://machibo.github.io/-/logos/inc.com.webp</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=computing.co.uk</t>
+          <t>https://machibo.github.io/-/logos/computing.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=crn.com</t>
+          <t>https://machibo.github.io/-/logos/crn.com.webp</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=intlbm.com</t>
+          <t>https://machibo.github.io/-/logos/intlbm.com.webp</t>
         </is>
       </c>
     </row>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=adexchanger.com</t>
+          <t>https://machibo.github.io/-/logos/adexchanger.com.webp</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thedrum.com</t>
+          <t>https://machibo.github.io/-/logos/thedrum.com.webp</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=globalbankingandfinance.com</t>
+          <t>https://machibo.github.io/-/logos/globalbankingandfinance.com.webp</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=financedigest.com</t>
+          <t>https://machibo.github.io/-/logos/financedigest.com.webp</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fastcompany.com</t>
+          <t>https://machibo.github.io/-/logos/fastcompany.com.webp</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=technologymagazine.com</t>
+          <t>https://machibo.github.io/-/logos/technologymagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aimagazine.com</t>
+          <t>https://machibo.github.io/-/logos/aimagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businesschief.eu</t>
+          <t>https://machibo.github.io/-/logos/businesschief.eu.webp</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=housingwire.com</t>
+          <t>https://machibo.github.io/-/logos/housingwire.com.webp</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=paymentscardsandmobile.com</t>
+          <t>https://machibo.github.io/-/logos/paymentscardsandmobile.com.webp</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=digitalconnectmag.com</t>
+          <t>https://machibo.github.io/-/logos/digitalconnectmag.com.webp</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=healthcarebusinesstoday.com</t>
+          <t>https://machibo.github.io/-/logos/healthcarebusinesstoday.com.webp</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=digiday.com</t>
+          <t>https://machibo.github.io/-/logos/digiday.com.webp</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aitimejournal.com</t>
+          <t>https://machibo.github.io/-/logos/aitimejournal.com.webp</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=geekextreme.com</t>
+          <t>https://machibo.github.io/-/logos/geekextreme.com.webp</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=coingape.com</t>
+          <t>https://machibo.github.io/-/logos/coingape.com.webp</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=arabianbusiness.com</t>
+          <t>https://machibo.github.io/-/logos/arabianbusiness.com.webp</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businesstechnet.com</t>
+          <t>https://machibo.github.io/-/logos/businesstechnet.com.webp</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techstacy.com</t>
+          <t>https://machibo.github.io/-/logos/techstacy.com.webp</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=europeanbusinessreview.com</t>
+          <t>https://machibo.github.io/-/logos/europeanbusinessreview.com.webp</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=educationtechnologyinsights.com</t>
+          <t>https://machibo.github.io/-/logos/educationtechnologyinsights.com.webp</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=digitaljournal.com</t>
+          <t>https://machibo.github.io/-/logos/digitaljournal.com.webp</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ealthybyte.com</t>
+          <t>https://machibo.github.io/-/logos/ealthybyte.com.webp</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techinasia.com</t>
+          <t>https://machibo.github.io/-/logos/techinasia.com.webp</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=siliconcanals.com</t>
+          <t>https://machibo.github.io/-/logos/siliconcanals.com.webp</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bizfortune.com</t>
+          <t>https://machibo.github.io/-/logos/bizfortune.com.webp</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ciobulletin.com</t>
+          <t>https://machibo.github.io/-/logos/ciobulletin.com.webp</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=abcmoney.co.uk</t>
+          <t>https://machibo.github.io/-/logos/abcmoney.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ceo-review.com</t>
+          <t>https://machibo.github.io/-/logos/ceo-review.com.webp</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=corporatevision-news.com</t>
+          <t>https://machibo.github.io/-/logos/corporatevision-news.com.webp</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=startupsmagazine.co.uk</t>
+          <t>https://machibo.github.io/-/logos/startupsmagazine.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lux-life.digital</t>
+          <t>https://machibo.github.io/-/logos/lux-life.digital.webp</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=build-review.com</t>
+          <t>https://machibo.github.io/-/logos/build-review.com.webp</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=smenews.digital</t>
+          <t>https://machibo.github.io/-/logos/smenews.digital.webp</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ghpnews.digital</t>
+          <t>https://machibo.github.io/-/logos/ghpnews.digital.webp</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=acquisition-international.com</t>
+          <t>https://machibo.github.io/-/logos/acquisition-international.com.webp</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ealthandfinance.digital</t>
+          <t>https://machibo.github.io/-/logos/ealthandfinance.digital.webp</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=eubusinessnews.com</t>
+          <t>https://machibo.github.io/-/logos/eubusinessnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=meamarkets.digital</t>
+          <t>https://machibo.github.io/-/logos/meamarkets.digital.webp</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=apacinsider.digital</t>
+          <t>https://machibo.github.io/-/logos/apacinsider.digital.webp</t>
         </is>
       </c>
     </row>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=coventryobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/coventryobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bromsgrovestandard.co.uk</t>
+          <t>https://machibo.github.io/-/logos/bromsgrovestandard.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=droitwichstandard.co.uk</t>
+          <t>https://machibo.github.io/-/logos/droitwichstandard.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=eveshamobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/eveshamobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kidderminsterstandard.co.uk</t>
+          <t>https://machibo.github.io/-/logos/kidderminsterstandard.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=leamingtonobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/leamingtonobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=malvernobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/malvernobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=redditchstandard.co.uk</t>
+          <t>https://machibo.github.io/-/logos/redditchstandard.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=rugbyobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/rugbyobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19385,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=solihullobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/solihullobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=stratfordobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/stratfordobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=orcesterobserver.co.uk</t>
+          <t>https://machibo.github.io/-/logos/orcesterobserver.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=richmond.com</t>
+          <t>https://machibo.github.io/-/logos/richmond.com.webp</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fredericksburg.com</t>
+          <t>https://machibo.github.io/-/logos/fredericksburg.com.webp</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=roanoke.com</t>
+          <t>https://machibo.github.io/-/logos/roanoke.com.webp</t>
         </is>
       </c>
     </row>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=newsadvance.com</t>
+          <t>https://machibo.github.io/-/logos/newsadvance.com.webp</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dailyprogress.com</t>
+          <t>https://machibo.github.io/-/logos/dailyprogress.com.webp</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=heraldcourier.com</t>
+          <t>https://machibo.github.io/-/logos/heraldcourier.com.webp</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=martinsvillebulletin.com</t>
+          <t>https://machibo.github.io/-/logos/martinsvillebulletin.com.webp</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=newsvirginian.com</t>
+          <t>https://machibo.github.io/-/logos/newsvirginian.com.webp</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thefranklinnewspost.com</t>
+          <t>https://machibo.github.io/-/logos/thefranklinnewspost.com.webp</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=godanriver.com</t>
+          <t>https://machibo.github.io/-/logos/godanriver.com.webp</t>
         </is>
       </c>
     </row>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=starexponent.com</t>
+          <t>https://machibo.github.io/-/logos/starexponent.com.webp</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=smithmountainlake.com</t>
+          <t>https://machibo.github.io/-/logos/smithmountainlake.com.webp</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=swvatoday.com</t>
+          <t>https://machibo.github.io/-/logos/swvatoday.com.webp</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=naludamagazine.com</t>
+          <t>https://machibo.github.io/-/logos/naludamagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tech-critter.com</t>
+          <t>https://machibo.github.io/-/logos/tech-critter.com.webp</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nasilemaktech.com</t>
+          <t>https://machibo.github.io/-/logos/nasilemaktech.com.webp</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=myeverydaytech.com</t>
+          <t>https://machibo.github.io/-/logos/myeverydaytech.com.webp</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businessfostermagazine.com</t>
+          <t>https://machibo.github.io/-/logos/businessfostermagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=business-money.com</t>
+          <t>https://machibo.github.io/-/logos/business-money.com.webp</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businesscloud.co.uk</t>
+          <t>https://machibo.github.io/-/logos/businesscloud.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gritdaily.com</t>
+          <t>https://machibo.github.io/-/logos/gritdaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thesiliconreview.com</t>
+          <t>https://machibo.github.io/-/logos/thesiliconreview.com.webp</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thestreet.com</t>
+          <t>https://machibo.github.io/-/logos/thestreet.com.webp</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thedefiant.io</t>
+          <t>https://machibo.github.io/-/logos/thedefiant.io.webp</t>
         </is>
       </c>
     </row>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=smartechdaily.com</t>
+          <t>https://machibo.github.io/-/logos/smartechdaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=meditechtoday.com</t>
+          <t>https://machibo.github.io/-/logos/meditechtoday.com.webp</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=financialtechtimes.com</t>
+          <t>https://machibo.github.io/-/logos/financialtechtimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=blocktelegraph.io</t>
+          <t>https://machibo.github.io/-/logos/blocktelegraph.io.webp</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=transittomorrow.com</t>
+          <t>https://machibo.github.io/-/logos/transittomorrow.com.webp</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=highnetworthmag.com</t>
+          <t>https://machibo.github.io/-/logos/highnetworthmag.com.webp</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=pharmatechnews.com</t>
+          <t>https://machibo.github.io/-/logos/pharmatechnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxurylamag.com</t>
+          <t>https://machibo.github.io/-/logos/luxurylamag.com.webp</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxurymiamimag.com</t>
+          <t>https://machibo.github.io/-/logos/luxurymiamimag.com.webp</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lawnewsday.com</t>
+          <t>https://machibo.github.io/-/logos/lawnewsday.com.webp</t>
         </is>
       </c>
     </row>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gametechdaily.com</t>
+          <t>https://machibo.github.io/-/logos/gametechdaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ealthtechdaily.com</t>
+          <t>https://machibo.github.io/-/logos/ealthtechdaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sportstechtoday.com</t>
+          <t>https://machibo.github.io/-/logos/sportstechtoday.com.webp</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=meditechwire.com</t>
+          <t>https://machibo.github.io/-/logos/meditechwire.com.webp</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=coinreviewnews.com</t>
+          <t>https://machibo.github.io/-/logos/coinreviewnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=innotechtoday.com</t>
+          <t>https://machibo.github.io/-/logos/innotechtoday.com.webp</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=csq.com</t>
+          <t>https://machibo.github.io/-/logos/csq.com.webp</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techfundingnews.com</t>
+          <t>https://machibo.github.io/-/logos/techfundingnews.com.webp</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=millennialmagazine.com</t>
+          <t>https://machibo.github.io/-/logos/millennialmagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=deccanherald.com</t>
+          <t>https://machibo.github.io/-/logos/deccanherald.com.webp</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=amazingarchitecture.com</t>
+          <t>https://machibo.github.io/-/logos/amazingarchitecture.com.webp</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=healthworkscollective.com</t>
+          <t>https://machibo.github.io/-/logos/healthworkscollective.com.webp</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=goodmenproject.com</t>
+          <t>https://machibo.github.io/-/logos/goodmenproject.com.webp</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gilmorehealth.com</t>
+          <t>https://machibo.github.io/-/logos/gilmorehealth.com.webp</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=papermag.com</t>
+          <t>https://machibo.github.io/-/logos/papermag.com.webp</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bust.com</t>
+          <t>https://machibo.github.io/-/logos/bust.com.webp</t>
         </is>
       </c>
     </row>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=villagevoice.com</t>
+          <t>https://machibo.github.io/-/logos/villagevoice.com.webp</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=irvineweekly.com</t>
+          <t>https://machibo.github.io/-/logos/irvineweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=marinatimes.com</t>
+          <t>https://machibo.github.io/-/logos/marinatimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23417,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thecharlotteweekly.com</t>
+          <t>https://machibo.github.io/-/logos/thecharlotteweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=theleadernews.com</t>
+          <t>https://machibo.github.io/-/logos/theleadernews.com.webp</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fortbendstar.com</t>
+          <t>https://machibo.github.io/-/logos/fortbendstar.com.webp</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23633,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lakerlutznews.com</t>
+          <t>https://machibo.github.io/-/logos/lakerlutznews.com.webp</t>
         </is>
       </c>
     </row>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=laweekly.com</t>
+          <t>https://machibo.github.io/-/logos/laweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ocweekly.com</t>
+          <t>https://machibo.github.io/-/logos/ocweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=inbuzzer.com</t>
+          <t>https://machibo.github.io/-/logos/inbuzzer.com.webp</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23921,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businessmole.com</t>
+          <t>https://machibo.github.io/-/logos/businessmole.com.webp</t>
         </is>
       </c>
     </row>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=instrumentalfx.co</t>
+          <t>https://machibo.github.io/-/logos/instrumentalfx.co.webp</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fadmagazine.com</t>
+          <t>https://machibo.github.io/-/logos/fadmagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=eraveyou.com</t>
+          <t>https://machibo.github.io/-/logos/eraveyou.com.webp</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sportsgossip.com</t>
+          <t>https://machibo.github.io/-/logos/sportsgossip.com.webp</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sportsmedia101.com</t>
+          <t>https://machibo.github.io/-/logos/sportsmedia101.com.webp</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bostonsportsextra.com</t>
+          <t>https://machibo.github.io/-/logos/bostonsportsextra.com.webp</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fangsbites.com</t>
+          <t>https://machibo.github.io/-/logos/fangsbites.com.webp</t>
         </is>
       </c>
     </row>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=alltechmagazine.com</t>
+          <t>https://machibo.github.io/-/logos/alltechmagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=architectureartdesigns.com</t>
+          <t>https://machibo.github.io/-/logos/architectureartdesigns.com.webp</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ceotodaymagazine.com</t>
+          <t>https://machibo.github.io/-/logos/ceotodaymagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=insidermonkey.com</t>
+          <t>https://machibo.github.io/-/logos/insidermonkey.com.webp</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=securityonline.info</t>
+          <t>https://machibo.github.io/-/logos/securityonline.info.webp</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=securityexpress.info</t>
+          <t>https://machibo.github.io/-/logos/securityexpress.info.webp</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=meterpreter.org</t>
+          <t>https://machibo.github.io/-/logos/meterpreter.org.webp</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techiexpert.com</t>
+          <t>https://machibo.github.io/-/logos/techiexpert.com.webp</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxuryhousingtrends.com</t>
+          <t>https://machibo.github.io/-/logos/luxuryhousingtrends.com.webp</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=iplocation.net</t>
+          <t>https://machibo.github.io/-/logos/iplocation.net.webp</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=opsmatters.com</t>
+          <t>https://machibo.github.io/-/logos/opsmatters.com.webp</t>
         </is>
       </c>
     </row>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businesshonor.com</t>
+          <t>https://machibo.github.io/-/logos/businesshonor.com.webp</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=highways.today</t>
+          <t>https://machibo.github.io/-/logos/highways.today.webp</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=hometownstation.com</t>
+          <t>https://machibo.github.io/-/logos/hometownstation.com.webp</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=latintimes.com</t>
+          <t>https://machibo.github.io/-/logos/latintimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techloy.com</t>
+          <t>https://machibo.github.io/-/logos/techloy.com.webp</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=americancraftbeer.com</t>
+          <t>https://machibo.github.io/-/logos/americancraftbeer.com.webp</t>
         </is>
       </c>
     </row>
@@ -25721,7 +25721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=beerconnoisseur.com</t>
+          <t>https://machibo.github.io/-/logos/beerconnoisseur.com.webp</t>
         </is>
       </c>
     </row>
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=porchdrinking.com</t>
+          <t>https://machibo.github.io/-/logos/porchdrinking.com.webp</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mantelligence.com</t>
+          <t>https://machibo.github.io/-/logos/mantelligence.com.webp</t>
         </is>
       </c>
     </row>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=brulosophy.com</t>
+          <t>https://machibo.github.io/-/logos/brulosophy.com.webp</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ashingtonbeerblog.com</t>
+          <t>https://machibo.github.io/-/logos/ashingtonbeerblog.com.webp</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=breweriesinpa.com</t>
+          <t>https://machibo.github.io/-/logos/breweriesinpa.com.webp</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26153,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sandiegobeer.news</t>
+          <t>https://machibo.github.io/-/logos/sandiegobeer.news.webp</t>
         </is>
       </c>
     </row>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=livemusicblog.com</t>
+          <t>https://machibo.github.io/-/logos/livemusicblog.com.webp</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=mybeerbuzz.com</t>
+          <t>https://machibo.github.io/-/logos/mybeerbuzz.com.webp</t>
         </is>
       </c>
     </row>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=highways.today</t>
+          <t>https://machibo.github.io/-/logos/highways.today.webp</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxuryhousingtrends.com</t>
+          <t>https://machibo.github.io/-/logos/luxuryhousingtrends.com.webp</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=timesla.com</t>
+          <t>https://machibo.github.io/-/logos/timesla.com.webp</t>
         </is>
       </c>
     </row>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gearrice.com</t>
+          <t>https://machibo.github.io/-/logos/gearrice.com.webp</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=inkl.com</t>
+          <t>https://machibo.github.io/-/logos/inkl.com.webp</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nyweekly.com</t>
+          <t>https://machibo.github.io/-/logos/nyweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=artistweekly.com</t>
+          <t>https://machibo.github.io/-/logos/artistweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ceoweekly.com</t>
+          <t>https://machibo.github.io/-/logos/ceoweekly.com.webp</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=atlwire.com</t>
+          <t>https://machibo.github.io/-/logos/atlwire.com.webp</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thechicagojournal.com</t>
+          <t>https://machibo.github.io/-/logos/thechicagojournal.com.webp</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=emonthlynews.com</t>
+          <t>https://machibo.github.io/-/logos/emonthlynews.com.webp</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lawire.com</t>
+          <t>https://machibo.github.io/-/logos/lawire.com.webp</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=beautyscene.net</t>
+          <t>https://machibo.github.io/-/logos/beautyscene.net.webp</t>
         </is>
       </c>
     </row>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=londonlovesproperty.com</t>
+          <t>https://machibo.github.io/-/logos/londonlovesproperty.com.webp</t>
         </is>
       </c>
     </row>
@@ -27377,7 +27377,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=londonlovestech.com</t>
+          <t>https://machibo.github.io/-/logos/londonlovestech.com.webp</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nimvo.com</t>
+          <t>https://machibo.github.io/-/logos/nimvo.com.webp</t>
         </is>
       </c>
     </row>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=chaospin.com</t>
+          <t>https://machibo.github.io/-/logos/chaospin.com.webp</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27593,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=malemodelscene.net</t>
+          <t>https://machibo.github.io/-/logos/malemodelscene.net.webp</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thebusinesswomanmedia.com</t>
+          <t>https://machibo.github.io/-/logos/thebusinesswomanmedia.com.webp</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techbullion.com</t>
+          <t>https://machibo.github.io/-/logos/techbullion.com.webp</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fashionuer.com</t>
+          <t>https://machibo.github.io/-/logos/fashionuer.com.webp</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=moneyinc.com</t>
+          <t>https://machibo.github.io/-/logos/moneyinc.com.webp</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=londonlovesbusiness.com</t>
+          <t>https://machibo.github.io/-/logos/londonlovesbusiness.com.webp</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bmmagazine.co.uk</t>
+          <t>https://machibo.github.io/-/logos/bmmagazine.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28097,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=designscene.net</t>
+          <t>https://machibo.github.io/-/logos/designscene.net.webp</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fashionuer.com</t>
+          <t>https://machibo.github.io/-/logos/fashionuer.com.webp</t>
         </is>
       </c>
     </row>
@@ -28241,7 +28241,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=entrepreneurhandbook.co.uk</t>
+          <t>https://machibo.github.io/-/logos/entrepreneurhandbook.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=notorious-mag.com</t>
+          <t>https://machibo.github.io/-/logos/notorious-mag.com.webp</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thelondoneconomic.com</t>
+          <t>https://machibo.github.io/-/logos/thelondoneconomic.com.webp</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techstartups.com</t>
+          <t>https://machibo.github.io/-/logos/techstartups.com.webp</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=swaggermagazine.com</t>
+          <t>https://machibo.github.io/-/logos/swaggermagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aijourn.com</t>
+          <t>https://machibo.github.io/-/logos/aijourn.com.webp</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=financefeeds.com</t>
+          <t>https://machibo.github.io/-/logos/financefeeds.com.webp</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sciencetimes.com</t>
+          <t>https://machibo.github.io/-/logos/sciencetimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=itechpost.com</t>
+          <t>https://machibo.github.io/-/logos/itechpost.com.webp</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28889,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=plainenglish.io</t>
+          <t>https://machibo.github.io/-/logos/plainenglish.io.webp</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techround.co.uk</t>
+          <t>https://machibo.github.io/-/logos/techround.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29033,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=eureporter.co</t>
+          <t>https://machibo.github.io/-/logos/eureporter.co.webp</t>
         </is>
       </c>
     </row>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dataconomy.com</t>
+          <t>https://machibo.github.io/-/logos/dataconomy.com.webp</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ceoworld.biz</t>
+          <t>https://machibo.github.io/-/logos/ceoworld.biz.webp</t>
         </is>
       </c>
     </row>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=allwomenstalk.com</t>
+          <t>https://machibo.github.io/-/logos/allwomenstalk.com.webp</t>
         </is>
       </c>
     </row>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ceoworld.biz</t>
+          <t>https://machibo.github.io/-/logos/ceoworld.biz.webp</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=u.today</t>
+          <t>https://machibo.github.io/-/logos/u.today.webp</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=esternjournal.com</t>
+          <t>https://machibo.github.io/-/logos/esternjournal.com.webp</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techworm.net</t>
+          <t>https://machibo.github.io/-/logos/techworm.net.webp</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ibtimes.com</t>
+          <t>https://machibo.github.io/-/logos/ibtimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=theubj.com</t>
+          <t>https://machibo.github.io/-/logos/theubj.com.webp</t>
         </is>
       </c>
     </row>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=archiscene.net</t>
+          <t>https://machibo.github.io/-/logos/archiscene.net.webp</t>
         </is>
       </c>
     </row>
@@ -29825,7 +29825,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=largest.org</t>
+          <t>https://machibo.github.io/-/logos/largest.org.webp</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dailycivil.com</t>
+          <t>https://machibo.github.io/-/logos/dailycivil.com.webp</t>
         </is>
       </c>
     </row>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tidtiltech.dk</t>
+          <t>https://machibo.github.io/-/logos/tidtiltech.dk.webp</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=asianatimes.com</t>
+          <t>https://machibo.github.io/-/logos/asianatimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=musicraiser.net</t>
+          <t>https://machibo.github.io/-/logos/musicraiser.net.webp</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=utilizewindows.com</t>
+          <t>https://machibo.github.io/-/logos/utilizewindows.com.webp</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thetvjunkies.com</t>
+          <t>https://machibo.github.io/-/logos/thetvjunkies.com.webp</t>
         </is>
       </c>
     </row>
@@ -30329,7 +30329,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tu.tv</t>
+          <t>https://machibo.github.io/-/logos/tu.tv.webp</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=networthrant.com</t>
+          <t>https://machibo.github.io/-/logos/networthrant.com.webp</t>
         </is>
       </c>
     </row>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=jewelbeat.com</t>
+          <t>https://machibo.github.io/-/logos/jewelbeat.com.webp</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=desksgram.net</t>
+          <t>https://machibo.github.io/-/logos/desksgram.net.webp</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=vxchnge.com</t>
+          <t>https://machibo.github.io/-/logos/vxchnge.com.webp</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=liberalco.org</t>
+          <t>https://machibo.github.io/-/logos/liberalco.org.webp</t>
         </is>
       </c>
     </row>
@@ -30761,7 +30761,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kiwibox.com</t>
+          <t>https://machibo.github.io/-/logos/kiwibox.com.webp</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ebsta.me</t>
+          <t>https://machibo.github.io/-/logos/ebsta.me.webp</t>
         </is>
       </c>
     </row>
@@ -30905,7 +30905,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techktimes.co.uk</t>
+          <t>https://machibo.github.io/-/logos/techktimes.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=koreaittimes.com</t>
+          <t>https://machibo.github.io/-/logos/koreaittimes.com.webp</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=breakingac.com</t>
+          <t>https://machibo.github.io/-/logos/breakingac.com.webp</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31121,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=maryberryrecipes.co.uk</t>
+          <t>https://machibo.github.io/-/logos/maryberryrecipes.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=londontime.co</t>
+          <t>https://machibo.github.io/-/logos/londontime.co.webp</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31265,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=theluxurylifestylemagazine.com</t>
+          <t>https://machibo.github.io/-/logos/theluxurylifestylemagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxurylifestylemag.co.uk</t>
+          <t>https://machibo.github.io/-/logos/luxurylifestylemag.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxurialifestyle.com</t>
+          <t>https://machibo.github.io/-/logos/luxurialifestyle.com.webp</t>
         </is>
       </c>
     </row>
@@ -31481,7 +31481,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=spacedaily.com</t>
+          <t>https://machibo.github.io/-/logos/spacedaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=racinecountyeye.com</t>
+          <t>https://machibo.github.io/-/logos/racinecountyeye.com.webp</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=timesofisrael.com</t>
+          <t>https://machibo.github.io/-/logos/timesofisrael.com.webp</t>
         </is>
       </c>
     </row>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=hardreset.info</t>
+          <t>https://machibo.github.io/-/logos/hardreset.info.webp</t>
         </is>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=imei.info</t>
+          <t>https://machibo.github.io/-/logos/imei.info.webp</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=applesn.info</t>
+          <t>https://machibo.github.io/-/logos/applesn.info.webp</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dataconomy.com</t>
+          <t>https://machibo.github.io/-/logos/dataconomy.com.webp</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=radaronline.com</t>
+          <t>https://machibo.github.io/-/logos/radaronline.com.webp</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=okmagazine.com</t>
+          <t>https://machibo.github.io/-/logos/okmagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=onderwall.com</t>
+          <t>https://machibo.github.io/-/logos/onderwall.com.webp</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=knewz.com</t>
+          <t>https://machibo.github.io/-/logos/knewz.com.webp</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=frontpagedetectives.com</t>
+          <t>https://machibo.github.io/-/logos/frontpagedetectives.com.webp</t>
         </is>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=omensgolfjournal.com</t>
+          <t>https://machibo.github.io/-/logos/omensgolfjournal.com.webp</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=morninghoney.com</t>
+          <t>https://machibo.github.io/-/logos/morninghoney.com.webp</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=dailycoin.com</t>
+          <t>https://machibo.github.io/-/logos/dailycoin.com.webp</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bestforandroid.com</t>
+          <t>https://machibo.github.io/-/logos/bestforandroid.com.webp</t>
         </is>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=esthawaiitoday.com</t>
+          <t>https://machibo.github.io/-/logos/esthawaiitoday.com.webp</t>
         </is>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=midweek.com</t>
+          <t>https://machibo.github.io/-/logos/midweek.com.webp</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=hawaiitribune-herald.com</t>
+          <t>https://machibo.github.io/-/logos/hawaiitribune-herald.com.webp</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=thegardenisland.com</t>
+          <t>https://machibo.github.io/-/logos/thegardenisland.com.webp</t>
         </is>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=staradvertiser.com</t>
+          <t>https://machibo.github.io/-/logos/staradvertiser.com.webp</t>
         </is>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ustimesnow.com</t>
+          <t>https://machibo.github.io/-/logos/ustimesnow.com.webp</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=homecrux.com</t>
+          <t>https://machibo.github.io/-/logos/homecrux.com.webp</t>
         </is>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=modelifestylemagazine.com</t>
+          <t>https://machibo.github.io/-/logos/modelifestylemagazine.com.webp</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aiworldtoday.net</t>
+          <t>https://machibo.github.io/-/logos/aiworldtoday.net.webp</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=digitalconvey.com</t>
+          <t>https://machibo.github.io/-/logos/digitalconvey.com.webp</t>
         </is>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=trillmag.com</t>
+          <t>https://machibo.github.io/-/logos/trillmag.com.webp</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businessoutstanders.com</t>
+          <t>https://machibo.github.io/-/logos/businessoutstanders.com.webp</t>
         </is>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=metapress.com</t>
+          <t>https://machibo.github.io/-/logos/metapress.com.webp</t>
         </is>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=geeky-gadgets.com</t>
+          <t>https://machibo.github.io/-/logos/geeky-gadgets.com.webp</t>
         </is>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gizchina.com</t>
+          <t>https://machibo.github.io/-/logos/gizchina.com.webp</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=coinprwire.com</t>
+          <t>https://machibo.github.io/-/logos/coinprwire.com.webp</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=psbios.me</t>
+          <t>https://machibo.github.io/-/logos/psbios.me.webp</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=timebulletin.com</t>
+          <t>https://machibo.github.io/-/logos/timebulletin.com.webp</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=cyberpress.org</t>
+          <t>https://machibo.github.io/-/logos/cyberpress.org.webp</t>
         </is>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gbhackers.com</t>
+          <t>https://machibo.github.io/-/logos/gbhackers.com.webp</t>
         </is>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=cybersecuritynews.com</t>
+          <t>https://machibo.github.io/-/logos/cybersecuritynews.com.webp</t>
         </is>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=analyticsinsight.net</t>
+          <t>https://machibo.github.io/-/logos/analyticsinsight.net.webp</t>
         </is>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=secureblitz.com</t>
+          <t>https://machibo.github.io/-/logos/secureblitz.com.webp</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techdee.com</t>
+          <t>https://machibo.github.io/-/logos/techdee.com.webp</t>
         </is>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=talkandroid.com</t>
+          <t>https://machibo.github.io/-/logos/talkandroid.com.webp</t>
         </is>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=technology.org</t>
+          <t>https://machibo.github.io/-/logos/technology.org.webp</t>
         </is>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=kalilinuxtutorials.com</t>
+          <t>https://machibo.github.io/-/logos/kalilinuxtutorials.com.webp</t>
         </is>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=startup.info</t>
+          <t>https://machibo.github.io/-/logos/startup.info.webp</t>
         </is>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fontsarena.com</t>
+          <t>https://machibo.github.io/-/logos/fontsarena.com.webp</t>
         </is>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=applegazette.com</t>
+          <t>https://machibo.github.io/-/logos/applegazette.com.webp</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bonjouridee.com</t>
+          <t>https://machibo.github.io/-/logos/bonjouridee.com.webp</t>
         </is>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=hardwaresecrets.com</t>
+          <t>https://machibo.github.io/-/logos/hardwaresecrets.com.webp</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=fontmirror.com</t>
+          <t>https://machibo.github.io/-/logos/fontmirror.com.webp</t>
         </is>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=technochops.com</t>
+          <t>https://machibo.github.io/-/logos/technochops.com.webp</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=socialnewsdaily.com</t>
+          <t>https://machibo.github.io/-/logos/socialnewsdaily.com.webp</t>
         </is>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=cssbasics.com</t>
+          <t>https://machibo.github.io/-/logos/cssbasics.com.webp</t>
         </is>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tubetorial.com</t>
+          <t>https://machibo.github.io/-/logos/tubetorial.com.webp</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=apps.uk</t>
+          <t>https://machibo.github.io/-/logos/apps.uk.webp</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=paktales.com</t>
+          <t>https://machibo.github.io/-/logos/paktales.com.webp</t>
         </is>
       </c>
     </row>
@@ -35439,11 +35439,7 @@
           <t>3–7 business days</t>
         </is>
       </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>https://machibo.github.io/-/?d=только</t>
-        </is>
-      </c>
+      <c r="N288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -35513,7 +35509,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techdee.com</t>
+          <t>https://machibo.github.io/-/logos/techdee.com.webp</t>
         </is>
       </c>
     </row>
@@ -35585,7 +35581,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=technoroll.org</t>
+          <t>https://machibo.github.io/-/logos/technoroll.org.webp</t>
         </is>
       </c>
     </row>
@@ -35657,7 +35653,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techstrange.com</t>
+          <t>https://machibo.github.io/-/logos/techstrange.com.webp</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35725,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techrado.com</t>
+          <t>https://machibo.github.io/-/logos/techrado.com.webp</t>
         </is>
       </c>
     </row>
@@ -35801,7 +35797,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=travellingforbusiness.co.uk</t>
+          <t>https://machibo.github.io/-/logos/travellingforbusiness.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35869,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=evpowered.co.uk</t>
+          <t>https://machibo.github.io/-/logos/evpowered.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35941,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=electrichome.uk</t>
+          <t>https://machibo.github.io/-/logos/electrichome.uk.webp</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36013,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=propertyportfolioinvestor.co.uk</t>
+          <t>https://machibo.github.io/-/logos/propertyportfolioinvestor.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36085,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techzeel.net</t>
+          <t>https://machibo.github.io/-/logos/techzeel.net.webp</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36157,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=learningtoday.net</t>
+          <t>https://machibo.github.io/-/logos/learningtoday.net.webp</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36229,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=allinsider.net</t>
+          <t>https://machibo.github.io/-/logos/allinsider.net.webp</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36301,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sportzbuzz.net</t>
+          <t>https://machibo.github.io/-/logos/sportzbuzz.net.webp</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36373,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=nextluxury.com</t>
+          <t>https://machibo.github.io/-/logos/nextluxury.com.webp</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36445,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=stepbystepbusiness.com</t>
+          <t>https://machibo.github.io/-/logos/stepbystepbusiness.com.webp</t>
         </is>
       </c>
     </row>
@@ -36521,7 +36517,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=jt.org</t>
+          <t>https://machibo.github.io/-/logos/jt.org.webp</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36589,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=blueandgreentomorrow.com</t>
+          <t>https://machibo.github.io/-/logos/blueandgreentomorrow.com.webp</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36661,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techspotty.com</t>
+          <t>https://machibo.github.io/-/logos/techspotty.com.webp</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36733,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=aboutchromebooks.com</t>
+          <t>https://machibo.github.io/-/logos/aboutchromebooks.com.webp</t>
         </is>
       </c>
     </row>
@@ -36809,7 +36805,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=digitaledge.org</t>
+          <t>https://machibo.github.io/-/logos/digitaledge.org.webp</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36877,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=connectioncafe.com</t>
+          <t>https://machibo.github.io/-/logos/connectioncafe.com.webp</t>
         </is>
       </c>
     </row>
@@ -36953,7 +36949,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tabletmonkeys.com</t>
+          <t>https://machibo.github.io/-/logos/tabletmonkeys.com.webp</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37021,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=quantumrun.com</t>
+          <t>https://machibo.github.io/-/logos/quantumrun.com.webp</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37093,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=gadgetfreeks.com</t>
+          <t>https://machibo.github.io/-/logos/gadgetfreeks.com.webp</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37165,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=hatsontech.co.uk</t>
+          <t>https://machibo.github.io/-/logos/hatsontech.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -37241,7 +37237,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=voddler.co.uk</t>
+          <t>https://machibo.github.io/-/logos/voddler.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -37313,7 +37309,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=citybiz.co</t>
+          <t>https://machibo.github.io/-/logos/citybiz.co.webp</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37381,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=insiderpaper.com</t>
+          <t>https://machibo.github.io/-/logos/insiderpaper.com.webp</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37453,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=onlinebizbooster.net</t>
+          <t>https://machibo.github.io/-/logos/onlinebizbooster.net.webp</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37525,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businessandpower.com</t>
+          <t>https://machibo.github.io/-/logos/businessandpower.com.webp</t>
         </is>
       </c>
     </row>
@@ -37601,7 +37597,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=solidsmack.com</t>
+          <t>https://machibo.github.io/-/logos/solidsmack.com.webp</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37669,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=jguru.com</t>
+          <t>https://machibo.github.io/-/logos/jguru.com.webp</t>
         </is>
       </c>
     </row>
@@ -37745,7 +37741,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=alltechbuzz.net</t>
+          <t>https://machibo.github.io/-/logos/alltechbuzz.net.webp</t>
         </is>
       </c>
     </row>
@@ -37817,7 +37813,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=baycitizen.org</t>
+          <t>https://machibo.github.io/-/logos/baycitizen.org.webp</t>
         </is>
       </c>
     </row>
@@ -37889,7 +37885,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=silicon</t>
+          <t>https://machibo.github.io/-/logos/silicon.webp</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37957,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=triphippies.com</t>
+          <t>https://machibo.github.io/-/logos/triphippies.com.webp</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38029,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=learningtoday.net</t>
+          <t>https://machibo.github.io/-/logos/learningtoday.net.webp</t>
         </is>
       </c>
     </row>
@@ -38105,7 +38101,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ecommercefastlane.com</t>
+          <t>https://machibo.github.io/-/logos/ecommercefastlane.com.webp</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38173,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=netizensreport.com</t>
+          <t>https://machibo.github.io/-/logos/netizensreport.com.webp</t>
         </is>
       </c>
     </row>
@@ -38247,11 +38243,7 @@
           <t>3–7 business days</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>https://machibo.github.io/-/?d=startup</t>
-        </is>
-      </c>
+      <c r="N327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -38321,7 +38313,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=guruhitech.com</t>
+          <t>https://machibo.github.io/-/logos/guruhitech.com.webp</t>
         </is>
       </c>
     </row>
@@ -38393,7 +38385,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=britishwire.com</t>
+          <t>https://machibo.github.io/-/logos/britishwire.com.webp</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38457,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=investing.com</t>
+          <t>https://machibo.github.io/-/logos/investing.com.webp</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38529,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=the-tech-trend.com</t>
+          <t>https://machibo.github.io/-/logos/the-tech-trend.com.webp</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38601,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=arrington-worldwide.co.uk</t>
+          <t>https://machibo.github.io/-/logos/arrington-worldwide.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38673,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=archeyes.com</t>
+          <t>https://machibo.github.io/-/logos/archeyes.com.webp</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38745,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=sportswane.com</t>
+          <t>https://machibo.github.io/-/logos/sportswane.com.webp</t>
         </is>
       </c>
     </row>
@@ -38825,7 +38817,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=techwalls.com</t>
+          <t>https://machibo.github.io/-/logos/techwalls.com.webp</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38889,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=lawbhoomi.com</t>
+          <t>https://machibo.github.io/-/logos/lawbhoomi.com.webp</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38961,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=businessnewsthisweek.com</t>
+          <t>https://machibo.github.io/-/logos/businessnewsthisweek.com.webp</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39033,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=guardian.ng</t>
+          <t>https://machibo.github.io/-/logos/guardian.ng.webp</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39105,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=londondaily.news</t>
+          <t>https://machibo.github.io/-/logos/londondaily.news.webp</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39177,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=london-post.co.uk</t>
+          <t>https://machibo.github.io/-/logos/london-post.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39249,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=omenontopp.com</t>
+          <t>https://machibo.github.io/-/logos/omenontopp.com.webp</t>
         </is>
       </c>
     </row>
@@ -39329,7 +39321,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=impactwealth.org</t>
+          <t>https://machibo.github.io/-/logos/impactwealth.org.webp</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39393,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=africa.businessinsider.com</t>
+          <t>https://machibo.github.io/-/logos/africa.businessinsider.com.webp</t>
         </is>
       </c>
     </row>
@@ -39473,7 +39465,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=measurescopez.com</t>
+          <t>https://machibo.github.io/-/logos/measurescopez.com.webp</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39537,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ukbusinesstimes.co.uk</t>
+          <t>https://machibo.github.io/-/logos/ukbusinesstimes.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39609,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=londoninsider.co.uk</t>
+          <t>https://machibo.github.io/-/logos/londoninsider.co.uk.webp</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39681,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=ibusiness.news</t>
+          <t>https://machibo.github.io/-/logos/ibusiness.news.webp</t>
         </is>
       </c>
     </row>
@@ -39761,7 +39753,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=theluxauthority.com</t>
+          <t>https://machibo.github.io/-/logos/theluxauthority.com.webp</t>
         </is>
       </c>
     </row>
@@ -39833,7 +39825,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=congress.net</t>
+          <t>https://machibo.github.io/-/logos/congress.net.webp</t>
         </is>
       </c>
     </row>
@@ -39905,7 +39897,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=bitzuma.com</t>
+          <t>https://machibo.github.io/-/logos/bitzuma.com.webp</t>
         </is>
       </c>
     </row>
@@ -39977,7 +39969,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=asiapresswire.com</t>
+          <t>https://machibo.github.io/-/logos/asiapresswire.com.webp</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40041,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=grazia.si</t>
+          <t>https://machibo.github.io/-/logos/grazia.si.webp</t>
         </is>
       </c>
     </row>
@@ -40121,7 +40113,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=luxuo.com</t>
+          <t>https://machibo.github.io/-/logos/luxuo.com.webp</t>
         </is>
       </c>
     </row>
@@ -40193,7 +40185,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=glamour.bg</t>
+          <t>https://machibo.github.io/-/logos/glamour.bg.webp</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40348,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=digitalbusiness.kz</t>
+          <t>https://machibo.github.io/-/logos/digitalbusiness.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40415,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=zakon.kz</t>
+          <t>https://machibo.github.io/-/logos/zakon.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40490,7 +40482,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=informburo.kz</t>
+          <t>https://machibo.github.io/-/logos/informburo.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40557,7 +40549,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=rasdaily.kz</t>
+          <t>https://machibo.github.io/-/logos/rasdaily.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40616,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=caravan.kz</t>
+          <t>https://machibo.github.io/-/logos/caravan.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40683,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=tengrinews.kz</t>
+          <t>https://machibo.github.io/-/logos/tengrinews.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40750,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=centralmedia24.kz</t>
+          <t>https://machibo.github.io/-/logos/centralmedia24.kz.webp</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40817,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://machibo.github.io/-/?d=orda.kz</t>
+          <t>https://machibo.github.io/-/logos/orda.kz.webp</t>
         </is>
       </c>
     </row>
